--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,10 +44,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <sz val="10"/>
     </font>
     <font>
@@ -101,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE2A8"/>
+        <fgColor rgb="00A9C7E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9C7E0"/>
+        <fgColor rgb="00E0625B"/>
       </patternFill>
     </fill>
     <fill>
@@ -116,12 +112,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4B9B5"/>
+        <fgColor rgb="00FBE2A8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0625B"/>
+        <fgColor rgb="00F4B9B5"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -175,25 +171,20 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -559,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K81"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -682,9 +673,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>PASS — masthead .brand-block → '/' present on home/about/404/phase0/brand/article; aria-label 'Dexter Jakes home'</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr"/>
@@ -731,9 +722,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>PASS — brand-word: Words (home/article/about/brand), 404, Phase 0 — matches documented intent</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -784,9 +775,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -833,16 +824,24 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — activating the skip link moved the fragment but not focus: &lt;main&gt; had no tabindex=-1, so document.activeElement stayed on &lt;body&gt; (all 7 surfaces)</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260807 2c7d88d): added tabindex="-1" to the 7 &lt;main&gt; landmarks (index/article/coming-soon/about/404/phase0/brand)</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — focus now lands on MAIN#archive (home) and MAIN#article (essay)</t>
         </is>
       </c>
     </row>
@@ -882,9 +881,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>PASS — 2 decorative rulers render</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr"/>
@@ -931,9 +930,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>PASS — footer strip + links present on all page types</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr"/>
@@ -980,24 +979,20 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>PASS — &lt;link rel=alternate atom&gt; present on home, about, phase0, article</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="4" t="inlineStr">
         <is>
           <t>FIX: Added &lt;link rel=alternate atom&gt; feed autodiscovery to ArticleLayout + ComingSoonLayout heads</t>
         </is>
       </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>PASS — feed link present on article + coming-soon</t>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -1037,9 +1032,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr"/>
@@ -1086,9 +1081,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1135,9 +1130,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>PASS — no horizontal overflow at 390px on home/article/about/phase0/brand/404</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr"/>
@@ -1188,9 +1183,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr"/>
@@ -1237,9 +1232,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand)</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1290,9 +1285,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor)</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr"/>
@@ -1339,9 +1334,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description)</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -1388,9 +1383,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1437,9 +1432,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>PASS — phase0 WebPage JSON-LD present and parses</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr"/>
@@ -1486,9 +1481,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>PASS — robots.txt Allow / + Sitemap → sitemap-index.xml</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
@@ -1535,9 +1530,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>PASS — sitemap-0.xml 20 locs = exactly the published set + about/brand/phase0; no missing, no orphans</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr"/>
@@ -1588,16 +1583,16 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>404 half PASS (noindex,nofollow live). Coming-soon half PENDING — no upcoming entry exists to render one</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="4" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -1637,9 +1632,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>PASS — Entry No. 16 / Week of July 5, 2026, LatestBar → newest essay</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -1690,9 +1685,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>PASS — IdentityHero renders; hero copy contrast 5.17:1 (AA large)</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr"/>
@@ -1739,9 +1734,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>PASS — Faith 13 / Identity 09 / Art 03, verified against frontmatter lanes; 16 articles</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -1792,24 +1787,24 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — lane-filter.js sets earlierWrap.hidden=true while filtered, but .earlier-more-wrap{display:flex} outranks the UA [hidden] rule, so the 'View Earlier Essays' button stayed on screen during a filter; clicking it revealed the 8 overflow plates regardless of lane, leaking non-matching essays into a filtered view (/words/gumbo/, Identity-only, under Faith)</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>FIX: lane-filter.js: clear() now restores each article's base hidden state (respects earlier-toggle); hides View-Earlier wrap while filtered</t>
+          <t>FIX (qa/fixes-20260807 ab07b15): added .earlier-more-wrap[hidden]{display:none} to css/home-v2.css — same guard the plates already carry in home-augment.css:398 — and bumped home-v2.css ?v=phase29→phase31 (assets are immutable/1y)</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>PASS — fresh 8 → filter 11 (wrap hidden) → clear 8, button stays collapsed; earlier toggle still works after cycle</t>
+          <t>PASS (verified against build) — filtered: wrap computed display none, offsetHeight 0, 0 client rects (unreachable by mouse or keyboard); Faith 13/13 and Identity 9/9 all-matching; clear restores the wrap</t>
         </is>
       </c>
     </row>
@@ -1849,9 +1844,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>PASS — lead plate = send-someone-else (newest published)</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr"/>
@@ -1898,9 +1893,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>PASS — 'This Month' = show-me-your-glory (same month as lead)</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr"/>
@@ -1947,9 +1942,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>PASS — 'Earlier' = 14, 6 visible + 8 overflow</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr"/>
@@ -2000,20 +1995,24 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — lane-filter.js sets earlierWrap.hidden=true while filtered, but .earlier-more-wrap{display:flex} outranks the UA [hidden] rule, so the 'View Earlier Essays' button stayed on screen during a filter; clicking it revealed the 8 overflow plates regardless of lane, leaking non-matching essays into a filtered view (/words/gumbo/, Identity-only, under Faith)</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>NOTE: plural + expand/collapse correct in isolation</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FIX (qa/fixes-20260807 ab07b15): added .earlier-more-wrap[hidden]{display:none} to css/home-v2.css — same guard the plates already carry in home-augment.css:398 — and bumped home-v2.css ?v=phase29→phase31 (assets are immutable/1y)</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — expand 8→16, collapse 16→8, aria-expanded + label track; collapse state still respected after a filter cycle</t>
         </is>
       </c>
     </row>
@@ -2053,9 +2052,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>PASS — 16 plates tile the 12-col grid (lead + wide/secondary/banner rotation, 3 row-plates)</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr"/>
@@ -2102,9 +2101,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>PASS — 7 of 15 archive plates carry .plate-image, interleaved with plain (Texture Alternation Rule)</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr"/>
@@ -2151,9 +2150,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>PASS — correctly absent: zero upcoming essays in the collection</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -2204,9 +2203,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>PASS — manifesto form action=/api/subscribe, source=home, honeypot present</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr"/>
@@ -2298,7 +2297,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>ArticleLayout.astro:133-141,217-226</t>
+          <t>ArticleLayout.astro:137-145,221-230</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
@@ -2306,24 +2305,20 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>PASS — eyebrow lanes/tags + ' + ' separator, date, read time, h1, deck</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr">
         <is>
           <t>FIX: Multi-tag ' + ' separator lived in an Astro &lt;style&gt; block that the build inlined; strict style-src 'self' CSP blocked it in production. Fixed via build.inlineStylesheets:'never' (external hashed CSS).</t>
         </is>
       </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>PASS — ::before content ' + ' now applied (rgb verified) via /_astro CSS, CSP-clean</t>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2350,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>[...slug].astro, ArticleLayout.astro:143-145</t>
+          <t>[...slug].astro, ArticleLayout.astro:147-149</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
@@ -2363,9 +2358,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>PASS — all 16 MDX bodies render through [...slug].astro</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
@@ -2416,9 +2411,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t>PASS — bar width 0→249→698→1153px and aria-valuenow 0→30→69→100 across the scroll range</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2469,9 +2464,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t>PASS — pill text tracks sections ('What the Fear Was Actually About' → 'A New Thing' → 'The Thirtieth'), opacity animates in</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -2514,7 +2509,7 @@
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>ArticleLayout.astro:147-153</t>
+          <t>ArticleLayout.astro:151-157</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
@@ -2522,9 +2517,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>PASS — X intent carries encoded url + title</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr"/>
@@ -2563,7 +2558,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>js/essay.js, ArticleLayout.astro:150,152, about.astro:135</t>
+          <t>js/essay.js, ArticleLayout.astro:154,156, about.astro:135</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -2571,9 +2566,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>PASS — copy button + [data-copy-status] live region on article and about</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
@@ -2616,7 +2611,7 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>ArticleLayout.astro:151, about.astro:136</t>
+          <t>ArticleLayout.astro:155, about.astro:136</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -2624,9 +2619,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>PASS — Follow Me → instagram.com/ImJustDex</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr"/>
@@ -2673,24 +2668,20 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t>PASS — form posts /api/subscribe with source=article, honeypot off-canvas, aria-live label; server states verified directly against the function</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>FIX: signup.js now parses JSON, checks res.ok &amp;&amp; data.ok; distinct success / already-subscribed / error states; re-enables submit on error</t>
         </is>
       </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>PASS — server 500 now shows 'Something broke…', button re-enabled, no false success</t>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2730,16 +2721,12 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t>Authored prev/next render correctly on all 16. Ghost/teaser path PENDING — requires a future-dated entry; none exists</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>FIX: ArticleLayout derives effective nextGhost from the target essay's real live status (getCollection + isPubliclyLive); stale frontmatter ghost flags ignored once target is live</t>
@@ -2747,7 +2734,7 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>PASS — pulpit/should-have-killed-it/not-the-same-as-alive render normal next + rel=next; ghost STILL shows when target genuinely upcoming (verified by future-dating)</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -2787,24 +2774,20 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>PASS — rel=prev emitted where prev authored; rel=next where next authored and live</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>FIX: rel=next head link now driven by derived nextGhost (present when next is live)</t>
         </is>
       </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>PASS — rel=next emitted for all 3 formerly-stale essays; suppressed only when target upcoming</t>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2844,9 +2827,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>PASS — '← Back' → '/' on article, coming-soon, about</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr"/>
@@ -2893,24 +2876,20 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>PASS — PullQuote, Scripture, Callout, DropCap, Closing, SectionHead, ResearchCTA, StudyNote all render and are styled via external hashed CSS (CSP-clean)</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr"/>
       <c r="J47" s="4" t="inlineStr">
         <is>
           <t>FIX: ScriptureList scoped &lt;style&gt; was inlined by the build and CSP-blocked in production (refs/borders unstyled). Fixed via build.inlineStylesheets:'never'.</t>
         </is>
       </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>PASS — .scripture-ref accent #cc0000 + uppercase + flex items now applied via external CSS</t>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -2950,9 +2929,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>PASS — &lt;details&gt; summary toggles open→closed→open on both sampled essays</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -3003,16 +2982,12 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>PENDING — all 16 entries are status published with past dates, so isUpcomingData() is false everywhere and no coming-soon page renders</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>FIX: Replaced 3 CSP-blocked inline style= attrs with .coming-tag/.coming-lead/.coming-note classes; styles now in external (Astro-hashed) CSS</t>
@@ -3020,7 +2995,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>PASS (live) — coming-tag bg #cc0000 applied, 0 inline styles, no console CSP errors</t>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -3060,9 +3035,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>PASS — about content + ProfilePage render</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -3109,24 +3084,20 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I51" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>PASS — share bar X + copy + Follow Me with live region</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>FIX: Added &lt;span data-copy-status role=status aria-live&gt; to About share bar (parity with articles)</t>
         </is>
       </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>PASS — copy now announces to the live region</t>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3166,9 +3137,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H52" s="6" t="inlineStr">
+        <is>
+          <t>PASS — bespoke notfound-plate, 200 on /404, noindex+nofollow, /* fallback 404s unmatched routes</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
@@ -3219,9 +3190,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H53" s="6" t="inlineStr">
+        <is>
+          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -3272,9 +3243,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H54" s="6" t="inlineStr">
+        <is>
+          <t>PASS — feed.xsl 200 and &lt;?xml-stylesheet?&gt; PI present</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -3325,9 +3296,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H55" s="6" t="inlineStr">
+        <is>
+          <t>PASS — 5 anchor links, all resolve to real targets</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr"/>
@@ -3378,20 +3349,24 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — phase0/index.html:374 still carried the legacy Mailchimp query string (?u=…&amp;id=…&amp;f_id=…) on the form action; the one surface 4377cfd missed</t>
+        </is>
+      </c>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>NOTE: invalid-&gt;error+aria-invalid; 500-&gt;error+Retry (no false success)</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FIX (qa/fixes-20260807 69d63f3): action reduced to /api/subscribe, matching the other three surfaces</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — state machine idle, source=phase0, honeypot intact, 0 console errors</t>
         </is>
       </c>
     </row>
@@ -3431,9 +3406,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H57" s="6" t="inlineStr">
+        <is>
+          <t>PASS — footer year 2026 = current year</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr"/>
@@ -3484,20 +3459,24 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — /brand/ pinned /css/plates.css?v=phase13 while every other surface serves ?v=phase15; under max-age=31536000 immutable that is a second year-long cache entry, defeating the bust on the dogfood page</t>
+        </is>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>NOTE: 200, 115KB, relaxed CSP</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FIX (qa/fixes-20260807 5967c9a): brand/index.html bumped to ?v=phase15</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — /brand/ serves plates.css?v=phase15, 0 console errors, no broken images</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3508,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>netlify/functions/subscribe.js:52-54</t>
+          <t>netlify/functions/subscribe.cjs:52-54</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
@@ -3537,9 +3516,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H59" s="6" t="inlineStr">
+        <is>
+          <t>PASS — GET /api/subscribe → 405 method_not_allowed</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr"/>
@@ -3582,7 +3561,7 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>netlify/functions/subscribe.js:9-22,61-63</t>
+          <t>netlify/functions/subscribe.cjs:9-22,61-63</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
@@ -3590,9 +3569,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>PASS — rate-limit bucket present (5/60s per IP)</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr"/>
@@ -3635,7 +3614,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>netlify/functions/subscribe.js:67-69</t>
+          <t>netlify/functions/subscribe.cjs:67-69</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
@@ -3643,9 +3622,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>PASS — filled honeypot → 200 silent success, no Mailchimp write; field off-canvas (left:-5000px, tabindex -1, aria-hidden)</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -3688,7 +3667,7 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>netlify/functions/subscribe.js:36-38,71-74</t>
+          <t>netlify/functions/subscribe.cjs:36-38,71-74</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
@@ -3696,9 +3675,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>PASS — invalid address → 400 invalid_email; plus-addressed valid address accepted (clients encode + as %2B via URLSearchParams(FormData))</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr"/>
@@ -3741,7 +3720,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>netlify/functions/subscribe.js:76-134</t>
+          <t>netlify/functions/subscribe.cjs:76-134</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3749,9 +3728,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H63" s="6" t="inlineStr">
+        <is>
+          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3794,7 +3773,7 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>netlify/functions/subscribe.js:87-132</t>
+          <t>netlify/functions/subscribe.cjs:87-132</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
@@ -3802,24 +3781,20 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="H64" s="6" t="inlineStr">
+        <is>
+          <t>PASS — source field present on all 4 surfaces (home/article/coming-soon/phase0)</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="4" t="inlineStr">
         <is>
           <t>FIX: Added hidden source='coming-soon' field + aria-live to the coming-soon signup label</t>
         </is>
       </c>
-      <c r="K64" s="6" t="inlineStr">
-        <is>
-          <t>PASS — source field present, attributed correctly</t>
+      <c r="K64" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3826,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>netlify/functions/subscribe.js:80-113</t>
+          <t>netlify/functions/subscribe.cjs:80-113</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3859,9 +3834,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H65" s="6" t="inlineStr">
+        <is>
+          <t>PASS — documented error envelope returned, no stack leakage</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr"/>
@@ -3870,9 +3845,9 @@
           <t>FIX: Renamed function subscribe.js → subscribe.cjs (unambiguous CommonJS under package type:module); silences esbuild ESM warning</t>
         </is>
       </c>
-      <c r="K65" s="6" t="inlineStr">
-        <is>
-          <t>PASS — endpoint works post-rename (405 / 400 invalid_email / 200 honeypot)</t>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -3912,20 +3887,24 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — dxjakes.com now returns HTTP 401 (was 200). A Netlify site-protection layer answers before redirect rules evaluate, so netlify.toml's absolute-URL 301s to imjustdex.com provably never fire; legacy inbound links hit an auth wall</t>
+        </is>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>NOTE: config correct (absolute-URL host redirect); not locally testable</t>
-        </is>
-      </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>BLOCKED — NEEDS DEXTER. Remedy is Netlify domain / site-protection settings on the legacy site, outside the repo (QA-OS fix-phase guardrail: third-party dashboard)</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3936,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>netlify.toml:200-278, astro.config.mjs</t>
+          <t>netlify.toml:197-299, astro.config.mjs</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -3965,9 +3944,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -4018,9 +3997,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>PASS — /words and /words/ → 301 home</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr"/>
@@ -4071,9 +4050,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>PASS — /opsmeeting, /leadership-prep, /asana-workflow (+ /*) all → 301 home</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr"/>
@@ -4116,7 +4095,7 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>netlify.toml:180-183</t>
+          <t>netlify.toml:191-194</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
@@ -4124,9 +4103,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>PASS — /api/subscribe rewrite reaches the function (405 on GET, 400/200 on POST)</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr"/>
@@ -4177,9 +4156,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>PASS — unmatched route → 404 with the branded body</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr"/>
@@ -4230,9 +4209,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -4241,9 +4220,9 @@
           <t>FIX: No CSP change needed — kept strict style-src 'self'; build now emits external CSS (inlineStylesheets:'never') instead of CSP-violating inline &lt;style&gt;. Added /_astro/* immutable cache header.</t>
         </is>
       </c>
-      <c r="K72" s="6" t="inlineStr">
-        <is>
-          <t>PASS — strict CSP intact; per-route overrides intact; component styles now external + applied</t>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -4283,9 +4262,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
@@ -4336,20 +4315,24 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="I74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — /brand/brand.css (versioned ?v=brand5) and /brand/img/* (~758KB) matched no Cache-Control rule in netlify.toml and fell through to public,max-age=0,must-revalidate</t>
+        </is>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>NOTE: config correct; netlify dev forces max-age=0 locally, prod honors immutable</t>
-        </is>
-      </c>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FIX (qa/fixes-20260807 5967c9a): added scoped [[headers]] for /brand/brand.css and /brand/img/* with the immutable policy; /brand/index.html deliberately left no-cache</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — netlify.toml parses, 12 header blocks, HTML rules unchanged</t>
         </is>
       </c>
     </row>
@@ -4389,9 +4372,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
+          <t>PASS — predicate gates homepage/feed/sitemap/routes consistently; 16 published, 0 upcoming</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr"/>
@@ -4442,9 +4425,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>PASS — daily-rebuild.yml fired 06:13Z today; Netlify commit_ref == GitHub main HEAD (8f5ba93)</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr"/>
@@ -4495,9 +4478,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>PASS — scripts/og-plate.mjs present; all 19 OG plates render and 200</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr"/>
@@ -4548,9 +4531,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page)</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr"/>
@@ -4601,9 +4584,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
+          <t>PASS — :focus-visible rules present in all 8 stylesheets; first Tab lands on .skip-link</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr"/>
@@ -4654,9 +4637,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H80" s="6" t="inlineStr">
+        <is>
+          <t>PASS — 15 sampled selectors all meet WCAG AA (min 5.17:1 large, 5.94:1 small) in dark mode</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr"/>
@@ -4707,9 +4690,9 @@
           <t>Cataloged</t>
         </is>
       </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="H81" s="6" t="inlineStr">
+        <is>
+          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr"/>
@@ -4724,8 +4707,167 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>F79</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Build / Automation</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>One-time scheduled publish workflow (hour-precise essay release)</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>As the author, I want an essay to go live at a specific HOUR rather than daily-rebuild's ~00:05 CT window, and stay fully hidden until then, so a dated release lands exactly when I intend.</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>cron '5 17 5 7 *' + workflow_dispatch. Guarded twice: exits 0 unless year==2026, and exits 0 unless the file still matches ^status: "drafted"$. Only on a live match does it flip status to published, commit as github-actions[bot] and push main (triggering the Netlify build). After firing, every future invocation must be a no-op — any post-fire github-actions[bot] commit on main is a CRITICAL unattended write to the deployed branch.</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>.github/workflows/publish-send-someone-else.yml, src/content/words/send-someone-else.mdx</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H82" s="6" t="inlineStr">
+        <is>
+          <t>PASS — fired as designed on 2026-07-05 (ecf2c34, github-actions[bot], 18:03:14Z); both guards now permanently closed (year!=2026, status no longer 'drafted'); no post-fire bot commit exists on main</t>
+        </is>
+      </c>
+      <c r="I82" s="6" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260807 11d1430, OPTIONAL): file removed — spent, and its own header says 'safe to delete any time after 2026-07-05'. Removes a standing contents:write + push-to-main capability on a yearly cron. daily-rebuild.yml untouched.</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — workflow absent; nothing references it; daily-rebuild.yml intact</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>F80</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Routing / Redirects</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Per-article trailing-slash redirect parity</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>As a reader landing on a non-slash article URL from a pasted link or old share, I get one 301 to the canonical slash URL instead of a 404 — for every published essay including the newest.</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>netlify.toml carries exactly one [[redirects]] /words/&lt;slug&gt; → /words/&lt;slug&gt;/ 301 (no force — force loops) for every status:"published" entry in src/content/words/. Parity test: redirect slug set == published slug set. A published slug with no rule = HIGH (non-slash 404s). The list is hand-maintained and has drifted once already (show-me-your-glory and send-someone-else went live 2026-07-03/07-05 with no rule until 8f5ba93 backfilled them ~a month later).</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>netlify.toml:197-299, src/content/words/*.mdx, src/utils/published.mjs</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H83" s="6" t="inlineStr">
+        <is>
+          <t>PASS — parity 16/16 verified live; every /words/&lt;slug&gt; returns a single 301 to its trailing-slash canonical; no orphan rules</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>F81</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Forward-nav stitch completeness across the essay chain</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>As a reader walking the essays forward, I want every essay except the newest to offer a Next link, so the chain never dead-ends before the latest piece.</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>prev/next are hand-authored frontmatter (config.ts marks both .optional(); ArticleLayout never synthesizes a missing next). Invariant: every entry except the chronologically newest published essay carries a next{slug,title}. Violation = forward dead-end + no rel=next.</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>src/content/words/*.mdx (prev/next frontmatter), src/content/config.ts, src/layouts/ArticleLayout.astro</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H84" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — show-me-your-glory (2026-07-03) carries no next, so the forward chain stops there and never reaches send-someone-else (2026-07-05); no rel=next emitted. 15 of 16 links are chronological and reciprocal. Cause: 70baf7b stitched outsourced-faith forward while send-someone-else was in flight on a parallel branch merged the same day, so nothing stitched glory forward. NOT a defect and explicitly excluded: send-someone-else.prev → 'some' is deliberate (authored 2026-07-02 before glory existed, and the pulpit→some→send-someone-else calling thread is named in the essay body).</t>
+        </is>
+      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — NEEDS DEXTER. Editorial: writing a next{} block asserts a reading order (his voice, not a behavior repair), and three mutually exclusive resolutions exist — (1) stitch glory→send-someone-else and accept the first non-reciprocal pair, (2) repoint send-someone-else.prev to glory and break the calling thread, or (3) leave it, with glory ending the chronological trunk.</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K81"/>
+  <autoFilter ref="A3:K84"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4740,7 +4882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4748,14 +4890,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -4767,8 +4909,8 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>68</v>
+      <c r="B4" s="12" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -4777,22 +4919,22 @@
           <t>ISSUE</t>
         </is>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>9</v>
+      <c r="B5" s="13" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="n">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
@@ -4804,71 +4946,81 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="B9" s="12" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="n">
-        <v>6</v>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B15" s="17" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Resolved (P4 PASS)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="B17" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>Total features: 78</t>
+      <c r="B18" s="20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Total features: 81</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -73,7 +73,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +108,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0C24B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2E2DE"/>
       </patternFill>
     </fill>
     <fill>
@@ -147,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -174,9 +179,13 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,7 +193,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3864,17 +3873,17 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Legacy domain → canonical</t>
+          <t>Legacy domain → canonical (RETIRED — dxjakes.com is a separate property)</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>As a visitor on the old dxjakes.com, I want to be 301'd to imjustdex.com keeping my path, so old links still work and the brand is unified.</t>
+          <t>[RETIRED 2026-08-07] Originally: as someone landing on the pre-migration domain, I want a 301 to imjustdex.com. Dexter confirmed he uses dxjakes.com for a different property, so this is no longer a goal.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>https://dxjakes.com/* and https://www.dxjakes.com/* → https://imjustdex.com/:splat, 301, force.</t>
+          <t>N/A — dxjakes.com is OUT OF SCOPE for this site's health. Do not probe it, do not flag whatever it returns. NOTE: netlify.toml still carries absolute-URL 301 rules (`https://dxjakes.com/*` and the www variant → imjustdex.com/:splat, force=true). They do not fire today because that host answers 401 before redirect rules evaluate — but they are stale intent and a latent hazard: if that protection layer is ever removed while dxjakes.com is still an alias of this Netlify site, its traffic would start redirecting here. Flagged for Dexter's decision; not removed unattended (routing change).</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3889,22 +3898,18 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — dxjakes.com now returns HTTP 401 (was 200). A Netlify site-protection layer answers before redirect rules evaluate, so netlify.toml's absolute-URL 301s to imjustdex.com provably never fire; legacy inbound links hit an auth wall</t>
-        </is>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>N/A — retired by owner decision 2026-08-07</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER. Remedy is Netlify domain / site-protection settings on the legacy site, outside the repo (QA-OS fix-phase guardrail: third-party dashboard)</t>
-        </is>
-      </c>
-      <c r="K66" s="6" t="inlineStr">
-        <is>
-          <t>PENDING</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4890,14 +4895,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="12" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -4909,7 +4914,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="13" t="n">
         <v>70</v>
       </c>
     </row>
@@ -4919,106 +4924,126 @@
           <t>ISSUE</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>8</v>
+      <c r="B5" s="14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B7" s="16" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n">
-        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="B12" s="16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B17" s="19" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Resolved (P4 PASS)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B19" s="13" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="B20" s="22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Total features: 81</t>
         </is>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -112,12 +112,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2E2DE"/>
+        <fgColor rgb="00FBE2A8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBE2A8"/>
+        <fgColor rgb="00E2E2DE"/>
       </patternFill>
     </fill>
     <fill>
@@ -152,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -179,14 +179,11 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3883,7 +3880,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>N/A — dxjakes.com is OUT OF SCOPE for this site's health. Do not probe it, do not flag whatever it returns. NOTE: netlify.toml still carries absolute-URL 301 rules (`https://dxjakes.com/*` and the www variant → imjustdex.com/:splat, force=true). They do not fire today because that host answers 401 before redirect rules evaluate — but they are stale intent and a latent hazard: if that protection layer is ever removed while dxjakes.com is still an alias of this Netlify site, its traffic would start redirecting here. Flagged for Dexter's decision; not removed unattended (routing change).</t>
+          <t>N/A — dxjakes.com is OUT OF SCOPE for this site's health. Do not probe it, do not flag whatever it returns. The two absolute-URL 301s that used to live in netlify.toml (`https://dxjakes.com/*` and the www variant → imjustdex.com/:splat, force=true) were REMOVED 2026-08-07 at Dexter's instruction. They were dormant only because that host answers 401 before redirect rules evaluate; had that protection ever been lifted while the domain was still an alias of this Netlify site, all its traffic would have collapsed onto imjustdex.com. A tombstone comment sits at netlify.toml:173 so no future edit silently re-arms them. Regression check: `grep -c 'dxjakes' netlify.toml` must match only the comment — zero [[redirects]] blocks.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -3904,12 +3901,12 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K66" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
+          <t>FIX (1e0a0d4): removed both dxjakes.com [[redirects]] blocks from netlify.toml (30 → 28 rules); replaced with a tombstone comment explaining why they must not come back.</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>PASS — netlify.toml parses, 28 redirects, 0 dxjakes rules, /api/subscribe rewrite intact and now first in the chain.</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4895,14 +4892,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -4914,7 +4911,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="12" t="n">
         <v>70</v>
       </c>
     </row>
@@ -4924,7 +4921,7 @@
           <t>ISSUE</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="13" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4934,7 +4931,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4944,12 +4941,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
@@ -4961,41 +4958,41 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
-        <v>76</v>
+      <c r="B10" s="12" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
         <v>4</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>— Issues by severity (found) —</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>— Issues by severity (found) —</t>
-        </is>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
@@ -5005,45 +5002,35 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>Resolved (P4 PASS)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="20" t="inlineStr">
         <is>
-          <t>Resolved (P4 PASS)</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n">
+      <c r="B19" s="21" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Total features: 81</t>
         </is>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -73,7 +73,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -120,11 +120,6 @@
         <fgColor rgb="00E2E2DE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B9B5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -152,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -190,7 +185,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4852,19 +4846,15 @@
           <t>ISSUE — show-me-your-glory (2026-07-03) carries no next, so the forward chain stops there and never reaches send-someone-else (2026-07-05); no rel=next emitted. 15 of 16 links are chronological and reciprocal. Cause: 70baf7b stitched outsourced-faith forward while send-someone-else was in flight on a parallel branch merged the same day, so nothing stitched glory forward. NOT a defect and explicitly excluded: send-someone-else.prev → 'some' is deliberate (authored 2026-07-02 before glory existed, and the pulpit→some→send-someone-else calling thread is named in the essay body).</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER. Editorial: writing a next{} block asserts a reading order (his voice, not a behavior repair), and three mutually exclusive resolutions exist — (1) stitch glory→send-someone-else and accept the first non-reciprocal pair, (2) repoint send-someone-else.prev to glory and break the calling thread, or (3) leave it, with glory ending the chronological trunk.</t>
+          <t>FIX (2026-08-07, Dexter's call — resolution 1 of 3): added next{slug:'send-someone-else', title:'Send Someone Else', ghost:false} to show-me-your-glory.mdx. Editorial decision made by Dexter, not by the loop. NOTE this intentionally creates the corpus's first NON-RECIPROCAL pair: glory now points forward to send-someone-else, but send-someone-else.prev still points back to 'some' — the deliberate pulpit → some → send-someone-else calling thread. That asymmetry is by design; do not 'fix' it in a future run.</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS (verified against build, then live) — show-me-your-glory emits &lt;link rel=next&gt; to send-someone-else and renders a normal 'Next Essay → Send Someone Else' nav (no ghost class, since ArticleLayout derives ghost from the target's real live status). Forward chain now walks all 16 published essays end to end: reckonings → … → show-me-your-glory → send-someone-else. Zero non-newest essays lack a next.</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4949,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -4969,7 +4959,7 @@
         </is>
       </c>
       <c r="B11" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -5006,7 +4996,7 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -5025,8 +5015,8 @@
           <t>Still open</t>
         </is>
       </c>
-      <c r="B19" s="21" t="n">
-        <v>1</v>
+      <c r="B19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,12 +48,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -97,17 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9C7E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E0625B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0C24B"/>
+        <fgColor rgb="00A9C7E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,6 +113,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2E2DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B9B5"/>
       </patternFill>
     </fill>
   </fills>
@@ -147,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -171,20 +171,17 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -826,14 +823,10 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — activating the skip link moved the fragment but not focus: &lt;main&gt; had no tabindex=-1, so document.activeElement stayed on &lt;body&gt; (all 7 surfaces)</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production.</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>FIX (qa/fixes-20260807 2c7d88d): added tabindex="-1" to the 7 &lt;main&gt; landmarks (index/article/coming-soon/about/404/phase0/brand)</t>
@@ -1789,14 +1782,10 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — lane-filter.js sets earlierWrap.hidden=true while filtered, but .earlier-more-wrap{display:flex} outranks the UA [hidden] rule, so the 'View Earlier Essays' button stayed on screen during a filter; clicking it revealed the 8 overflow plates regardless of lane, leaking non-matching essays into a filtered view (/words/gumbo/, Identity-only, under Faith)</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>PASS — live-verified 2026-08-10: Faith 13/13, Identity 9/9, Art 3/3 with zero non-matching plates in any filtered view; while filtered the .earlier-more-wrap computes display:none, 0 client rects, offsetHeight 0 (unreachable by mouse or keyboard). The ab07b15 fix holds in production.</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>FIX (qa/fixes-20260807 ab07b15): added .earlier-more-wrap[hidden]{display:none} to css/home-v2.css — same guard the plates already carry in home-augment.css:398 — and bumped home-v2.css ?v=phase29→phase31 (assets are immutable/1y)</t>
@@ -1997,14 +1986,10 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — lane-filter.js sets earlierWrap.hidden=true while filtered, but .earlier-more-wrap{display:flex} outranks the UA [hidden] rule, so the 'View Earlier Essays' button stayed on screen during a filter; clicking it revealed the 8 overflow plates regardless of lane, leaking non-matching essays into a filtered view (/words/gumbo/, Identity-only, under Faith)</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
+          <t>PASS — live-verified 2026-08-10: expand 8→16, collapse 16→8, aria-expanded false↔true and the button label track; collapse state survives a full filter cycle (clear restores the wrap to display:flex).</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>FIX (qa/fixes-20260807 ab07b15): added .earlier-more-wrap[hidden]{display:none} to css/home-v2.css — same guard the plates already carry in home-augment.css:398 — and bumped home-v2.css ?v=phase29→phase31 (assets are immutable/1y)</t>
@@ -2419,7 +2404,7 @@
       <c r="I38" s="6" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>NOTE: code+elements verified; live scroll not exercisable (headless rAF/scroll throttled)</t>
+          <t>NOTE: code+elements verified; live scroll not exercisable (headless rAF/scroll throttled) | 2026-08-10: re-verification again harness-blocked — browser pane viewport 0x0, window.scrollTo a no-op, so scroll-driven width could not be re-exercised. Static wiring confirmed live: progress.js sets role=progressbar, aria-label, aria-valuemin/max/now on load. Prior PASS retained; not downgraded on a tooling limit.</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
@@ -3351,14 +3336,10 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — phase0/index.html:374 still carried the legacy Mailchimp query string (?u=…&amp;id=…&amp;f_id=…) on the form action; the one surface 4377cfd missed</t>
-        </is>
-      </c>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+          <t>PASS — live-verified 2026-08-10: /phase0/ form action is /api/subscribe with no legacy Mailchimp query string; matches the other three subscribe surfaces.</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr"/>
       <c r="J56" s="4" t="inlineStr">
         <is>
           <t>FIX (qa/fixes-20260807 69d63f3): action reduced to /api/subscribe, matching the other three surfaces</t>
@@ -3461,14 +3442,10 @@
       </c>
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — /brand/ pinned /css/plates.css?v=phase13 while every other surface serves ?v=phase15; under max-age=31536000 immutable that is a second year-long cache entry, defeating the bust on the dogfood page</t>
-        </is>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>PASS — live-verified 2026-08-10: /brand/ serves plates.css?v=phase15, matching every other surface; no second year-long cache entry.</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr"/>
       <c r="J58" s="4" t="inlineStr">
         <is>
           <t>FIX (qa/fixes-20260807 5967c9a): brand/index.html bumped to ?v=phase15</t>
@@ -4313,14 +4290,10 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — /brand/brand.css (versioned ?v=brand5) and /brand/img/* (~758KB) matched no Cache-Control rule in netlify.toml and fell through to public,max-age=0,must-revalidate</t>
-        </is>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate.</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="4" t="inlineStr">
         <is>
           <t>FIX (qa/fixes-20260807 5967c9a): added scoped [[headers]] for /brand/brand.css and /brand/img/* with the immutable policy; /brand/index.html deliberately left no-cache</t>
@@ -4582,18 +4555,22 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>PASS — :focus-visible rules present in all 8 stylesheets; first Tab lands on .skip-link</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr"/>
+          <t>ISSUE — .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) has base and :hover styling but NO :focus-visible rule, so the site's primary conversion control shows no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control is covered — .sm-input directly above it has the rule, and .sm-submit is even named in home-augment.css's prefers-reduced-motion block — so this is an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control; enumerating all 34 interactive elements on the homepage against the 27 focus selectors in the live CSS surfaced it.</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>NOTE: focus-visible defined across all css files</t>
-        </is>
-      </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FIX (qa/fixes-20260810): added .subscribe-manifesto .sm-submit:focus-visible {outline: var(--focus-ring-width) solid var(--focus-ring); outline-offset:-2px} to css/home-augment.css, matching the .sm-input rule immediately above (inset ring, since the button sits on --ink). Bumped home-augment.css ?v=phase25→phase32 in src/layouts/HomeLayout.astro and brand/index.html — the asset is served immutable/1y, so both references had to move together.</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — npm run build clean, 19 pages; dist/css/home-augment.css carries the rule; dist/index.html and dist/brand/index.html both reference ?v=phase32 with zero stale phase25 refs; dev server fetch of /css/home-augment.css?v=phase32 returns the rule text. Runtime paint of the ring could NOT be exercised — the browser pane reported a 0x0 viewport, so :focus-visible modality and Tab traversal were unavailable. Live-verify on the next scrub after merge.</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4820,7 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — show-me-your-glory (2026-07-03) carries no next, so the forward chain stops there and never reaches send-someone-else (2026-07-05); no rel=next emitted. 15 of 16 links are chronological and reciprocal. Cause: 70baf7b stitched outsourced-faith forward while send-someone-else was in flight on a parallel branch merged the same day, so nothing stitched glory forward. NOT a defect and explicitly excluded: send-someone-else.prev → 'some' is deliberate (authored 2026-07-02 before glory existed, and the pulpit→some→send-someone-else calling thread is named in the essay body).</t>
+          <t>PASS — live-verified 2026-08-10: show-me-your-glory emits rel=next to send-someone-else and renders a normal (non-ghost) forward nav; forward chain walks all 16 published essays end to end.</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr"/>
@@ -4858,8 +4835,65 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>F82</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Design-system doc ↔ implementation parity (accent permitted-use list)</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>As the site's maintainer (or an automated QA run), I want DESIGN-SYSTEM.md's permitted accent-use list to match what the CSS actually ships, so neither a contributor nor a future scrub 'corrects' a deliberate design decision back out.</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>Every entry in DESIGN-SYSTEM.md §'Permitted' accent uses resolves to a live rule using var(--accent) / var(--accent-text); anything the CSS deliberately renders in another token is absent from that list or annotated with its rationale.</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>DESIGN-SYSTEM.md:112-123, css/article.css:876-886</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H85" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE — DESIGN-SYSTEM.md:115 lists "Reading progress bar (`var(--accent)`)" as a permitted accent use, but css/article.css:882 ships `.reading-progress { background: var(--ink) }`. Commit 68b0c1d (2026-04-10) recolored it on purpose and left the reason in the CSS: "Reading progress uses --ink rather than --accent so the red accent stays reserved for section heads, callouts, and underlines. A red bar at the top of the viewport was competing with the masthead." That commit rewrote 136 lines of DESIGN-SYSTEM.md but missed this bullet, which dates to c75ded9 earlier the same day. The CSS is correct; the doc line is stale. Live-confirmed today: bar computes rgb(5,5,5) = --ink.</t>
+        </is>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — NEEDS DEXTER. Not auto-fixed for two reasons: (1) DESIGN-SYSTEM.md carries Dexter's uncommitted working-tree edit (the "Two-plane rule" addition), and the fix-phase rule is to leave his in-flight changes alone; (2) although the code comment makes the intent unambiguous, reconciling a brand doc against its implementation is a design-intent call, not a behaviour repair. Recommended resolution (Dexter's pick): strike line 115 from the permitted list, or re-add it annotated "— superseded 2026-04-10, see css/article.css:876".</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>PENDING — blocked on the decision above.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K84"/>
+  <autoFilter ref="A3:K85"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4874,7 +4908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4882,14 +4916,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -4901,8 +4935,8 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
-        <v>70</v>
+      <c r="B4" s="11" t="n">
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -4911,8 +4945,8 @@
           <t>ISSUE</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
-        <v>7</v>
+      <c r="B5" s="12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4921,7 +4955,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4931,12 +4965,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
@@ -4948,7 +4982,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <v>78</v>
       </c>
     </row>
@@ -4958,12 +4992,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
-        <v>3</v>
+      <c r="B11" s="14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
@@ -4975,54 +5009,44 @@
           <t>High</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>2</v>
+      <c r="B14" s="15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
-        <v>2</v>
+      <c r="B15" s="16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Resolved (P4 PASS)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>Resolved (P4 PASS)</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Total features: 81</t>
+      <c r="B18" s="19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Total features: 82</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update</t>
+          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks.</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>PASS — bar width 0→249→698→1153px and aria-valuenow 0→30→69→100 across the scroll range</t>
+          <t>PASS — bar width 0→249→698→1153px and aria-valuenow 0→30→69→100 across the scroll range. 2026-08-10 PM re-check: structural half re-verified (progress.js math recomputed by hand at 50% scroll = 51.5%; .article-body + .reading-progress present; role/aria-label/aria-valuemin/max initialized on load). Runtime paint not re-exercisable this run — the browser pane reports document.visibilityState 'hidden', so requestAnimationFrame never fires and the CSS width transition stays frozen at 0. Harness limitation, not a site regression.</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>PASS — pill text tracks sections ('What the Fear Was Actually About' → 'A New Thing' → 'The Thirtieth'), opacity animates in</t>
+          <t>PASS — pill text tracks sections ('What the Fear Was Actually About' → 'A New Thing' → 'The Thirtieth'), opacity animates in. 2026-08-10 PM re-check: section collection re-verified live (5 .section-head h2 landmarks found on /words/send-someone-else/; the 40%-viewport rule resolves to the correct current section). Opacity fade not observable this run — same hidden-tab rAF/transition suspension as F35.</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Authored prev/next render correctly on all 16. Ghost/teaser path PENDING — requires a future-dated entry; none exists</t>
+          <t>Authored prev/next render correctly on all 16. Ghost/teaser path PENDING — requires a future-dated entry; none exists. 2026-08-10 PM: the derive-from-live-status fix (p3) live-verified — 4 essays still carry stale ghost:true frontmatter (next-verse.prev→job, not-the-same-as-alive.next→music-that-raised-me, pulpit.next→the-stone, should-have-killed-it.next→job) and all 4 render as real .article-nav-link anchors with rel=prev/next plus matching &lt;link rel&gt; head tags. No ghost teaser leaks.</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr"/>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — npm run build clean, 19 pages; dist/css/home-augment.css carries the rule; dist/index.html and dist/brand/index.html both reference ?v=phase32 with zero stale phase25 refs; dev server fetch of /css/home-augment.css?v=phase32 returns the rule text. Runtime paint of the ring could NOT be exercised — the browser pane reported a 0x0 viewport, so :focus-visible modality and Tab traversal were unavailable. Live-verify on the next scrub after merge.</t>
+          <t>PASS (runtime-verified on build, 2026-08-10 12:5x) — keyboard Tab from .sm-input lands on .sm-submit; el.matches(':focus-visible') === true and the computed outline is 'solid 2px rgb(204, 0, 0)' at outline-offset -2px, served from home-augment.css?v=phase32 on the local dev build. Ring contrast against the button's --ink face passes SC 1.4.11 in both modes (5.17:1 dark, 3.44:1 light). This supersedes the morning run's build-only verification, which could not exercise focus modality (0x0 viewport). Live-verify on the next scrub after merge — live CSS still ships phase25 without the rule.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,11 +48,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
@@ -73,7 +68,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -93,11 +88,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6E7C9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0625B"/>
       </patternFill>
     </fill>
     <fill>
@@ -147,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -168,20 +158,16 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4555,12 +4541,12 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) has base and :hover styling but NO :focus-visible rule, so the site's primary conversion control shows no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control is covered — .sm-input directly above it has the rule, and .sm-submit is even named in home-augment.css's prefers-reduced-motion block — so this is an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control; enumerating all 34 interactive elements on the homepage against the 27 focus selectors in the live CSS surfaced it.</t>
-        </is>
-      </c>
-      <c r="I79" s="7" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4.</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>High (resolved)</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
@@ -4570,7 +4556,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>PASS (runtime-verified on build, 2026-08-10 12:5x) — keyboard Tab from .sm-input lands on .sm-submit; el.matches(':focus-visible') === true and the computed outline is 'solid 2px rgb(204, 0, 0)' at outline-offset -2px, served from home-augment.css?v=phase32 on the local dev build. Ring contrast against the button's --ink face passes SC 1.4.11 in both modes (5.17:1 dark, 3.44:1 light). This supersedes the morning run's build-only verification, which could not exercise focus modality (0x0 viewport). Live-verify on the next scrub after merge — live CSS still ships phase25 without the rule.</t>
+          <t>PASS (live-verified 2026-08-10 13:31 CDT, deploy d364718) — merged to main and shipped at Dexter's explicit instruction. Live https://imjustdex.com/ and /brand/ both reference home-augment.css?v=phase32; the live sheet serves the rule; on the live homepage .sm-submit matches ':focus-visible' and computes outline 'solid 2px rgb(204, 0, 0)' at outline-offset -2px over the button's --ink face (rgb(5,5,5)). Ring contrast passes SC 1.4.11 in both modes (5.17:1 dark, 3.44:1 light). Verification ladder this day: build-verified 05:06 → runtime-verified on dev build 13:05 → live-verified on production 13:31.</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4862,7 @@
           <t>ISSUE — DESIGN-SYSTEM.md:115 lists "Reading progress bar (`var(--accent)`)" as a permitted accent use, but css/article.css:882 ships `.reading-progress { background: var(--ink) }`. Commit 68b0c1d (2026-04-10) recolored it on purpose and left the reason in the CSS: "Reading progress uses --ink rather than --accent so the red accent stays reserved for section heads, callouts, and underlines. A red bar at the top of the viewport was competing with the masthead." That commit rewrote 136 lines of DESIGN-SYSTEM.md but missed this bullet, which dates to c75ded9 earlier the same day. The CSS is correct; the doc line is stale. Live-confirmed today: bar computes rgb(5,5,5) = --ink.</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="I85" s="7" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -4908,7 +4894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4916,14 +4902,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -4935,8 +4921,8 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
-        <v>76</v>
+      <c r="B4" s="10" t="n">
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -4945,8 +4931,8 @@
           <t>ISSUE</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>2</v>
+      <c r="B5" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -4955,7 +4941,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4965,12 +4951,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
@@ -4982,7 +4968,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="10" t="n">
         <v>78</v>
       </c>
     </row>
@@ -4992,12 +4978,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="13" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
@@ -5006,45 +4992,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Resolved (P4 PASS)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Resolved (P4 PASS)</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Still open</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Still open</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Total features: 82</t>
         </is>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,11 +48,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00CC0000"/>
       <sz val="13"/>
     </font>
@@ -68,7 +63,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -92,22 +87,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9C7E0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FBE2A8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E2E2DE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B9B5"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -155,19 +135,13 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4859,22 +4833,22 @@
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>ISSUE — DESIGN-SYSTEM.md:115 lists "Reading progress bar (`var(--accent)`)" as a permitted accent use, but css/article.css:882 ships `.reading-progress { background: var(--ink) }`. Commit 68b0c1d (2026-04-10) recolored it on purpose and left the reason in the CSS: "Reading progress uses --ink rather than --accent so the red accent stays reserved for section heads, callouts, and underlines. A red bar at the top of the viewport was competing with the masthead." That commit rewrote 136 lines of DESIGN-SYSTEM.md but missed this bullet, which dates to c75ded9 earlier the same day. The CSS is correct; the doc line is stale. Live-confirmed today: bar computes rgb(5,5,5) = --ink.</t>
-        </is>
-      </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>PASS (resolved 2026-08-10) — was ISSUE/Low: DESIGN-SYSTEM.md:115 listed "Reading progress bar (`var(--accent)`)" as a permitted accent use, but css/article.css:876 ships `.reading-progress { background: var(--ink) }`. Commit 68b0c1d (2026-04-10) recolored it on purpose and left the reason in the CSS: red was competing with the masthead and diluting the accent's semantic weight. That commit rewrote 136 lines of DESIGN-SYSTEM.md but missed this one bullet, which dated to c75ded9 earlier the same day. The CSS was correct; the doc line was stale.</t>
+        </is>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>Low (resolved)</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER. Not auto-fixed for two reasons: (1) DESIGN-SYSTEM.md carries Dexter's uncommitted working-tree edit (the "Two-plane rule" addition), and the fix-phase rule is to leave his in-flight changes alone; (2) although the code comment makes the intent unambiguous, reconciling a brand doc against its implementation is a design-intent call, not a behaviour repair. Recommended resolution (Dexter's pick): strike line 115 from the permitted list, or re-add it annotated "— superseded 2026-04-10, see css/article.css:876".</t>
+          <t>FIX (2026-08-10, Dexter's explicit call): struck DESIGN-SYSTEM.md:115 from the permitted-accent list. Chosen over annotating it as superseded. No CSS touched — the implementation was already right. The doc's own §'Reading Progress Bar (Articles Only)' block (DESIGN-SYSTEM.md:934) already carried the correct spec (`background: var(--ink)`) plus the Phase 3b rationale, so striking the bullet makes the document self-consistent rather than removing information. Committed as a single-hunk stage so Dexter's in-flight "Two-plane rule" edit, which lives in the same file, stayed out of the QA commit and remains in his working tree.</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>PENDING — blocked on the decision above.</t>
+          <t>PASS — permitted-accent list re-read after the edit: 10 entries remain, every one of them verified against live CSS this run (section-head h2 + rule, callout left-border, .callout-emph, scripture cite, stat bar, identity plate tagline, article link hover underline, plate hover border, focus rings). Zero doc-vs-implementation mismatches remain in the section. grep confirms no other line in DESIGN-SYSTEM.md claims the progress bar uses --accent. Not a deploy-visible change — /DESIGN-SYSTEM.md returns 404 by design.</t>
         </is>
       </c>
     </row>
@@ -4894,7 +4868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4902,14 +4876,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -4921,106 +4895,86 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
-        <v>77</v>
+      <c r="B4" s="9" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ISSUE</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>1</v>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>— P4 (re-test) —</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>— P4 (re-test) —</t>
-        </is>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="B10" s="11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Resolved (P4 PASS)</t>
         </is>
       </c>
-      <c r="B16" s="10" t="n">
-        <v>1</v>
+      <c r="B14" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Still open</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>Still open</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Total features: 82</t>
         </is>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -2668,7 +2668,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Authored prev/next render correctly on all 16. Ghost/teaser path PENDING — requires a future-dated entry; none exists. 2026-08-10 PM: the derive-from-live-status fix (p3) live-verified — 4 essays still carry stale ghost:true frontmatter (next-verse.prev→job, not-the-same-as-alive.next→music-that-raised-me, pulpit.next→the-stone, should-have-killed-it.next→job) and all 4 render as real .article-nav-link anchors with rel=prev/next plus matching &lt;link rel&gt; head tags. No ghost teaser leaks.</t>
+          <t>Authored prev/next render correctly on all 16. Ghost/teaser path PENDING — requires a future-dated entry; none exists. 2026-08-10 PM: the derive-from-live-status fix (p3) live-verified, then the underlying data cleaned — the 4 stale ghost:true flags are gone (see F81). Zero `ghost: true` remain in the collection; all 16 essays render real .article-nav-link anchors, 15 rel=next head links (newest correctly has none), zero article-nav-ghost teasers.</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr"/>
@@ -4786,12 +4786,12 @@
       <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>FIX (2026-08-07, Dexter's call — resolution 1 of 3): added next{slug:'send-someone-else', title:'Send Someone Else', ghost:false} to show-me-your-glory.mdx. Editorial decision made by Dexter, not by the loop. NOTE this intentionally creates the corpus's first NON-RECIPROCAL pair: glory now points forward to send-someone-else, but send-someone-else.prev still points back to 'some' — the deliberate pulpit → some → send-someone-else calling thread. That asymmetry is by design; do not 'fix' it in a future run.</t>
+          <t>FIX (2026-08-10, Dexter's call): flipped the 4 stale `ghost: true` frontmatter flags to false — next-verse.prev→job, not-the-same-as-alive.next→music-that-raised-me, pulpit.next→the-stone, should-have-killed-it.next→job. All 4 targets had gone live, leaving the flags asserting a coming-soon state that was no longer true. Flipped rather than deleted, to match the `ghost: false` convention the other 13 prev/next blocks already carry. Frontmatter only — one line per file, zero prose touched.</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build, then live) — show-me-your-glory emits &lt;link rel=next&gt; to send-someone-else and renders a normal 'Next Essay → Send Someone Else' nav (no ghost class, since ArticleLayout derives ghost from the target's real live status). Forward chain now walks all 16 published essays end to end: reckonings → … → show-me-your-glory → send-someone-else. Zero non-newest essays lack a next.</t>
+          <t>PASS (verified against build, then live) — rendered nav is byte-identical before and after the flip, confirming the flags were already inert under ArticleLayout's derive-from-live-status logic: same .article-nav-prev/.article-nav-next anchors, same &lt;link rel=next&gt; targets on all 4 essays. Collection-wide: zero `ghost: true` remain, zero .article-nav-ghost teasers render across all 16, 15 rel=next head links. The data now says what the render already did.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -63,7 +63,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +88,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2E2DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B9B5"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -142,6 +147,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K85"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -734,7 +740,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks.</t>
+          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks. | 2026-08-13 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways; --bg/--ink/--accent-text all re-resolved (#060606/#f3f0e8/#ff4d4d dark, #f4f4f1/#050505/#c00 light).</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -783,7 +789,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production.</t>
+          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production. | 2026-08-13 re-verified live: tab-target verified on live: .skip-link reveals from left:-999px to a 83x69 box at (12,12), cream-on-ink 17.79:1; activating it moved document.activeElement to MAIN#archive (tabindex=-1). Article pages target #article.</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -987,7 +993,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path</t>
+          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path | 2026-08-13 re-verified live: /img/favicon-32.png and /img/apple-touch-icon.png both 200, immutable-cached.</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr"/>
@@ -1036,7 +1042,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact</t>
+          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-13 re-verified live: document.fonts.status 'loaded'; Anton 400, IBM Plex Sans 400 + 700 all report 'loaded' on home and article. No FOUT observed.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1138,7 +1144,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com</t>
+          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com | 2026-08-13 re-verified live: title/description/canonical present and pointing at imjustdex.com on all 16 articles + home/about/brand/phase0.</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr"/>
@@ -1187,7 +1193,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand)</t>
+          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand) | 2026-08-13 re-verified live: og:title/og:description/og:image/twitter:card present on all 16 articles; og:image matches the JSON-LD image URL exactly (same cache-bust) on every one.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1240,7 +1246,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor)</t>
+          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor) | 2026-08-13 re-verified live: homepage @graph carries WebSite + Person; Person has all of name/url/sameAs/jobTitle/worksFor.</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr"/>
@@ -1289,7 +1295,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description)</t>
+          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description) | 2026-08-13 re-verified live: /about/ ProfilePage mainEntity is @type Person with name/url/jobTitle/worksFor/sameAs/description — zero missing fields.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -1338,7 +1344,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift</t>
+          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift | 2026-08-13 re-verified live: all 16 BlogPosting blocks carry every required field (headline, description, datePublished, dateModified, author.@type=Person + name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount); zero og-default.png drift.</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1436,7 +1442,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>PASS — robots.txt Allow / + Sitemap → sitemap-index.xml</t>
+          <t>PASS — robots.txt Allow / + Sitemap → sitemap-index.xml | 2026-08-13 re-verified live: /robots.txt 200, Sitemap directive -&gt; https://imjustdex.com/sitemap-index.xml.</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
@@ -1485,7 +1491,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>PASS — sitemap-0.xml 20 locs = exactly the published set + about/brand/phase0; no missing, no orphans</t>
+          <t>PASS — sitemap-0.xml 20 locs = exactly the published set + about/brand/phase0; no missing, no orphans | 2026-08-13 re-verified live: /sitemap-index.xml -&gt; sitemap-0.xml; sitemap-0 lists 20 URLs covering all 16 articles + /, /about/, /brand/, /phase0/. Zero missing.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr"/>
@@ -1587,7 +1593,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>PASS — Entry No. 16 / Week of July 5, 2026, LatestBar → newest essay</t>
+          <t>PASS — Entry No. 16 / Week of July 5, 2026, LatestBar → newest essay | 2026-08-13 re-verified live: LatestBar reads 'Entry No. 16 / Week of July 5, 2026' and links to /words/send-someone-else/ (the newest). NOTE: its .latest-tag chip is the F77 finding this run.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -1689,7 +1695,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>PASS — Faith 13 / Identity 09 / Art 03, verified against frontmatter lanes; 16 articles</t>
+          <t>PASS — Faith 13 / Identity 09 / Art 03, verified against frontmatter lanes; 16 articles | 2026-08-13 re-verified live: lane-index counts Faith 13 / Identity 09 / Art 03 — non-negative, zero-padded, and consistent with 16 essays counted per lane (15 .plate-lane chips + 1 .lead-badge-lane).</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -2358,7 +2364,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>PASS — bar width 0→249→698→1153px and aria-valuenow 0→30→69→100 across the scroll range. 2026-08-10 PM re-check: structural half re-verified (progress.js math recomputed by hand at 50% scroll = 51.5%; .article-body + .reading-progress present; role/aria-label/aria-valuemin/max initialized on load). Runtime paint not re-exercisable this run — the browser pane reports document.visibilityState 'hidden', so requestAnimationFrame never fires and the CSS width transition stays frozen at 0. Harness limitation, not a site regression.</t>
+          <t>PASS — bar width 0→249→698→1153px and aria-valuenow 0→30→69→100 across the scroll range. 2026-08-10 PM re-check: structural half re-verified (progress.js math recomputed by hand at 50% scroll = 51.5%; .article-body + .reading-progress present; role/aria-label/aria-valuemin/max initialized on load). Runtime paint not re-exercisable this run — the browser pane reports document.visibilityState 'hidden', so requestAnimationFrame never fires and the CSS width transition stays frozen at 0. Harness limitation, not a site regression. | 2026-08-13 re-verified live: reading-progress present on articles at 3px, background var(--ink) rgb(5,5,5) — correct per F82; the doc bullet claiming --accent was struck 2026-08-10.</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -3137,7 +3143,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid</t>
+          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid | 2026-08-13 re-verified live: /feed.xml 200, Atom namespace, 16 &lt;entry&gt; elements — exactly matching the 16 articles on the homepage, zero set difference either direction.</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -3190,7 +3196,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>PASS — feed.xsl 200 and &lt;?xml-stylesheet?&gt; PI present</t>
+          <t>PASS — feed.xsl 200 and &lt;?xml-stylesheet?&gt; PI present | 2026-08-13 re-verified live: /feed.xsl 200 and referenced via &lt;?xml-stylesheet?&gt; in the feed prolog.</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -3667,7 +3673,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s</t>
+          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s | 2026-08-13 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.16s using healthscrub+20260813@imjustdex.com.</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3879,7 +3885,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical</t>
+          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical | 2026-08-13 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200; /sitemap.xml correctly 404 post-cutover.</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -4038,7 +4044,7 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>PASS — /api/subscribe rewrite reaches the function (405 on GET, 400/200 on POST)</t>
+          <t>PASS — /api/subscribe rewrite reaches the function (405 on GET, 400/200 on POST) | 2026-08-13 re-verified live: /api/subscribe rewrite reached the Netlify function and returned a Mailchimp success body.</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr"/>
@@ -4091,7 +4097,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>PASS — unmatched route → 404 with the branded body</t>
+          <t>PASS — unmatched route → 404 with the branded body | 2026-08-13 re-verified live: /404 returns 200 with the bespoke 'Nothing to Document Here' body and noindex; /DESIGN-SYSTEM.md and /audit/features.json both 404 (docs not leaking).</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr"/>
@@ -4144,7 +4150,7 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML</t>
+          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML | 2026-08-13 re-verified live: CSP header present and ENFORCING — a runtime &lt;style&gt; injection was blocked by style-src 'self' during F77 verification, which is direct proof the policy is live, not just declared. Per-route /brand/ and /feed.xml relaxations by design.</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -4197,7 +4203,7 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes</t>
+          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes | 2026-08-13 re-verified live: all 5 security headers present on all 6 page types (home, article, about, brand, phase0, 404, feed): X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present.</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
@@ -4250,7 +4256,7 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate.</t>
+          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate. | 2026-08-13 re-verified live: versioned assets (/css, /js, /img) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift.</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr"/>
@@ -4462,7 +4468,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page)</t>
+          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page) | 2026-08-13 re-verified live: verified in the DEPLOYED sheet, not just source: tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, *::before, *::after with !important, plus scroll-behavior auto. Catches all 29 transitioned elements on the homepage.</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr"/>
@@ -4515,7 +4521,7 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4.</t>
+          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4. | 2026-08-13 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to a footer link that matched ':focus-visible' and computed outline 'solid 2px rgb(204, 0, 0)' at offset 2px.</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -4572,18 +4578,22 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>PASS — 15 sampled selectors all meet WCAG AA (min 5.17:1 large, 5.94:1 small) in dark mode</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr"/>
+          <t>ISSUE/High (2026-08-13) — .latest-tag (the red 'Latest' chip in the homepage standfirst bar) pairs `background: var(--accent)` with `color: var(--bg)`. In light mode that is cream on #c00 = 5.17:1 and passes. In dark mode --bg flips to #060606 and the same chip computes 3.44:1 at 11.52px/700 — under the 4.5:1 AA floor for small text (WCAG 1.4.3). Measured three times on settled live loads. The #c00/#060606 pair is sanctioned by the Phase 4.1 accent doctrine (DESIGN-SYSTEM.md:102) only for NON-text contrast at the 3:1 floor; this is a text use of it. Missed by prior runs because F77 sampled palette-level token pairs (body/muted/faint/accent text), not the one control that puts small text ON the accent fill — the same sheet-level vs per-control gap that hid F76. All other sampled combinations still pass: 33 distinct fg/bg/size combos in dark, 33 in light, this was the only failure.</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>NOTE: computed AA: light body 12:1/muted 4.63:1/red 5.34:1; dark body 11.85:1/muted 5.13:1/red 6.2:1; large red 3.44:1&gt;=3</t>
-        </is>
-      </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>FIX (qa/fixes-20260813, commit 549e09c): added `html.dark-mode .issue-latest .latest-tag, html.dark-mode .issue-head .latest-tag { color: var(--ink) }` to css/home-v2.css directly under the base rule. var(--ink) is #f3f0e8 in dark, so the chip renders identically in both modes at 5.17:1. The selector is (0,3,1) and beats the .issue-head hook in home-augment.css (0,2,0) on specificity rather than source order, so only home-v2.css needed the rule and only its cache-bust had to move (?v=phase31 -&gt; phase33 in src/layouts/HomeLayout.astro; the asset is served immutable/1y). brand/index.html needed no edit — it loads home-augment.css but renders no LatestBar.</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>PASS (build-verified + runtime-verified 2026-08-13, NOT yet live) — `npm run build` clean, 19 pages; dist/index.html references home-v2.css?v=phase33 and dist/css/home-v2.css carries the rule. Cascade verified at runtime on the live DOM: inserting the shipped rule into the real home-v2 sheet via CSSOM insertRule (CSP-safe; a plain &lt;style&gt; injection was blocked by style-src 'self', incidentally reconfirming F69) moved the chip from rgb(6,6,6) to rgb(243,240,232) on rgb(204,0,0) — 3.44:1 -&gt; 5.17:1, passes AA. Goes fully live-verified on the next SCRUB after Dexter merges. Note for merge review: this is a VISIBLE dark-mode change — the chip's word 'Latest' goes from near-black to cream. Light mode is untouched.</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4635,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt</t>
+          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt | 2026-08-13 re-verified live: home and article both single-h1, zero skipped heading levels (home H1 then 17x H2; article H1,H2,H2,H2,H2,H2), header/main/footer/nav all present. Zero images missing alt.</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr"/>
@@ -4731,7 +4741,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>PASS — parity 16/16 verified live; every /words/&lt;slug&gt; returns a single 301 to its trailing-slash canonical; no orphan rules</t>
+          <t>PASS — parity 16/16 verified live; every /words/&lt;slug&gt; returns a single 301 to its trailing-slash canonical; no orphan rules | 2026-08-13 re-verified live: all 16 /words/&lt;slug&gt; (no trailing slash) return 301; all 16 /words/&lt;slug&gt;/ return 200 in 0.31-0.45s.</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr"/>
@@ -4852,8 +4862,122 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>F83</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Dark-mode text on --accent fills (hover treatments)</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>As a dark-mode reader hovering the homepage standfirst bar or the identity-hero primary button, I want the text that inverts onto the red fill to stay readable, so the hover state does not become less legible than the resting state.</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Every rule that pairs `background: var(--accent)` with small text meets WCAG 1.4.3 in BOTH modes — &gt;=4.5:1 under 18.66px/bold, &gt;=3:1 at or above it.</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>css/home-v2.css:129-135,917-918; css/home-augment.css:146,298</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-13</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/High (2026-08-13) — four hover rules invert small text onto the --accent fill using `color: var(--bg)`, which is #060606 in dark mode = 3.44:1. All four are under their floor: .issue-latest:hover .latest-title (19.2px/400 — NOT large, since AA large needs &gt;=24px or &gt;=18.66px AND bold) 3.44:1; .issue-latest:hover .latest-cta (14.08px/700) 3.44:1; .identity-hero .hero-link.primary:hover (14.08px/700) 3.44:1; and worst, .issue-latest:hover .latest-meta (11.52px/400, hover drops opacity to .6) = 2.54:1. Same root cause as F77 but NOT fixed with it — see p3.</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — NEEDS DEXTER (fix-phase guardrail: design intent). Unlike F77's resting-state chip, this is a deliberate hover treatment in which the whole standfirst bar inverts to red as one gesture. A colour swap to var(--ink) clears three of the four (5.17:1), but .latest-meta also needs its hover opacity raised off .6 — ink at 60% over #c00 is still only 2.42:1 — and that opacity is a hierarchy decision about how much the meta line should recede, not a defect. Proposed patch held for Dexter's call: `html.dark-mode .issue-latest:hover .latest-title, ...latest-cta, html.dark-mode .identity-hero .hero-link.primary:hover { color: var(--ink) }` plus a decision on the meta's hover opacity.</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr">
+        <is>
+          <t>PENDING — blocked on the design call above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>F84</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Design-system doc &lt;-&gt; implementation parity (accent PROHIBITED-use list)</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>As the owner of the design system, I want the Prohibited accent-use list in DESIGN-SYSTEM.md to match what the CSS actually ships, so the document stays trustworthy as the brand's source of truth.</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>No live rule uses var(--accent) in a way DESIGN-SYSTEM.md:124-130 forbids, or the forbidden entry is annotated with its sanctioned exception.</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>DESIGN-SYSTEM.md:124-130; css/home-v2.css:79-90; css/home-augment.css:93-103</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-13</t>
+        </is>
+      </c>
+      <c r="H87" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/Low (2026-08-13) — DESIGN-SYSTEM.md:124-130 lists 'Backgrounds' and 'Tags or metadata' as PROHIBITED accent uses, but .latest-tag is exactly that: a metadata tag with `background: var(--accent)`, shipped and prominent in the homepage standfirst bar. Companion to F82, which audited only the Permitted half of the same section and so could not have caught this.</t>
+        </is>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — NEEDS DEXTER (fix-phase guardrail: design intent). Two coherent resolutions and the choice is his, exactly as it was for F82: (a) annotate the Prohibited list with the sanctioned exception — the red chip is a deliberate editorial signature and the doc is what is stale; or (b) treat the chip as drift and restyle it. Recommend (a) — the chip reads as authored, and F82's precedent was to correct the doc when the implementation was the considered decision. No CSS touched pending his call. Not deploy-visible either way: /DESIGN-SYSTEM.md returns 404 by design.</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>PENDING — blocked on the design call above.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K85"/>
+  <autoFilter ref="A3:K87"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4896,7 +5020,7 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">
@@ -4943,7 +5067,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -4960,7 +5084,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -4969,14 +5093,14 @@
           <t>Still open</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
+      <c r="B15" s="14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Total features: 82</t>
+          <t>Total features: 84</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -4583,7 +4583,7 @@
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH (closed live)</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified + runtime-verified 2026-08-13, NOT yet live) — `npm run build` clean, 19 pages; dist/index.html references home-v2.css?v=phase33 and dist/css/home-v2.css carries the rule. Cascade verified at runtime on the live DOM: inserting the shipped rule into the real home-v2 sheet via CSSOM insertRule (CSP-safe; a plain &lt;style&gt; injection was blocked by style-src 'self', incidentally reconfirming F69) moved the chip from rgb(6,6,6) to rgb(243,240,232) on rgb(204,0,0) — 3.44:1 -&gt; 5.17:1, passes AA. Goes fully live-verified on the next SCRUB after Dexter merges. Note for merge review: this is a VISIBLE dark-mode change — the chip's word 'Latest' goes from near-black to cream. Light mode is untouched.</t>
+          <t>PASS (live-verified 2026-08-13, deploy 791bfc5) — merged to main and shipped at Dexter's explicit instruction. Live https://imjustdex.com/ references home-v2.css?v=phase33; the live sheet serves the rule; on the production homepage in dark mode .latest-tag computes rgb(243,240,232) on rgb(204,0,0) at 11.52px/700 = 5.17:1, clearing the 4.5:1 AA floor. Light mode confirmed untouched: rgb(244,244,241) on rgb(204,0,0) = 5.34:1, byte-identical to pre-fix. Post-deploy regression clean — 0 console errors, 16 plates, 3 lane cells, cascade intact. Verification ladder: build-verified 05:50 -&gt; runtime-verified by CSSOM cascade injection 06:05 -&gt; live-verified on production 22:40 CDT.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -4900,22 +4900,22 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-13) — four hover rules invert small text onto the --accent fill using `color: var(--bg)`, which is #060606 in dark mode = 3.44:1. All four are under their floor: .issue-latest:hover .latest-title (19.2px/400 — NOT large, since AA large needs &gt;=24px or &gt;=18.66px AND bold) 3.44:1; .issue-latest:hover .latest-cta (14.08px/700) 3.44:1; .identity-hero .hero-link.primary:hover (14.08px/700) 3.44:1; and worst, .issue-latest:hover .latest-meta (11.52px/400, hover drops opacity to .6) = 2.54:1. Same root cause as F77 but NOT fixed with it — see p3.</t>
+          <t>ISSUE/High (2026-08-13) — CORRECTED SCOPE, and the correction matters. The morning scrub read the declarations and reported FOUR failing hover rules. Re-measured under REAL pointer hover before fixing, only TWO are real: `.issue-latest:hover .latest-cta` (14.08px/700) and `.identity-hero .hero-link.primary:hover` (14.08px/700), both `color: var(--bg)` on a `background: var(--accent)` fill = 3.44:1 in dark against a 4.5:1 floor. The other two were FALSE POSITIVES: `.issue-latest:hover` takes the BAR to var(--ink), not var(--accent), so .latest-title measures 17.79:1 and .latest-meta 5.23:1 (at opacity .6) against cream — both already clear. The morning read assumed the accent fill was the surface for every child of the hover state; it is only the surface for .latest-cta, which sets its own background. Lesson: resolve the PAINTED surface under real hover, never infer it from the parent's declarations.</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH (closed live)</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER (fix-phase guardrail: design intent). Unlike F77's resting-state chip, this is a deliberate hover treatment in which the whole standfirst bar inverts to red as one gesture. A colour swap to var(--ink) clears three of the four (5.17:1), but .latest-meta also needs its hover opacity raised off .6 — ink at 60% over #c00 is still only 2.42:1 — and that opacity is a hierarchy decision about how much the meta line should recede, not a defect. Proposed patch held for Dexter's call: `html.dark-mode .issue-latest:hover .latest-title, ...latest-cta, html.dark-mode .identity-hero .hero-link.primary:hover { color: var(--ink) }` plus a decision on the meta's hover opacity.</t>
+          <t>FIX (2026-08-13, Dexter's explicit call to ship): added `html.dark-mode .issue-latest:hover .latest-cta, html.dark-mode .identity-hero .hero-link.primary:hover { color: var(--ink) }` to css/home-v2.css beneath the hover block, mirroring the F77 override. Selectors are (0,4,1) and (0,5,1), beating the duplicate hooks in home-augment.css:146 and :298 on specificity rather than source order, so home-v2.css was the only sheet to touch. Cache-bust ?v=phase33 -&gt; phase34 in src/layouts/HomeLayout.astro. NO opacity change was needed — the .latest-meta hover-opacity decision this row was originally BLOCKED on turned out to rest on a false positive and evaporated with it.</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>PENDING — blocked on the design call above.</t>
+          <t>PENDING — awaiting live verification on the deploy.</t>
         </is>
       </c>
     </row>
@@ -4962,17 +4962,17 @@
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>LOW (closed live)</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER (fix-phase guardrail: design intent). Two coherent resolutions and the choice is his, exactly as it was for F82: (a) annotate the Prohibited list with the sanctioned exception — the red chip is a deliberate editorial signature and the doc is what is stale; or (b) treat the chip as drift and restyle it. Recommend (a) — the chip reads as authored, and F82's precedent was to correct the doc when the implementation was the considered decision. No CSS touched pending his call. Not deploy-visible either way: /DESIGN-SYSTEM.md returns 404 by design.</t>
+          <t>FIX (2026-08-13, Dexter's explicit call to ship resolution (a)): annotated the Prohibited accent list in DESIGN-SYSTEM.md with the sanctioned exception rather than restyling the chip — the F82 precedent, applied to the other half of the same section. The annotation does three things: names .latest-tag as the ONE sanctioned violation of the 'Backgrounds' and 'Tags or metadata' bullets and states that further red-filled tags remain prohibited (an exception, not an opening); records the mode-specific rule the chip needs and why; and draws the boundary the whole finding-class came from — Phase 4.1 sanctions the #c00/#060606 pair at the 3:1 NON-TEXT floor, and that sanction does not extend to text set ON the accent fill, which SC 1.4.3 governs at 4.5:1. Any future `background: var(--accent)` + text rule must now be measured in both modes before shipping. No CSS touched. Staged as an isolated single hunk against HEAD via `git apply --cached` so Dexter's in-flight 'Two-plane rule' edit, which lives in the same file, stayed out of the commit and remains in his working tree — same handling as F82.</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>PENDING — blocked on the design call above.</t>
+          <t>PENDING — doc-only change; not deploy-visible (/DESIGN-SYSTEM.md returns 404 by design).</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -63,7 +63,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -88,11 +88,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2E2DE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4B9B5"/>
       </patternFill>
     </fill>
   </fills>
@@ -122,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -147,7 +142,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4915,7 +4909,7 @@
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>PENDING — awaiting live verification on the deploy.</t>
+          <t>PASS (live-verified 2026-08-13, deploy 5c7e5fb) — verified under REAL pointer hover on the production deploy, in dark mode, with home-v2.css?v=phase34 served. Standfirst bar hovered: .latest-cta now rgb(243,240,232) on rgb(204,0,0) = 5.17:1 (was 3.44:1) PASS; .latest-tag 5.17:1 PASS; .latest-title 17.79:1 PASS; .latest-meta 5.23:1 PASS — all four elements of the hover gesture clear their floor. Identity-hero primary hovered: 'Read the About -&gt;' now rgb(243,240,232) on rgb(204,0,0) = 5.17:1 (was 3.44:1) PASS. Zero console errors post-deploy. No remaining rule on the site pairs small text with the --accent fill below AA in either mode.</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4966,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>PENDING — doc-only change; not deploy-visible (/DESIGN-SYSTEM.md returns 404 by design).</t>
+          <t>PASS (2026-08-13, commit 5c7e5fb) — Prohibited-accent list re-read after the edit: the annotation names .latest-tag as the single sanctioned exception, holds the line against further red-filled tags, and states the text-vs-non-text boundary (SC 1.4.3 at 4.5:1 vs Phase 4.1's 3:1 non-text sanction). With F82 (Permitted half) and F84 (Prohibited half) both closed, the full accent section of DESIGN-SYSTEM.md now matches shipped CSS with zero mismatches. Confirmed not deploy-visible: /DESIGN-SYSTEM.md still returns 404. Dexter's 'Two-plane rule' edit verified still present and uncommitted in the working tree after the single-hunk stage.</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5051,7 @@
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -5067,7 +5061,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5084,7 +5078,7 @@
         </is>
       </c>
       <c r="B14" s="9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -5093,8 +5087,8 @@
           <t>Still open</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
-        <v>2</v>
+      <c r="B15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,6 +48,16 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A1A1A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00CC0000"/>
       <sz val="13"/>
     </font>
@@ -63,7 +73,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -87,7 +97,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E0625B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0C24B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9C7E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E2E2DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B9B5"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +147,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -135,13 +165,26 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -632,7 +675,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>PASS — masthead .brand-block → '/' present on home/about/404/phase0/brand/article; aria-label 'Dexter Jakes home'</t>
+          <t>PASS — masthead .brand-block → '/' present on home/about/404/phase0/brand/article; aria-label 'Dexter Jakes home' | 2026-08-15 re-verified live: brand-block present and linking / on all 20 pages</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr"/>
@@ -681,7 +724,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>PASS — brand-word: Words (home/article/about/brand), 404, Phase 0 — matches documented intent</t>
+          <t>PASS — brand-word: Words (home/article/about/brand), 404, Phase 0 — matches documented intent | 2026-08-15 re-verified live: brand-word: home/about/article 'Words', 404 '404', phase0 'Phase 0' — matches the documented about-page quirk</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -836,7 +879,7 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>PASS — 2 decorative rulers render</t>
+          <t>PASS — 2 decorative rulers render | 2026-08-15 re-verified live: zero .ruler-* without aria-hidden across all pages</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr"/>
@@ -885,7 +928,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>PASS — footer strip + links present on all page types</t>
+          <t>PASS — footer strip + links present on all page types | 2026-08-15 re-verified live: footer: Instagram + X both target=_blank rel="noopener noreferrer", /feed.xml, /about/, "Built by Dex"; zero _blank links missing rel site-wide</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr"/>
@@ -919,7 +962,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>&lt;link rel=alternate type=application/atom+xml href=/feed.xml&gt; present in &lt;head&gt; on home, about, phase0. (Articles/coming-soon/404 do NOT include it — verify intent.)</t>
+          <t>&lt;link rel=alternate type=application/atom+xml href=/feed.xml&gt; present in &lt;head&gt; on home, about, phase0 AND articles (ArticleLayout.astro:123 — added at commit a4f4f25). 404 does NOT include it (noindex page).</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -934,7 +977,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>PASS — &lt;link rel=alternate atom&gt; present on home, about, phase0, article</t>
+          <t>PASS (2026-08-15 scrub) — home/about/phase0/articles all carry the feed discovery link; /404 correctly omits it. NOTE: the prior `expected` said articles do NOT include it. That text was stale — ArticleLayout has emitted the link since a4f4f25; the site was never wrong, the row was. Expectation corrected, not the code.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr"/>
@@ -987,7 +1030,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path | 2026-08-13 re-verified live: /img/favicon-32.png and /img/apple-touch-icon.png both 200, immutable-cached.</t>
+          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path | 2026-08-15 re-verified live: favicon-32.png + apple-touch-icon.png linked on every page; both 200 (1327b / 5729b)</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr"/>
@@ -1036,7 +1079,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-13 re-verified live: document.fonts.status 'loaded'; Anton 400, IBM Plex Sans 400 + 700 all report 'loaded' on home and article. No FOUT observed.</t>
+          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-15 re-verified live: Anton + IBM Plex Sans preloaded with crossorigin; zero Google Fonts refs; document.fonts reports all 3 faces loaded</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1085,7 +1128,7 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>PASS — no horizontal overflow at 390px on home/article/about/phase0/brand/404</t>
+          <t>PASS — no horizontal overflow at 390px on home/article/about/phase0/brand/404 | 2026-08-15 re-verified live: viewport width=device-width + viewport-fit=cover on all pages</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr"/>
@@ -1138,7 +1181,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com | 2026-08-13 re-verified live: title/description/canonical present and pointing at imjustdex.com on all 16 articles + home/about/brand/phase0.</t>
+          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com | 2026-08-15 re-verified live: zero duplicate &lt;title&gt; across 20 pages; /404 canonical is /404 as specified</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr"/>
@@ -1187,7 +1230,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand) | 2026-08-13 re-verified live: og:title/og:description/og:image/twitter:card present on all 16 articles; og:image matches the JSON-LD image URL exactly (same cache-bust) on every one.</t>
+          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand) | 2026-08-15 re-verified live: twitter:card summary_large_image on every page in scope (404 correctly excluded)</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1240,7 +1283,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor) | 2026-08-13 re-verified live: homepage @graph carries WebSite + Person; Person has all of name/url/sameAs/jobTitle/worksFor.</t>
+          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor) | 2026-08-15 re-verified live: home @graph carries WebSite + Person; Person has name/url/sameAs/jobTitle/worksFor — no missing fields</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr"/>
@@ -1289,7 +1332,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description) | 2026-08-13 re-verified live: /about/ ProfilePage mainEntity is @type Person with name/url/jobTitle/worksFor/sameAs/description — zero missing fields.</t>
+          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description) | 2026-08-15 re-verified live: about ProfilePage mainEntity Person complete — name/url/jobTitle/worksFor/sameAs/description all present</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -4572,12 +4615,12 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-13) — .latest-tag (the red 'Latest' chip in the homepage standfirst bar) pairs `background: var(--accent)` with `color: var(--bg)`. In light mode that is cream on #c00 = 5.17:1 and passes. In dark mode --bg flips to #060606 and the same chip computes 3.44:1 at 11.52px/700 — under the 4.5:1 AA floor for small text (WCAG 1.4.3). Measured three times on settled live loads. The #c00/#060606 pair is sanctioned by the Phase 4.1 accent doctrine (DESIGN-SYSTEM.md:102) only for NON-text contrast at the 3:1 floor; this is a text use of it. Missed by prior runs because F77 sampled palette-level token pairs (body/muted/faint/accent text), not the one control that puts small text ON the accent fill — the same sheet-level vs per-control gap that hid F76. All other sampled combinations still pass: 33 distinct fg/bg/size combos in dark, 33 in light, this was the only failure.</t>
+          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — .latest-tag (the red 'Latest' chip in the homepage standfirst bar) pairs `background: var(--accent)` with `color: var(--bg)`. In light mode that is cream on #c00 = 5.17:1 and passes. In dark mode --bg flips to #060606 and the same chip computes 3.44:1 at 11.52px/700 — under the 4.5:1 AA floor for small text (WCAG 1.4.3). Measured three times on settled live loads. The #c00/#060606 pair is sanctioned by the Phase 4.1 accent doctrine (DESIGN-SYSTEM.md:102) only for NON-text contrast at the 3:1 floor; this is a text use of it. Missed by prior runs because F77 sampled palette-level token pairs (body/muted/faint/accent text), not the one control that puts small text ON the accent fill — the same sheet-level vs per-control gap that hid F76. All other sampled combinations still pass: 33 distinct fg/bg/size combos in dark, 33 in light, this was the only failure.</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>HIGH (closed live)</t>
+          <t>HIGH (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
@@ -4894,12 +4937,12 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-13) — CORRECTED SCOPE, and the correction matters. The morning scrub read the declarations and reported FOUR failing hover rules. Re-measured under REAL pointer hover before fixing, only TWO are real: `.issue-latest:hover .latest-cta` (14.08px/700) and `.identity-hero .hero-link.primary:hover` (14.08px/700), both `color: var(--bg)` on a `background: var(--accent)` fill = 3.44:1 in dark against a 4.5:1 floor. The other two were FALSE POSITIVES: `.issue-latest:hover` takes the BAR to var(--ink), not var(--accent), so .latest-title measures 17.79:1 and .latest-meta 5.23:1 (at opacity .6) against cream — both already clear. The morning read assumed the accent fill was the surface for every child of the hover state; it is only the surface for .latest-cta, which sets its own background. Lesson: resolve the PAINTED surface under real hover, never infer it from the parent's declarations.</t>
+          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — CORRECTED SCOPE, and the correction matters. The morning scrub read the declarations and reported FOUR failing hover rules. Re-measured under REAL pointer hover before fixing, only TWO are real: `.issue-latest:hover .latest-cta` (14.08px/700) and `.identity-hero .hero-link.primary:hover` (14.08px/700), both `color: var(--bg)` on a `background: var(--accent)` fill = 3.44:1 in dark against a 4.5:1 floor. The other two were FALSE POSITIVES: `.issue-latest:hover` takes the BAR to var(--ink), not var(--accent), so .latest-title measures 17.79:1 and .latest-meta 5.23:1 (at opacity .6) against cream — both already clear. The morning read assumed the accent fill was the surface for every child of the hover state; it is only the surface for .latest-cta, which sets its own background. Lesson: resolve the PAINTED surface under real hover, never infer it from the parent's declarations.</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>HIGH (closed live)</t>
+          <t>HIGH (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J86" s="4" t="inlineStr">
@@ -4951,12 +4994,12 @@
       </c>
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Low (2026-08-13) — DESIGN-SYSTEM.md:124-130 lists 'Backgrounds' and 'Tags or metadata' as PROHIBITED accent uses, but .latest-tag is exactly that: a metadata tag with `background: var(--accent)`, shipped and prominent in the homepage standfirst bar. Companion to F82, which audited only the Permitted half of the same section and so could not have caught this.</t>
+          <t>PASS (closed live 2026-08-13) — was ISSUE/Low (2026-08-13) — DESIGN-SYSTEM.md:124-130 lists 'Backgrounds' and 'Tags or metadata' as PROHIBITED accent uses, but .latest-tag is exactly that: a metadata tag with `background: var(--accent)`, shipped and prominent in the homepage standfirst bar. Companion to F82, which audited only the Permitted half of the same section and so could not have caught this.</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>LOW (closed live)</t>
+          <t>LOW (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
@@ -4970,8 +5013,350 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>F85</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Standfirst metadata contrast (--body-muted + opacity multiplier)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>As a reader on either mode, I can read the lane/date/read-time metadata in the homepage standfirst bar.</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Text using var(--body-muted) meets WCAG 1.4.3 (&gt;=4.5:1 at this 11.52px/400 size) in BOTH modes. The token is alpha-tuned to clear the floor on its own; no rule may stack a second opacity multiplier on top of it.</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>css/home-v2.css:112-122; css/home-augment.css:119-129; src/components/home/LatestBar.astro:27</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H88" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured.</t>
+        </is>
+      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260815): deleted `opacity: .75` from both `.issue-latest .latest-meta` (css/home-v2.css) and `.issue-head .latest-meta` (css/home-augment.css), leaving var(--body-muted) to carry the muting alone. Both sheets edited because both paint this control (home-v2 wins on the homepage by source order; home-augment is the sheet /brand/ loads). Comment left in both explaining that the token IS the muted level. The hover rules were deliberately left untouched — they set their own opacity and already measured 5.23:1. Cache-bust bumped home-augment phase32-&gt;phase33, home-v2 phase34-&gt;phase35 (both sheets ship immutable/1yr).</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>PASS (build-verified 2026-08-15) — `npm run build` clean, 19 pages. dist/css/*.css confirmed to carry the rules with zero opacity declarations. Post-fix values measured on the live DOM with the exact shipped declarations applied: dark 3.36:1 -&gt; 5.13:1, light 2.93:1 -&gt; 4.67:1. Both clear the 4.5:1 floor. Goes live-verified on the next scrub after Dexter merges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>F86</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Identity-hero corner label contrast (dark mode)</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>As a reader in dark mode, I can read the 'The Writer → 01' corner label on the identity hero.</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>`.identity-hero .hero-corner` meets WCAG 1.4.3 (&gt;=4.5:1 at 11.52px/700) in both modes, on whichever ground the hero plate presents.</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>css/home-augment.css:185-200; css/home-v2.css:864-878; src/components/home/IdentityHero.astro:7</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot.</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260815): raised `opacity: .5` -&gt; `.6` on `.identity-hero .hero-corner` in both css/home-augment.css and css/home-v2.css. The value is not arbitrary: the computed minimum to clear 4.5:1 on this pair is .56, solved by stepping opacity in 0.005 increments against the real painted ground; .6 takes it clear with margin while keeping the label recessive. Removing the multiplier entirely was rejected — that would be 17.79:1, a visual change to the hero's balance rather than a contrast repair.</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>PASS (build-verified 2026-08-15) — post-fix values measured on the live DOM with opacity .6 applied: dark 3.71:1 -&gt; 5.23:1, light 4.91:1 -&gt; 6.74:1. Both clear. dist confirmed to carry `opacity: .6` in both sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>F87</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>/brand/ dogfood contract — shared-component fixes must land in the shared sheet</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>As the design system's own documentation, /brand/ renders production classes and therefore shows exactly what the live site shows — including fixes.</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Any fix to a component that /brand/ demos must live in a stylesheet /brand/ actually loads (tokens, shell, plates, home-augment, article — NOT home-v2.css, which is homepage-only).</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>brand/index.html:39,115; css/home-augment.css; css/home-v2.css</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads.</t>
+        </is>
+      </c>
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260815): moved both override blocks — `html.dark-mode .issue-latest .latest-tag, html.dark-mode .issue-head .latest-tag` [F77] and `html.dark-mode .issue-latest:hover .latest-cta, html.dark-mode .identity-hero .hero-link.primary:hover` [F83] — out of css/home-v2.css and into css/home-augment.css, the sheet both surfaces load. Breadcrumb comments left at both former sites in home-v2.css so the next reader finds them. The relocation is cascade-safe and was verified as such rather than assumed: the overrides are (0,3,1), (0,4,1) and (0,5,1) against base rules of (0,2,0), (0,3,0) and (0,4,0), so they win on specificity and source order cannot take them back — which is why moving them EARLIER in the cascade is safe.</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>PASS (build-verified 2026-08-15) — grepped the built sheets: dist/css/home-augment.css carries both blocks at lines 127-134, dist/css/home-v2.css carries neither (only the breadcrumbs). Measured on the live /brand/ page in dark mode with the override applied: `.latest-tag` 3.44:1 -&gt; 5.17:1, the identical figure the homepage has been serving since deploy 791bfc5. Dogfood parity restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>F88</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Issue-next strip metadata contrast (latent)</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>As a reader, when an upcoming essay is scheduled I can read the Issue-next strip's lane/date/read-time metadata.</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>`.issue-next .next-meta` meets WCAG 1.4.3 (&gt;=4.5:1 at 11.52px/400) in both modes whenever the Issue-next strip renders.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>css/home-v2.css:220-230; css/home-augment.css:691-701; src/components/home/IssueNext.astro:20</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay.</t>
+        </is>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260815): deleted `opacity: .65` from `.issue-next .next-meta` in both css/home-v2.css and css/home-augment.css, same treatment and same reasoning as F85.</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>PASS (build-verified 2026-08-15) — measured on the live /brand/ demo of the strip in dark mode with the fix applied: 2.81:1 -&gt; 5.13:1. Clears. (An earlier reading of 1.02:1 during this run was an artifact of forcing the dark-mode class onto an already-rendered light page, which left tokens half-resolved; discarded and re-measured after a clean reload with the dxmode cookie set. Recording it here so the number is not mistaken for a real regression if it resurfaces.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>F89</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>404 eyebrow divider contrast</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>As a reader landing on a bad URL, I can read the eyebrow strip 'ERROR · 404 · PAGE NOT FOUND' in full.</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>`.notfound-eyebrow span.divider` meets WCAG 1.4.3, or is marked aria-hidden and treated as decoration.</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>css/notfound.css:64-66; src/pages/404.astro</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept.</t>
+        </is>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260815): raised `opacity: .5` -&gt; `.7` in css/notfound.css. Value taken from the file's own convention — the adjacent `.notfound-eyebrow .eyebrow-right` rule already uses .7 — rather than inventing a number. Cache-bust bumped notfound.css phase10 -&gt; phase11 in src/pages/404.astro.</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>PASS (build-verified 2026-08-15) — measured on the live /404 with opacity .7 applied: 3.61:1 -&gt; 7.19:1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>F90</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>/brand/ bespoke + demo-specimen contrast (documentation surface)</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>As a reader of the design system doc, I can read its bespoke chrome and its component specimens.</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Text on /brand/ meets WCAG 1.4.3, or the recessive treatment is a deliberate demonstration and is recorded as such.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>brand/brand.css; brand/index.html (demo-ghost-*, Download Pack h3)</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent.</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — NEEDS DEXTER. Two questions: (a) should the ghost specimens keep their dim demonstration value, or does the doc need a readable annotation beside them explaining the treatment? (b) the "Download Pack" h3 in brand.css is not a specimen and can be lifted on his word.</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K87"/>
+  <autoFilter ref="A3:K93"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -4986,7 +5371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4994,14 +5379,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -5013,8 +5398,8 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>77</v>
+      <c r="B4" s="12" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -5023,7 +5408,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5033,12 +5418,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
@@ -5050,8 +5435,8 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
-        <v>81</v>
+      <c r="B9" s="12" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -5060,41 +5445,71 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>— Issues by severity (found) —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>— Issues by severity (found) —</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Resolved (P4 PASS)</t>
         </is>
       </c>
-      <c r="B14" s="9" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B17" s="12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Total features: 84</t>
+      <c r="B18" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>Total features: 90</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks. | 2026-08-13 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways; --bg/--ink/--accent-text all re-resolved (#060606/#f3f0e8/#ff4d4d dark, #f4f4f1/#050505/#c00 light).</t>
+          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks. | 2026-08-13 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways; --bg/--ink/--accent-text all re-resolved (#060606/#f3f0e8/#ff4d4d dark, #f4f4f1/#050505/#c00 light). | 2026-08-16 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways (dxmode=light then dxmode=dark); --bg #060606&lt;-&gt;#f4f4f1 and --ink #f3f0e8&lt;-&gt;#050505 both re-resolved; label and aria-pressed tracked ('Mode: Dark'/true &lt;-&gt; 'Mode: Light'/false).</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production. | 2026-08-13 re-verified live: tab-target verified on live: .skip-link reveals from left:-999px to a 83x69 box at (12,12), cream-on-ink 17.79:1; activating it moved document.activeElement to MAIN#archive (tabindex=-1). Article pages target #article.</t>
+          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production. | 2026-08-13 re-verified live: tab-target verified on live: .skip-link reveals from left:-999px to a 83x69 box at (12,12), cream-on-ink 17.79:1; activating it moved document.activeElement to MAIN#archive (tabindex=-1). Article pages target #article. | 2026-08-16 re-verified live: structural half re-verified live: .skip-link is the first focusable element in document order on every page type, and its target (MAIN#article / MAIN#archive / MAIN#phase0 / MAIN#main) carries tabindex=-1. End-to-end activation NOT re-exercisable this run — the browser pane reports document.visibilityState 'hidden' and drops page focus on every reload, so a fresh-load Tab lands on BODY. Harness limitation, not a site regression; last live activation was 2026-08-13. NOTE: this row's sweep is what surfaced F91 — see that row.</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-15 re-verified live: Anton + IBM Plex Sans preloaded with crossorigin; zero Google Fonts refs; document.fonts reports all 3 faces loaded</t>
+          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-15 re-verified live: Anton + IBM Plex Sans preloaded with crossorigin; zero Google Fonts refs; document.fonts reports all 3 faces loaded | 2026-08-16 re-verified live: Anton + IBM Plex Sans (Regular/Bold) all report document.fonts status 'loaded', document.fonts.status 'loaded'; zero Google Fonts references. /brand/ additionally preloads IBMPlexSans-Italic.woff2 and the console warns it is 'not used within a few seconds of load' — investigated and DISMISSED as a non-finding: the italic face is genuinely used by 13 elements on that page and reports status 'loaded'; the warning is a below-the-fold timing artifact. No other page preloads italic, which is correct.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift | 2026-08-13 re-verified live: all 16 BlogPosting blocks carry every required field (headline, description, datePublished, dateModified, author.@type=Person + name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount); zero og-default.png drift.</t>
+          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift | 2026-08-13 re-verified live: all 16 BlogPosting blocks carry every required field (headline, description, datePublished, dateModified, author.@type=Person + name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount); zero og-default.png drift. | 2026-08-16 re-verified live: all 16 BlogPosting blocks re-verified live: every required field present (headline, description, datePublished, dateModified, author.@type=Person, publisher, mainEntityOfPage, image, url, inLanguage, wordCount) and JSON-LD image === og:image exactly, cache-bust included, on all 16. Zero og-default.png drift.</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: Faith 13/13, Identity 9/9, Art 3/3 with zero non-matching plates in any filtered view; while filtered the .earlier-more-wrap computes display:none, 0 client rects, offsetHeight 0 (unreachable by mouse or keyboard). The ab07b15 fix holds in production.</t>
+          <t>PASS — live-verified 2026-08-10: Faith 13/13, Identity 9/9, Art 3/3 with zero non-matching plates in any filtered view; while filtered the .earlier-more-wrap computes display:none, 0 client rects, offsetHeight 0 (unreachable by mouse or keyboard). The ab07b15 fix holds in production. | 2026-08-16 re-verified live: all three lanes re-verified live: Faith 13, Identity 9, Art 3 — exactly matching the lane-index counts. Verified against the real filter key (data-lane, space-separated) rather than the visible chips: all 9 identity plates carry 'identity' in data-lane. While filtered, .earlier-more-wrap computes display:none with 0 client rects; clearing restores display:flex.</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr"/>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: expand 8→16, collapse 16→8, aria-expanded false↔true and the button label track; collapse state survives a full filter cycle (clear restores the wrap to display:flex).</t>
+          <t>PASS — live-verified 2026-08-10: expand 8→16, collapse 16→8, aria-expanded false↔true and the button label track; collapse state survives a full filter cycle (clear restores the wrap to display:flex). | 2026-08-16 re-verified live: expand 8-&gt;16 and collapse 16-&gt;8 re-verified live; aria-expanded false&lt;-&gt;true and the label tracked ('View Earlier Essays — 8 more' &lt;-&gt; 'Show Less — showing all'); collapse state survived a full filter cycle.</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid | 2026-08-13 re-verified live: /feed.xml 200, Atom namespace, 16 &lt;entry&gt; elements — exactly matching the 16 articles on the homepage, zero set difference either direction.</t>
+          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid | 2026-08-13 re-verified live: /feed.xml 200, Atom namespace, 16 &lt;entry&gt; elements — exactly matching the 16 articles on the homepage, zero set difference either direction. | 2026-08-16 re-verified live: /feed.xml 200 with 16 &lt;entry&gt; elements; set-compared against the 16 article links on the live homepage — zero difference in either direction.</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s | 2026-08-13 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.16s using healthscrub+20260813@imjustdex.com.</t>
+          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s | 2026-08-13 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.16s using healthscrub+20260813@imjustdex.com. | 2026-08-16 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.05s using healthscrub+20260816@imjustdex.com.</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical | 2026-08-13 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200; /sitemap.xml correctly 404 post-cutover.</t>
+          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical | 2026-08-13 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200; /sitemap.xml correctly 404 post-cutover. | 2026-08-16 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200 and /words/the-stone -&gt; 301 -&gt; /words/the-stone/ re-verified live; /sitemap.xml correctly 404 post-cutover; /words -&gt; 301 home; /opsmeeting -&gt; 301 home.</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML | 2026-08-13 re-verified live: CSP header present and ENFORCING — a runtime &lt;style&gt; injection was blocked by style-src 'self' during F77 verification, which is direct proof the policy is live, not just declared. Per-route /brand/ and /feed.xml relaxations by design.</t>
+          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML | 2026-08-13 re-verified live: CSP header present and ENFORCING — a runtime &lt;style&gt; injection was blocked by style-src 'self' during F77 verification, which is direct proof the policy is live, not just declared. Per-route /brand/ and /feed.xml relaxations by design. | 2026-08-16 re-verified live: CSP present and strict on every page type; /brand/ and /feed.xml keep their by-design style-src 'unsafe-inline' relaxation. Zero inline &lt;style&gt; blocks in any built Astro page (home 0, article 0, about 0, phase0 0). Policy proven live again this run — a &lt;style&gt; injection was blocked, while CSSOM mutation of the already-loaded sheet succeeded, which is the documented distinction.</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes | 2026-08-13 re-verified live: all 5 security headers present on all 6 page types (home, article, about, brand, phase0, 404, feed): X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present.</t>
+          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes | 2026-08-13 re-verified live: all 5 security headers present on all 6 page types (home, article, about, brand, phase0, 404, feed): X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present. | 2026-08-16 re-verified live: all security headers re-verified live on home/article/brand/404/feed: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy, COOP same-origin, CORP same-origin.</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate. | 2026-08-13 re-verified live: versioned assets (/css, /js, /img) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift.</t>
+          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate. | 2026-08-13 re-verified live: versioned assets (/css, /js, /img) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-16 re-verified live: versioned assets (/css, /js, /img, /fonts) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift.</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page) | 2026-08-13 re-verified live: verified in the DEPLOYED sheet, not just source: tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, *::before, *::after with !important, plus scroll-behavior auto. Catches all 29 transitioned elements on the homepage.</t>
+          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page) | 2026-08-13 re-verified live: verified in the DEPLOYED sheet, not just source: tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, *::before, *::after with !important, plus scroll-behavior auto. Catches all 29 transitioned elements on the homepage. | 2026-08-16 re-verified live: re-verified in the LOADED CSSOM (not source): tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, ::before, ::after with !important plus scroll-behavior auto — catching all 8 transitioned elements on the article page.</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4. | 2026-08-13 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to a footer link that matched ':focus-visible' and computed outline 'solid 2px rgb(204, 0, 0)' at offset 2px.</t>
+          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4. | 2026-08-13 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to a footer link that matched ':focus-visible' and computed outline 'solid 2px rgb(204, 0, 0)' at offset 2px. | 2026-08-16 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to SUMMARY.study-note-trigger, which matched ':focus-visible' and computed outline 'rgb(204, 0, 0) solid 2px' at offset -2px.</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — .latest-tag (the red 'Latest' chip in the homepage standfirst bar) pairs `background: var(--accent)` with `color: var(--bg)`. In light mode that is cream on #c00 = 5.17:1 and passes. In dark mode --bg flips to #060606 and the same chip computes 3.44:1 at 11.52px/700 — under the 4.5:1 AA floor for small text (WCAG 1.4.3). Measured three times on settled live loads. The #c00/#060606 pair is sanctioned by the Phase 4.1 accent doctrine (DESIGN-SYSTEM.md:102) only for NON-text contrast at the 3:1 floor; this is a text use of it. Missed by prior runs because F77 sampled palette-level token pairs (body/muted/faint/accent text), not the one control that puts small text ON the accent fill — the same sheet-level vs per-control gap that hid F76. All other sampled combinations still pass: 33 distinct fg/bg/size combos in dark, 33 in light, this was the only failure.</t>
+          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — .latest-tag (the red 'Latest' chip in the homepage standfirst bar) pairs `background: var(--accent)` with `color: var(--bg)`. In light mode that is cream on #c00 = 5.17:1 and passes. In dark mode --bg flips to #060606 and the same chip computes 3.44:1 at 11.52px/700 — under the 4.5:1 AA floor for small text (WCAG 1.4.3). Measured three times on settled live loads. The #c00/#060606 pair is sanctioned by the Phase 4.1 accent doctrine (DESIGN-SYSTEM.md:102) only for NON-text contrast at the 3:1 floor; this is a text use of it. Missed by prior runs because F77 sampled palette-level token pairs (body/muted/faint/accent text), not the one control that puts small text ON the accent fill — the same sheet-level vs per-control gap that hid F76. All other sampled combinations still pass: 33 distinct fg/bg/size combos in dark, 33 in light, this was the only failure. | 2026-08-16 re-verified live: full-page compositor sweep across home (dark 92 elements / light 88), article (70), about (15), phase0 (84), brand and 404. Two light-mode 'failures' on .plate-image plates (h2.plate-title.inverse and p.plate-deck, both 1.06:1) were investigated and DISMISSED as false positives: those plates carry an ::after `linear-gradient(to top, rgba(0,0,0,.78) ...)` scrim, so the white text sits on a dark overlay, not the cream plate colour the compositor resolved — confirmed visually in a light-mode screenshot. Two compounding methodology bugs were behind the false read and are now fixed in the sweep: (a) the compositor walked background-COLOR only and ignored pseudo-element layers, (b) selector-level dedupe merged image and non-image plates under the same class string, so a passing element inherited a failing element's number. Lesson is the same shape as F84's: resolve the PAINTED surface, never infer it from an ancestor's declarations.</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt | 2026-08-13 re-verified live: home and article both single-h1, zero skipped heading levels (home H1 then 17x H2; article H1,H2,H2,H2,H2,H2), header/main/footer/nav all present. Zero images missing alt.</t>
+          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt | 2026-08-13 re-verified live: home and article both single-h1, zero skipped heading levels (home H1 then 17x H2; article H1,H2,H2,H2,H2,H2), header/main/footer/nav all present. Zero images missing alt. | 2026-08-16 re-verified live: single &lt;h1&gt; and zero skipped heading levels across all 21 live pages; header/main/footer/nav present on every page type; zero &lt;img&gt; without an alt attribute.</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr"/>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured.</t>
+          <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.latest-meta` 3.36:1 dark / 2.93:1 light on the homepage, and 3.36:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot.</t>
+          <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.hero-corner` 3.71:1 dark on the homepage, and 3.71:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads.</t>
+          <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: /brand/ `.latest-tag` 3.44:1 — and /brand/'s loaded-sheet list confirms the cause directly: tokens, shell, plates, home-augment, article, brand.css, with NO home-v2.css. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay.</t>
+          <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.next-meta` 2.81:1 dark on the /brand/ dogfood demo (still latent on the live homepage — no upcoming essay exists). Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept.</t>
+          <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.notfound-eyebrow span.divider` 3.61:1 on /404. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent.</t>
+          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions.</t>
         </is>
       </c>
       <c r="I93" s="9" t="inlineStr">
@@ -5355,8 +5355,65 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>F91</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Skip-link contrast on bespoke-CSS surfaces (cascade specificity)</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>As a keyboard user landing on any page — including the bespoke passthrough pages — I can read the skip link when it takes focus.</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>`.skip-link` renders its designed inverted chip (background var(--ink), text var(--bg)) on EVERY surface. No page-level stylesheet may out-specify the shell rule and repaint the chip's text, and the rendered pair must meet WCAG 1.4.3 at &gt;=4.5:1.</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>css/shell.css:12-27; css/phase0.css:55; phase0/index.html:80</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Cataloged</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/High (2026-08-16) — /phase0/'s skip link, the first focusable element on the page, computed `color: rgba(243,240,232,.82)` on its own `background: var(--ink)` cream chip: 1.00:1. This is the worst ratio the ledger has recorded and the only finding to date where the text is not merely low-contrast but literally invisible — a sighted keyboard user sees the accent focus ring land on a blank cream box. NOT a colour bug: `--bg` resolves correctly to #060606 at every level of the chain (verified by walking the ancestor chain: A.skip-link / BODY.phase0 / HTML.dark-mode all report #060606). It is a specificity bug. Three rules set colour on this element — `a {color:inherit}` (0,0,1) in tokens.css, `.skip-link {color:var(--bg)}` (0,1,0) in shell.css, and `.phase0 a {color:inherit}` (0,1,1) in phase0.css. The last wins on specificity and hands the chip back the inherited body cream. Scope is exactly one page: /brand/, the other bespoke-CSS surface, carries no blanket `a` rule and measured clean. Missed by every prior run because the skip link sits at left:-999px in its resting state, so a sweep that filters to on-screen elements never measures it — this run caught it by measuring every element with layout geometry regardless of viewport position.</t>
+        </is>
+      </c>
+      <c r="I94" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260816, commit 79df261): hardened the shell rule to `.skip-link, .skip-link:link, .skip-link:visited` — specificity (0,2,0), which beats `.phase0 a` (0,1,1) on the class/pseudo-class count regardless of source order. Fixed in the SHARED sheet rather than in phase0.css deliberately, so any future bespoke surface that adds a blanket link rule inherits the immunity: this is the F87 lesson applied forward (fix the shared sheet, not the one surface that happened to break). A skip link always carries an href, so :link/:visited covers every real state including :focus. Cache-bust shell.css phase23-&gt;36 across all 7 referencing files — the sheet ships `immutable, max-age=31536000`, so without the bump returning visitors would hold the broken sheet for a year.</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>PASS (build-verified 2026-08-16) — `npm run build` clean, 19 pages; dist/css/shell.css carries the hardened selector and all 21 built pages reference shell.css?v=phase36. Cascade verified empirically rather than by reasoning alone: inserted the exact committed selector into the live shell.css CSSOM (CSP blocks &lt;style&gt; injection but not CSSOM mutation of an already-loaded same-origin sheet) and re-measured — /phase0/ 1.00:1 -&gt; 17.79:1, with the colour flipping to the intended rgb(6,6,6) on cream. Regression-checked on the two surfaces most likely to be disturbed: homepage and /brand/ both no-op (already rgb(6,6,6) on cream before and after). Goes live-verified on the next SCRUB after Dexter merges.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K93"/>
+  <autoFilter ref="A3:K94"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -5436,7 +5493,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -5463,7 +5520,7 @@
         </is>
       </c>
       <c r="B13" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -5493,7 +5550,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -5509,7 +5566,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Total features: 90</t>
+          <t>Total features: 91</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>PASS — masthead .brand-block → '/' present on home/about/404/phase0/brand/article; aria-label 'Dexter Jakes home' | 2026-08-15 re-verified live: brand-block present and linking / on all 20 pages</t>
+          <t>PASS — masthead .brand-block → '/' present on home/about/404/phase0/brand/article; aria-label 'Dexter Jakes home' | 2026-08-15 re-verified live: brand-block present and linking / on all 20 pages | 2026-08-25 re-verified live: brand-block present and linking / on all 20 crawled routes; aria-label intact.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>PASS — brand-word: Words (home/article/about/brand), 404, Phase 0 — matches documented intent | 2026-08-15 re-verified live: brand-word: home/about/article 'Words', 404 '404', phase0 'Phase 0' — matches the documented about-page quirk</t>
+          <t>PASS — brand-word: Words (home/article/about/brand), 404, Phase 0 — matches documented intent | 2026-08-15 re-verified live: brand-word: home/about/article 'Words', 404 '404', phase0 'Phase 0' — matches the documented about-page quirk | 2026-08-25 re-verified live: brand-word: "Words" on home/about/article, "404" on /404, "Phase 0" on /phase0/ — matches documented intent.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks. | 2026-08-13 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways; --bg/--ink/--accent-text all re-resolved (#060606/#f3f0e8/#ff4d4d dark, #f4f4f1/#050505/#c00 light). | 2026-08-16 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways (dxmode=light then dxmode=dark); --bg #060606&lt;-&gt;#f4f4f1 and --ink #f3f0e8&lt;-&gt;#050505 both re-resolved; label and aria-pressed tracked ('Mode: Dark'/true &lt;-&gt; 'Mode: Light'/false).</t>
+          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks. | 2026-08-13 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways; --bg/--ink/--accent-text all re-resolved (#060606/#f3f0e8/#ff4d4d dark, #f4f4f1/#050505/#c00 light). | 2026-08-16 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways (dxmode=light then dxmode=dark); --bg #060606&lt;-&gt;#f4f4f1 and --ink #f3f0e8&lt;-&gt;#050505 both re-resolved; label and aria-pressed tracked ('Mode: Dark'/true &lt;-&gt; 'Mode: Light'/false). | 2026-08-25 re-verified live: toggle re-verified with a REAL pointer click (not element.click()) on both the homepage and /words/the-stone/: page repaints dark&lt;-&gt;light, dxmode cookie written both ways, label and aria-pressed track. METHOD NOTE: a programmatic element.click() flips the class, the tokens and the cookie but leaves body's used background/color stale in getComputedStyle until a repaint is forced — that is a measurement artifact, NOT a site defect, and it read as an article-page mode regression for several minutes this run. Always verify this row with a real click.</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production. | 2026-08-13 re-verified live: tab-target verified on live: .skip-link reveals from left:-999px to a 83x69 box at (12,12), cream-on-ink 17.79:1; activating it moved document.activeElement to MAIN#archive (tabindex=-1). Article pages target #article. | 2026-08-16 re-verified live: structural half re-verified live: .skip-link is the first focusable element in document order on every page type, and its target (MAIN#article / MAIN#archive / MAIN#phase0 / MAIN#main) carries tabindex=-1. End-to-end activation NOT re-exercisable this run — the browser pane reports document.visibilityState 'hidden' and drops page focus on every reload, so a fresh-load Tab lands on BODY. Harness limitation, not a site regression; last live activation was 2026-08-13. NOTE: this row's sweep is what surfaced F91 — see that row.</t>
+          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production. | 2026-08-13 re-verified live: tab-target verified on live: .skip-link reveals from left:-999px to a 83x69 box at (12,12), cream-on-ink 17.79:1; activating it moved document.activeElement to MAIN#archive (tabindex=-1). Article pages target #article. | 2026-08-16 re-verified live: structural half re-verified live: .skip-link is the first focusable element in document order on every page type, and its target (MAIN#article / MAIN#archive / MAIN#phase0 / MAIN#main) carries tabindex=-1. End-to-end activation NOT re-exercisable this run — the browser pane reports document.visibilityState 'hidden' and drops page focus on every reload, so a fresh-load Tab lands on BODY. Harness limitation, not a site regression; last live activation was 2026-08-13. NOTE: this row's sweep is what surfaced F91 — see that row. | 2026-08-25 re-verified live: verified end-to-end live under REAL keyboard input on /words/the-stone/ — the gap the 2026-08-16 run had to leave open. .skip-link is the first focusable in DOM order, reveals from left:-999px to a 126x46 chip at (12,12), computes 17.79:1 (#060606 on #f3f0e8), and pressing Enter sets location.hash to #article and moves document.activeElement to MAIN#article (tabindex=-1).</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -928,7 +928,7 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>PASS — footer strip + links present on all page types | 2026-08-15 re-verified live: footer: Instagram + X both target=_blank rel="noopener noreferrer", /feed.xml, /about/, "Built by Dex"; zero _blank links missing rel site-wide</t>
+          <t>PASS — footer strip + links present on all page types | 2026-08-15 re-verified live: footer: Instagram + X both target=_blank rel="noopener noreferrer", /feed.xml, /about/, "Built by Dex"; zero _blank links missing rel site-wide | 2026-08-25 re-verified live: footer links resolve: instagram.com/ImJustDex 200, x.com/ImJustDex 200, /feed.xml 200.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr"/>
@@ -977,7 +977,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>PASS (2026-08-15 scrub) — home/about/phase0/articles all carry the feed discovery link; /404 correctly omits it. NOTE: the prior `expected` said articles do NOT include it. That text was stale — ArticleLayout has emitted the link since a4f4f25; the site was never wrong, the row was. Expectation corrected, not the code.</t>
+          <t>PASS (2026-08-15 scrub) — home/about/phase0/articles all carry the feed discovery link; /404 correctly omits it. NOTE: the prior `expected` said articles do NOT include it. That text was stale — ArticleLayout has emitted the link since a4f4f25; the site was never wrong, the row was. Expectation corrected, not the code. | 2026-08-25 re-verified live: &lt;link rel=alternate type=application/atom+xml href=/feed.xml&gt; present in head.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path | 2026-08-15 re-verified live: favicon-32.png + apple-touch-icon.png linked on every page; both 200 (1327b / 5729b)</t>
+          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path | 2026-08-15 re-verified live: favicon-32.png + apple-touch-icon.png linked on every page; both 200 (1327b / 5729b) | 2026-08-25 re-verified live: /img/favicon-32.png 200, /img/apple-touch-icon.png 200 on every referenced path.</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-15 re-verified live: Anton + IBM Plex Sans preloaded with crossorigin; zero Google Fonts refs; document.fonts reports all 3 faces loaded | 2026-08-16 re-verified live: Anton + IBM Plex Sans (Regular/Bold) all report document.fonts status 'loaded', document.fonts.status 'loaded'; zero Google Fonts references. /brand/ additionally preloads IBMPlexSans-Italic.woff2 and the console warns it is 'not used within a few seconds of load' — investigated and DISMISSED as a non-finding: the italic face is genuinely used by 13 elements on that page and reports status 'loaded'; the warning is a below-the-fold timing artifact. No other page preloads italic, which is correct.</t>
+          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-15 re-verified live: Anton + IBM Plex Sans preloaded with crossorigin; zero Google Fonts refs; document.fonts reports all 3 faces loaded | 2026-08-16 re-verified live: Anton + IBM Plex Sans (Regular/Bold) all report document.fonts status 'loaded', document.fonts.status 'loaded'; zero Google Fonts references. /brand/ additionally preloads IBMPlexSans-Italic.woff2 and the console warns it is 'not used within a few seconds of load' — investigated and DISMISSED as a non-finding: the italic face is genuinely used by 13 elements on that page and reports status 'loaded'; the warning is a below-the-fold timing artifact. No other page preloads italic, which is correct. | 2026-08-25 re-verified live: document.fonts.status "loaded"; Anton/400, IBM Plex Sans/400 and /700 all report loaded. All three woff2 200. No FOUT observed.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com | 2026-08-15 re-verified live: zero duplicate &lt;title&gt; across 20 pages; /404 canonical is /404 as specified</t>
+          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com | 2026-08-15 re-verified live: zero duplicate &lt;title&gt; across 20 pages; /404 canonical is /404 as specified | 2026-08-25 re-verified live: &lt;title&gt;, meta description and canonical present and correct on all 20 routes; every canonical points at imjustdex.com.</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand) | 2026-08-15 re-verified live: twitter:card summary_large_image on every page in scope (404 correctly excluded)</t>
+          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand) | 2026-08-15 re-verified live: twitter:card summary_large_image on every page in scope (404 correctly excluded) | 2026-08-25 re-verified live: og:title / og:description / og:image present on all 20; all 16 og-&lt;slug&gt;.png 200; og:image byte-identical to the JSON-LD image on all 16.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor) | 2026-08-15 re-verified live: home @graph carries WebSite + Person; Person has name/url/sameAs/jobTitle/worksFor — no missing fields</t>
+          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor) | 2026-08-15 re-verified live: home @graph carries WebSite + Person; Person has name/url/sameAs/jobTitle/worksFor — no missing fields | 2026-08-25 re-verified live: WebSite + Person @graph complete on /; Person carries name, url, sameAs, jobTitle, worksFor.</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description) | 2026-08-15 re-verified live: about ProfilePage mainEntity Person complete — name/url/jobTitle/worksFor/sameAs/description all present</t>
+          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description) | 2026-08-15 re-verified live: about ProfilePage mainEntity Person complete — name/url/jobTitle/worksFor/sameAs/description all present | 2026-08-25 re-verified live: ProfilePage on /about/ with mainEntity @type Person carrying name, url, jobTitle, worksFor, sameAs, description.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift | 2026-08-13 re-verified live: all 16 BlogPosting blocks carry every required field (headline, description, datePublished, dateModified, author.@type=Person + name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount); zero og-default.png drift. | 2026-08-16 re-verified live: all 16 BlogPosting blocks re-verified live: every required field present (headline, description, datePublished, dateModified, author.@type=Person, publisher, mainEntityOfPage, image, url, inLanguage, wordCount) and JSON-LD image === og:image exactly, cache-bust included, on all 16. Zero og-default.png drift.</t>
+          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift | 2026-08-13 re-verified live: all 16 BlogPosting blocks carry every required field (headline, description, datePublished, dateModified, author.@type=Person + name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount); zero og-default.png drift. | 2026-08-16 re-verified live: all 16 BlogPosting blocks re-verified live: every required field present (headline, description, datePublished, dateModified, author.@type=Person, publisher, mainEntityOfPage, image, url, inLanguage, wordCount) and JSON-LD image === og:image exactly, cache-bust included, on all 16. Zero og-default.png drift. | 2026-08-25 re-verified live: BlogPosting on all 16 articles; every required field present (headline, description, datePublished, dateModified, author.Person.name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount). Zero og-default.png regressions.</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>PASS — robots.txt Allow / + Sitemap → sitemap-index.xml | 2026-08-13 re-verified live: /robots.txt 200, Sitemap directive -&gt; https://imjustdex.com/sitemap-index.xml.</t>
+          <t>PASS — robots.txt Allow / + Sitemap → sitemap-index.xml | 2026-08-13 re-verified live: /robots.txt 200, Sitemap directive -&gt; https://imjustdex.com/sitemap-index.xml. | 2026-08-25 re-verified live: robots.txt = "User-agent: *\nAllow: /\n\nSitemap: https://imjustdex.com/sitemap-index.xml". /DESIGN-SYSTEM.md correctly 404s.</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>PASS — sitemap-0.xml 20 locs = exactly the published set + about/brand/phase0; no missing, no orphans | 2026-08-13 re-verified live: /sitemap-index.xml -&gt; sitemap-0.xml; sitemap-0 lists 20 URLs covering all 16 articles + /, /about/, /brand/, /phase0/. Zero missing.</t>
+          <t>PASS — sitemap-0.xml 20 locs = exactly the published set + about/brand/phase0; no missing, no orphans | 2026-08-13 re-verified live: /sitemap-index.xml -&gt; sitemap-0.xml; sitemap-0 lists 20 URLs covering all 16 articles + /, /about/, /brand/, /phase0/. Zero missing. | 2026-08-25 re-verified live: sitemap-index.xml references sitemap-0.xml; sitemap-0.xml carries exactly 20 locs = 16 articles + /, /about/, /brand/, /phase0/. The drafted essay is correctly absent.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>404 half PASS (noindex,nofollow live). Coming-soon half PENDING — no upcoming entry exists to render one</t>
+          <t>404 half PASS (noindex,nofollow live). Coming-soon half PENDING — no upcoming entry exists to render one | 2026-08-25: 404 half re-verified live (meta robots noindex,nofollow present, bespoke body served at HTTP 200). Coming-soon half still PENDING — no upcoming entry exists to render one.</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>PASS — Entry No. 16 / Week of July 5, 2026, LatestBar → newest essay | 2026-08-13 re-verified live: LatestBar reads 'Entry No. 16 / Week of July 5, 2026' and links to /words/send-someone-else/ (the newest). NOTE: its .latest-tag chip is the F77 finding this run.</t>
+          <t>PASS — Entry No. 16 / Week of July 5, 2026, LatestBar → newest essay | 2026-08-13 re-verified live: LatestBar reads 'Entry No. 16 / Week of July 5, 2026' and links to /words/send-someone-else/ (the newest). NOTE: its .latest-tag chip is the F77 finding this run. | 2026-08-25 re-verified live: issue head renders "Entry No. 16" / "Week of July 5, 2026" from the lead; standfirst links /words/send-someone-else/.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>PASS — Faith 13 / Identity 09 / Art 03, verified against frontmatter lanes; 16 articles | 2026-08-13 re-verified live: lane-index counts Faith 13 / Identity 09 / Art 03 — non-negative, zero-padded, and consistent with 16 essays counted per lane (15 .plate-lane chips + 1 .lead-badge-lane).</t>
+          <t>PASS — Faith 13 / Identity 09 / Art 03, verified against frontmatter lanes; 16 articles | 2026-08-13 re-verified live: lane-index counts Faith 13 / Identity 09 / Art 03 — non-negative, zero-padded, and consistent with 16 essays counted per lane (15 .plate-lane chips + 1 .lead-badge-lane). | 2026-08-25 re-verified live: lane counts render Faith 13 / Identity 09 / Art 03 — matches the frontmatter tally across the 16 tracked essays exactly (multi-lane counted per lane).</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>PASS — lead plate = send-someone-else (newest published)</t>
+          <t>PASS — lead plate = send-someone-else (newest published) | 2026-08-25 re-verified live: lead plate renders send-someone-else with correct eyebrow, deck and 16 min read.</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>PASS — correctly absent: zero upcoming essays in the collection</t>
+          <t>PASS — correctly absent: zero upcoming essays in the collection | 2026-08-25 re-verified live: correctly ABSENT — index.astro renders IssueNext only when an upcoming entry exists, and none does. Not a regression.</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Authored prev/next render correctly on all 16. Ghost/teaser path PENDING — requires a future-dated entry; none exists. 2026-08-10 PM: the derive-from-live-status fix (p3) live-verified, then the underlying data cleaned — the 4 stale ghost:true flags are gone (see F81). Zero `ghost: true` remain in the collection; all 16 essays render real .article-nav-link anchors, 15 rel=next head links (newest correctly has none), zero article-nav-ghost teasers.</t>
+          <t>Authored prev/next render correctly on all 16. Ghost/teaser path PENDING — requires a future-dated entry; none exists. 2026-08-10 PM: the derive-from-live-status fix (p3) live-verified, then the underlying data cleaned — the 4 stale ghost:true flags are gone (see F81). Zero `ghost: true` remain in the collection; all 16 essays render real .article-nav-link anchors, 15 rel=next head links (newest correctly has none), zero article-nav-ghost teasers. | 2026-08-25 re-verified live: all 16 essays render real .article-nav-link anchors; zero `ghost: true` remain in the collection. Ghost/teaser path still PENDING — still requires a future-dated entry and none exists.</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>PASS — rel=prev emitted where prev authored; rel=next where next authored and live</t>
+          <t>PASS — rel=prev emitted where prev authored; rel=next where next authored and live | 2026-08-25 re-verified live: rel=prev/next head links intact across the chain.</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr"/>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>PENDING — all 16 entries are status published with past dates, so isUpcomingData() is false everywhere and no coming-soon page renders</t>
+          <t>PENDING — all 16 entries are status published with past dates, so isUpcomingData() is false everywhere and no coming-soon page renders | 2026-08-25: still PENDING for the same structural reason — all 16 built entries are status:published with past dates. NOTE: an untracked draft (src/content/words/before-i-had-the-words.mdx, status:"drafted", publishedDate 2026-08-07) sits in Dexter's working tree. It is correctly excluded from the build (19 pages, 16 articles) and does not exercise this path either, since its date is in the past, not the future.</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid | 2026-08-13 re-verified live: /feed.xml 200, Atom namespace, 16 &lt;entry&gt; elements — exactly matching the 16 articles on the homepage, zero set difference either direction. | 2026-08-16 re-verified live: /feed.xml 200 with 16 &lt;entry&gt; elements; set-compared against the 16 article links on the live homepage — zero difference in either direction.</t>
+          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid | 2026-08-13 re-verified live: /feed.xml 200, Atom namespace, 16 &lt;entry&gt; elements — exactly matching the 16 articles on the homepage, zero set difference either direction. | 2026-08-16 re-verified live: /feed.xml 200 with 16 &lt;entry&gt; elements; set-compared against the 16 article links on the live homepage — zero difference in either direction. | 2026-08-25 re-verified live: /feed.xml 200, 16 &lt;entry&gt; elements matching the 16 published articles exactly — no gaps, no extras.</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>PASS — feed.xsl 200 and &lt;?xml-stylesheet?&gt; PI present | 2026-08-13 re-verified live: /feed.xsl 200 and referenced via &lt;?xml-stylesheet?&gt; in the feed prolog.</t>
+          <t>PASS — feed.xsl 200 and &lt;?xml-stylesheet?&gt; PI present | 2026-08-13 re-verified live: /feed.xsl 200 and referenced via &lt;?xml-stylesheet?&gt; in the feed prolog. | 2026-08-25 re-verified live: /feed.xsl 200 and feed.xml carries &lt;?xml-stylesheet href="/feed.xsl"?&gt;.</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>PASS — GET /api/subscribe → 405 method_not_allowed</t>
+          <t>PASS — GET /api/subscribe → 405 method_not_allowed | 2026-08-25 re-verified live: /api/subscribe reachable and behaving; rewrite chain intact.</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>PASS — filled honeypot → 200 silent success, no Mailchimp write; field off-canvas (left:-5000px, tabindex -1, aria-hidden)</t>
+          <t>PASS — filled honeypot → 200 silent success, no Mailchimp write; field off-canvas (left:-5000px, tabindex -1, aria-hidden) | 2026-08-25 re-verified live: honeypot re-verified live: POST with website=spam returned HTTP 200 {"ok":true,"message":"subscribed"} — the intended silent drop, indistinguishable from success to a bot.</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>PASS — invalid address → 400 invalid_email; plus-addressed valid address accepted (clients encode + as %2B via URLSearchParams(FormData))</t>
+          <t>PASS — invalid address → 400 invalid_email; plus-addressed valid address accepted (clients encode + as %2B via URLSearchParams(FormData)) | 2026-08-25 re-verified live: email validation re-verified live: POST email=notanemail returned HTTP 400 {"ok":false,"error":"invalid_email"}.</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s | 2026-08-13 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.16s using healthscrub+20260813@imjustdex.com. | 2026-08-16 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.05s using healthscrub+20260816@imjustdex.com.</t>
+          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s | 2026-08-13 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.16s using healthscrub+20260813@imjustdex.com. | 2026-08-16 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.05s using healthscrub+20260816@imjustdex.com. | 2026-08-25 re-verified live: smoke POST with healthscrub+20260825@imjustdex.com returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.20s.</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical | 2026-08-13 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200; /sitemap.xml correctly 404 post-cutover. | 2026-08-16 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200 and /words/the-stone -&gt; 301 -&gt; /words/the-stone/ re-verified live; /sitemap.xml correctly 404 post-cutover; /words -&gt; 301 home; /opsmeeting -&gt; 301 home.</t>
+          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical | 2026-08-13 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200; /sitemap.xml correctly 404 post-cutover. | 2026-08-16 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200 and /words/the-stone -&gt; 301 -&gt; /words/the-stone/ re-verified live; /sitemap.xml correctly 404 post-cutover; /words -&gt; 301 home; /opsmeeting -&gt; 301 home. | 2026-08-25 re-verified live: /about, /brand, /phase0 and /words/the-stone each return a single 301 to the trailing-slash form, which returns 200. No loops.</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>PASS — /api/subscribe rewrite reaches the function (405 on GET, 400/200 on POST) | 2026-08-13 re-verified live: /api/subscribe rewrite reached the Netlify function and returned a Mailchimp success body.</t>
+          <t>PASS — /api/subscribe rewrite reaches the function (405 on GET, 400/200 on POST) | 2026-08-13 re-verified live: /api/subscribe rewrite reached the Netlify function and returned a Mailchimp success body. | 2026-08-25 re-verified live: /api/subscribe rewrite to the Netlify function verified by the live smoke POST.</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr"/>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>PASS — unmatched route → 404 with the branded body | 2026-08-13 re-verified live: /404 returns 200 with the bespoke 'Nothing to Document Here' body and noindex; /DESIGN-SYSTEM.md and /audit/features.json both 404 (docs not leaking).</t>
+          <t>PASS — unmatched route → 404 with the branded body | 2026-08-13 re-verified live: /404 returns 200 with the bespoke 'Nothing to Document Here' body and noindex; /DESIGN-SYSTEM.md and /audit/features.json both 404 (docs not leaking). | 2026-08-25 re-verified live: /404 returns HTTP 200 with the bespoke notfound-plate body and meta robots noindex.</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML | 2026-08-13 re-verified live: CSP header present and ENFORCING — a runtime &lt;style&gt; injection was blocked by style-src 'self' during F77 verification, which is direct proof the policy is live, not just declared. Per-route /brand/ and /feed.xml relaxations by design. | 2026-08-16 re-verified live: CSP present and strict on every page type; /brand/ and /feed.xml keep their by-design style-src 'unsafe-inline' relaxation. Zero inline &lt;style&gt; blocks in any built Astro page (home 0, article 0, about 0, phase0 0). Policy proven live again this run — a &lt;style&gt; injection was blocked, while CSSOM mutation of the already-loaded sheet succeeded, which is the documented distinction.</t>
+          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML | 2026-08-13 re-verified live: CSP header present and ENFORCING — a runtime &lt;style&gt; injection was blocked by style-src 'self' during F77 verification, which is direct proof the policy is live, not just declared. Per-route /brand/ and /feed.xml relaxations by design. | 2026-08-16 re-verified live: CSP present and strict on every page type; /brand/ and /feed.xml keep their by-design style-src 'unsafe-inline' relaxation. Zero inline &lt;style&gt; blocks in any built Astro page (home 0, article 0, about 0, phase0 0). Policy proven live again this run — a &lt;style&gt; injection was blocked, while CSSOM mutation of the already-loaded sheet succeeded, which is the documented distinction. | 2026-08-25 re-verified live: CSP present on every route and empirically ENFORCED — an injected inline &lt;style&gt; during this run was blocked by style-src 'self' and logged as the only console error of the whole scrub. Per-route relaxation for /brand/ (style-src adds 'unsafe-inline') confirmed by design. Zero inline &lt;style&gt; blocks in any built page.</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes | 2026-08-13 re-verified live: all 5 security headers present on all 6 page types (home, article, about, brand, phase0, 404, feed): X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present. | 2026-08-16 re-verified live: all security headers re-verified live on home/article/brand/404/feed: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy, COOP same-origin, CORP same-origin.</t>
+          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes | 2026-08-13 re-verified live: all 5 security headers present on all 6 page types (home, article, about, brand, phase0, 404, feed): X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present. | 2026-08-16 re-verified live: all security headers re-verified live on home/article/brand/404/feed: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy, COOP same-origin, CORP same-origin. | 2026-08-25 re-verified live: all five headers present on / and on an article: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000; includeSubDomains; preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present on /.</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate. | 2026-08-13 re-verified live: versioned assets (/css, /js, /img) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-16 re-verified live: versioned assets (/css, /js, /img, /fonts) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift.</t>
+          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate. | 2026-08-13 re-verified live: versioned assets (/css, /js, /img) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-16 re-verified live: versioned assets (/css, /js, /img, /fonts) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-25 re-verified live: versioned CSS, fonts and images all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift on either tier.</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr"/>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page) | 2026-08-13 re-verified live: verified in the DEPLOYED sheet, not just source: tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, *::before, *::after with !important, plus scroll-behavior auto. Catches all 29 transitioned elements on the homepage. | 2026-08-16 re-verified live: re-verified in the LOADED CSSOM (not source): tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, ::before, ::after with !important plus scroll-behavior auto — catching all 8 transitioned elements on the article page.</t>
+          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page) | 2026-08-13 re-verified live: verified in the DEPLOYED sheet, not just source: tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, *::before, *::after with !important, plus scroll-behavior auto. Catches all 29 transitioned elements on the homepage. | 2026-08-16 re-verified live: re-verified in the LOADED CSSOM (not source): tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, ::before, ::after with !important plus scroll-behavior auto — catching all 8 transitioned elements on the article page. | 2026-08-25 re-verified live: tokens.css:584 zeroes transition-duration and animation-duration on *, ::before and ::after under prefers-reduced-motion: reduce and sets scroll-behavior auto; home-augment.css:1012 adds the targeted transition:none block. Both present in the served sheets.</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr"/>
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4. | 2026-08-13 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to a footer link that matched ':focus-visible' and computed outline 'solid 2px rgb(204, 0, 0)' at offset 2px. | 2026-08-16 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to SUMMARY.study-note-trigger, which matched ':focus-visible' and computed outline 'rgb(204, 0, 0) solid 2px' at offset -2px.</t>
+          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4. | 2026-08-13 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to a footer link that matched ':focus-visible' and computed outline 'solid 2px rgb(204, 0, 0)' at offset 2px. | 2026-08-16 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to SUMMARY.study-note-trigger, which matched ':focus-visible' and computed outline 'rgb(204, 0, 0) solid 2px' at offset -2px. | 2026-08-25 re-verified live: re-verified under REAL keyboard input: tabbing to .study-note-trigger on an article paints outline solid 2px rgb(204,0,0) (--focus-ring) at -2px offset. NOTE for future runs: a programmatic element.focus() does NOT satisfy :focus-visible in Chrome and will report outline:none across the board — a false positive this run initially produced.</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — .latest-tag (the red 'Latest' chip in the homepage standfirst bar) pairs `background: var(--accent)` with `color: var(--bg)`. In light mode that is cream on #c00 = 5.17:1 and passes. In dark mode --bg flips to #060606 and the same chip computes 3.44:1 at 11.52px/700 — under the 4.5:1 AA floor for small text (WCAG 1.4.3). Measured three times on settled live loads. The #c00/#060606 pair is sanctioned by the Phase 4.1 accent doctrine (DESIGN-SYSTEM.md:102) only for NON-text contrast at the 3:1 floor; this is a text use of it. Missed by prior runs because F77 sampled palette-level token pairs (body/muted/faint/accent text), not the one control that puts small text ON the accent fill — the same sheet-level vs per-control gap that hid F76. All other sampled combinations still pass: 33 distinct fg/bg/size combos in dark, 33 in light, this was the only failure. | 2026-08-16 re-verified live: full-page compositor sweep across home (dark 92 elements / light 88), article (70), about (15), phase0 (84), brand and 404. Two light-mode 'failures' on .plate-image plates (h2.plate-title.inverse and p.plate-deck, both 1.06:1) were investigated and DISMISSED as false positives: those plates carry an ::after `linear-gradient(to top, rgba(0,0,0,.78) ...)` scrim, so the white text sits on a dark overlay, not the cream plate colour the compositor resolved — confirmed visually in a light-mode screenshot. Two compounding methodology bugs were behind the false read and are now fixed in the sweep: (a) the compositor walked background-COLOR only and ignored pseudo-element layers, (b) selector-level dedupe merged image and non-image plates under the same class string, so a passing element inherited a failing element's number. Lesson is the same shape as F84's: resolve the PAINTED surface, never infer it from an ancestor's declarations.</t>
+          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — .latest-tag (the red 'Latest' chip in the homepage standfirst bar) pairs `background: var(--accent)` with `color: var(--bg)`. In light mode that is cream on #c00 = 5.17:1 and passes. In dark mode --bg flips to #060606 and the same chip computes 3.44:1 at 11.52px/700 — under the 4.5:1 AA floor for small text (WCAG 1.4.3). Measured three times on settled live loads. The #c00/#060606 pair is sanctioned by the Phase 4.1 accent doctrine (DESIGN-SYSTEM.md:102) only for NON-text contrast at the 3:1 floor; this is a text use of it. Missed by prior runs because F77 sampled palette-level token pairs (body/muted/faint/accent text), not the one control that puts small text ON the accent fill — the same sheet-level vs per-control gap that hid F76. All other sampled combinations still pass: 33 distinct fg/bg/size combos in dark, 33 in light, this was the only failure. | 2026-08-16 re-verified live: full-page compositor sweep across home (dark 92 elements / light 88), article (70), about (15), phase0 (84), brand and 404. Two light-mode 'failures' on .plate-image plates (h2.plate-title.inverse and p.plate-deck, both 1.06:1) were investigated and DISMISSED as false positives: those plates carry an ::after `linear-gradient(to top, rgba(0,0,0,.78) ...)` scrim, so the white text sits on a dark overlay, not the cream plate colour the compositor resolved — confirmed visually in a light-mode screenshot. Two compounding methodology bugs were behind the false read and are now fixed in the sweep: (a) the compositor walked background-COLOR only and ignored pseudo-element layers, (b) selector-level dedupe merged image and non-image plates under the same class string, so a passing element inherited a failing element's number. Lesson is the same shape as F84's: resolve the PAINTED surface, never infer it from an ancestor's declarations. | 2026-08-25 re-verified live: .latest-tag on the live homepage in dark mode measures 5.17:1 (rgb(243,240,232) on rgb(204,0,0)) — the F77 fix still holds, no regression.</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt | 2026-08-13 re-verified live: home and article both single-h1, zero skipped heading levels (home H1 then 17x H2; article H1,H2,H2,H2,H2,H2), header/main/footer/nav all present. Zero images missing alt. | 2026-08-16 re-verified live: single &lt;h1&gt; and zero skipped heading levels across all 21 live pages; header/main/footer/nav present on every page type; zero &lt;img&gt; without an alt attribute.</t>
+          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt | 2026-08-13 re-verified live: home and article both single-h1, zero skipped heading levels (home H1 then 17x H2; article H1,H2,H2,H2,H2,H2), header/main/footer/nav all present. Zero images missing alt. | 2026-08-16 re-verified live: single &lt;h1&gt; and zero skipped heading levels across all 21 live pages; header/main/footer/nav present on every page type; zero &lt;img&gt; without an alt attribute. | 2026-08-25 re-verified live: header/main/footer/nav present on every page type; exactly one &lt;h1&gt; per page across all 20 routes; zero skipped heading levels; zero &lt;img&gt; without alt.</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr"/>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>PASS — parity 16/16 verified live; every /words/&lt;slug&gt; returns a single 301 to its trailing-slash canonical; no orphan rules | 2026-08-13 re-verified live: all 16 /words/&lt;slug&gt; (no trailing slash) return 301; all 16 /words/&lt;slug&gt;/ return 200 in 0.31-0.45s.</t>
+          <t>PASS — parity 16/16 verified live; every /words/&lt;slug&gt; returns a single 301 to its trailing-slash canonical; no orphan rules | 2026-08-13 re-verified live: all 16 /words/&lt;slug&gt; (no trailing slash) return 301; all 16 /words/&lt;slug&gt;/ return 200 in 0.31-0.45s. | 2026-08-25 re-verified live: /words/the-stone -&gt; 301 -&gt; /words/the-stone/ -&gt; 200.</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr"/>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: show-me-your-glory emits rel=next to send-someone-else and renders a normal (non-ghost) forward nav; forward chain walks all 16 published essays end to end.</t>
+          <t>PASS — live-verified 2026-08-10: show-me-your-glory emits rel=next to send-someone-else and renders a normal (non-ghost) forward nav; forward chain walks all 16 published essays end to end. | 2026-08-25 re-verified live: forward chain walks all 16 published essays end to end; the chronologically newest (send-someone-else) correctly carries no next.</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr"/>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — CORRECTED SCOPE, and the correction matters. The morning scrub read the declarations and reported FOUR failing hover rules. Re-measured under REAL pointer hover before fixing, only TWO are real: `.issue-latest:hover .latest-cta` (14.08px/700) and `.identity-hero .hero-link.primary:hover` (14.08px/700), both `color: var(--bg)` on a `background: var(--accent)` fill = 3.44:1 in dark against a 4.5:1 floor. The other two were FALSE POSITIVES: `.issue-latest:hover` takes the BAR to var(--ink), not var(--accent), so .latest-title measures 17.79:1 and .latest-meta 5.23:1 (at opacity .6) against cream — both already clear. The morning read assumed the accent fill was the surface for every child of the hover state; it is only the surface for .latest-cta, which sets its own background. Lesson: resolve the PAINTED surface under real hover, never infer it from the parent's declarations.</t>
+          <t>PASS (closed live 2026-08-13) — was ISSUE/High (2026-08-13) — CORRECTED SCOPE, and the correction matters. The morning scrub read the declarations and reported FOUR failing hover rules. Re-measured under REAL pointer hover before fixing, only TWO are real: `.issue-latest:hover .latest-cta` (14.08px/700) and `.identity-hero .hero-link.primary:hover` (14.08px/700), both `color: var(--bg)` on a `background: var(--accent)` fill = 3.44:1 in dark against a 4.5:1 floor. The other two were FALSE POSITIVES: `.issue-latest:hover` takes the BAR to var(--ink), not var(--accent), so .latest-title measures 17.79:1 and .latest-meta 5.23:1 (at opacity .6) against cream — both already clear. The morning read assumed the accent fill was the surface for every child of the hover state; it is only the surface for .latest-cta, which sets its own background. Lesson: resolve the PAINTED surface under real hover, never infer it from the parent's declarations. | 2026-08-25 re-verified live: re-verified under REAL pointer hover on the live homepage in dark mode: .latest-cta 5.17:1, .latest-tag 5.17:1, .latest-title 17.79:1, .latest-meta (hover state) 5.23:1. No regression. Caveat carried to F87: the override lives in home-v2.css on the live deploy, so /brand/ still does not get it.</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.latest-meta` 3.36:1 dark / 2.93:1 light on the homepage, and 3.36:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
+          <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.latest-meta` 3.36:1 dark / 2.93:1 light on the homepage, and 3.36:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .latest-meta re-measured live 2026-08-25: 3.36:1 dark (homepage + /brand/), 2.93:1 light — unchanged from 2026-08-15. Root cause of the non-closure is NOT the fix: it is that the fix never shipped. origin/main is still b64a39b; the F85 commit (55a6d72) sits on LOCAL main, 8 commits ahead of origin, unpushed for 9 days.</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — `npm run build` clean, 19 pages. dist/css/*.css confirmed to carry the rules with zero opacity declarations. Post-fix values measured on the live DOM with the exact shipped declarations applied: dark 3.36:1 -&gt; 5.13:1, light 2.93:1 -&gt; 4.67:1. Both clear the 4.5:1 floor. Goes live-verified on the next scrub after Dexter merges.</t>
+          <t>PASS (build-verified 2026-08-15) — `npm run build` clean, 19 pages. dist/css/*.css confirmed to carry the rules with zero opacity declarations. Post-fix values measured on the live DOM with the exact shipped declarations applied: dark 3.36:1 -&gt; 5.13:1, light 2.93:1 -&gt; 4.67:1. Both clear the 4.5:1 floor. Goes live-verified on the next scrub after Dexter merges. | RETEST 2026-08-25 (build + live-DOM, both clean): fresh `npm run build` emits dist/css/home-augment.css:148-161 and dist/css/home-v2.css:107-118 with the opacity declaration absent and the explanatory comment intact. Then measured empirically rather than inferred — inserted the exact shipped state into the live home-v2.css CSSOM (insertRule, then deleteRule to restore): 3.36:1 -&gt; 5.13:1 on the homepage and 3.36:1 -&gt; 5.13:1 on /brand/. Matches the 2026-08-15 build-verified figure exactly. Fix holds; still not live.</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.hero-corner` 3.71:1 dark on the homepage, and 3.71:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
+          <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.hero-corner` 3.71:1 dark on the homepage, and 3.71:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .hero-corner re-measured live 2026-08-25: 3.71:1 dark. Unchanged — fix committed locally (55a6d72), never pushed.</t>
         </is>
       </c>
       <c r="I89" s="7" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — post-fix values measured on the live DOM with opacity .6 applied: dark 3.71:1 -&gt; 5.23:1, light 4.91:1 -&gt; 6.74:1. Both clear. dist confirmed to carry `opacity: .6` in both sheets.</t>
+          <t>PASS (build-verified 2026-08-15) — post-fix values measured on the live DOM with opacity .6 applied: dark 3.71:1 -&gt; 5.23:1, light 4.91:1 -&gt; 6.74:1. Both clear. dist confirmed to carry `opacity: .6` in both sheets. | RETEST 2026-08-25: dist carries `opacity: .6` in both sheets (home-augment.css:229, home-v2.css:860). Live-DOM CSSOM injection measured 3.71:1 -&gt; 5.23:1 on the homepage and on /brand/. Matches 2026-08-15. Fix holds; not live.</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: /brand/ `.latest-tag` 3.44:1 — and /brand/'s loaded-sheet list confirms the cause directly: tokens, shell, plates, home-augment, article, brand.css, with NO home-v2.css. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
+          <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: /brand/ `.latest-tag` 3.44:1 — and /brand/'s loaded-sheet list confirms the cause directly: tokens, shell, plates, home-augment, article, brand.css, with NO home-v2.css. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /brand/ re-measured live 2026-08-25: .latest-tag still 3.44:1 (the pre-F77 value), because live /brand/ serves home-augment.css?v=phase32 which does not yet carry the moved override blocks. The move (55a6d72) is committed locally and confirmed present in a fresh dist build; it has never been pushed.</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — grepped the built sheets: dist/css/home-augment.css carries both blocks at lines 127-134, dist/css/home-v2.css carries neither (only the breadcrumbs). Measured on the live /brand/ page in dark mode with the override applied: `.latest-tag` 3.44:1 -&gt; 5.17:1, the identical figure the homepage has been serving since deploy 791bfc5. Dogfood parity restored.</t>
+          <t>PASS (build-verified 2026-08-15) — grepped the built sheets: dist/css/home-augment.css carries both blocks at lines 127-134, dist/css/home-v2.css carries neither (only the breadcrumbs). Measured on the live /brand/ page in dark mode with the override applied: `.latest-tag` 3.44:1 -&gt; 5.17:1, the identical figure the homepage has been serving since deploy 791bfc5. Dogfood parity restored. | RETEST 2026-08-25: grepped the fresh build — dist/css/home-augment.css carries the dark-mode .latest-tag override (1 occurrence, lines 127-130); dist/css/home-v2.css carries none. Injecting that exact rule into the live /brand/ home-augment.css CSSOM took .latest-tag 3.44:1 -&gt; 5.17:1. Fix holds; not live.</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.next-meta` 2.81:1 dark on the /brand/ dogfood demo (still latent on the live homepage — no upcoming essay exists). Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
+          <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.next-meta` 2.81:1 dark on the /brand/ dogfood demo (still latent on the live homepage — no upcoming essay exists). Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .next-meta re-measured on the /brand/ demo of the strip 2026-08-25: still 2.81:1 dark. Unchanged — fix committed locally (55a6d72), never pushed. Still latent on the homepage itself: zero ghost:true flags remain in the collection and no upcoming entry exists, so IssueNext does not render.</t>
         </is>
       </c>
       <c r="I91" s="8" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — measured on the live /brand/ demo of the strip in dark mode with the fix applied: 2.81:1 -&gt; 5.13:1. Clears. (An earlier reading of 1.02:1 during this run was an artifact of forcing the dark-mode class onto an already-rendered light page, which left tokens half-resolved; discarded and re-measured after a clean reload with the dxmode cookie set. Recording it here so the number is not mistaken for a real regression if it resurfaces.)</t>
+          <t>PASS (build-verified 2026-08-15) — measured on the live /brand/ demo of the strip in dark mode with the fix applied: 2.81:1 -&gt; 5.13:1. Clears. (An earlier reading of 1.02:1 during this run was an artifact of forcing the dark-mode class onto an already-rendered light page, which left tokens half-resolved; discarded and re-measured after a clean reload with the dxmode cookie set. Recording it here so the number is not mistaken for a real regression if it resurfaces.) | RETEST 2026-08-25: dist/css/home-augment.css:728-740 and home-v2.css:206-216 both carry .next-meta with no opacity. Live /brand/ CSSOM injection: 2.81:1 -&gt; 5.13:1. Fix holds; not live.</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.notfound-eyebrow span.divider` 3.61:1 on /404. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy.</t>
+          <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.notfound-eyebrow span.divider` 3.61:1 on /404. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /404 span.divider re-measured live 2026-08-25: still 3.61:1 at opacity .5; live serves notfound.css?v=phase10 (the fix bumps it to phase11). Fix committed locally (8c1e6aa), never pushed.</t>
         </is>
       </c>
       <c r="I92" s="8" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — measured on the live /404 with opacity .7 applied: 3.61:1 -&gt; 7.19:1.</t>
+          <t>PASS (build-verified 2026-08-15) — measured on the live /404 with opacity .7 applied: 3.61:1 -&gt; 7.19:1. | RETEST 2026-08-25: dist/css/notfound.css:64-69 carries `opacity: .7` and dist/404.html references notfound.css?v=phase11. Live /404 CSSOM injection: 3.61:1 -&gt; 7.19:1. Matches 2026-08-15. Fix holds; not live.</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions.</t>
+          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions. | Re-confirmed live 2026-08-25, all five values unchanged: .demo-ghost-meta 2.05:1, .demo-ghost-date 2.45:1, .demo-ghost-title 2.93:1 (vs its 3:1 large-text floor), .demo-plate-meta 3.17:1, and the bespoke "Download Pack" h3 2.87:1 (#ff4d4d on the cream panel). Still BLOCKED — still the same two questions for Dexter, now open 10 days.</t>
         </is>
       </c>
       <c r="I93" s="9" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-16) — /phase0/'s skip link, the first focusable element on the page, computed `color: rgba(243,240,232,.82)` on its own `background: var(--ink)` cream chip: 1.00:1. This is the worst ratio the ledger has recorded and the only finding to date where the text is not merely low-contrast but literally invisible — a sighted keyboard user sees the accent focus ring land on a blank cream box. NOT a colour bug: `--bg` resolves correctly to #060606 at every level of the chain (verified by walking the ancestor chain: A.skip-link / BODY.phase0 / HTML.dark-mode all report #060606). It is a specificity bug. Three rules set colour on this element — `a {color:inherit}` (0,0,1) in tokens.css, `.skip-link {color:var(--bg)}` (0,1,0) in shell.css, and `.phase0 a {color:inherit}` (0,1,1) in phase0.css. The last wins on specificity and hands the chip back the inherited body cream. Scope is exactly one page: /brand/, the other bespoke-CSS surface, carries no blanket `a` rule and measured clean. Missed by every prior run because the skip link sits at left:-999px in its resting state, so a sweep that filters to on-screen elements never measures it — this run caught it by measuring every element with layout geometry regardless of viewport position.</t>
+          <t>ISSUE/High (2026-08-16) — /phase0/'s skip link, the first focusable element on the page, computed `color: rgba(243,240,232,.82)` on its own `background: var(--ink)` cream chip: 1.00:1. This is the worst ratio the ledger has recorded and the only finding to date where the text is not merely low-contrast but literally invisible — a sighted keyboard user sees the accent focus ring land on a blank cream box. NOT a colour bug: `--bg` resolves correctly to #060606 at every level of the chain (verified by walking the ancestor chain: A.skip-link / BODY.phase0 / HTML.dark-mode all report #060606). It is a specificity bug. Three rules set colour on this element — `a {color:inherit}` (0,0,1) in tokens.css, `.skip-link {color:var(--bg)}` (0,1,0) in shell.css, and `.phase0 a {color:inherit}` (0,1,1) in phase0.css. The last wins on specificity and hands the chip back the inherited body cream. Scope is exactly one page: /brand/, the other bespoke-CSS surface, carries no blanket `a` rule and measured clean. Missed by every prior run because the skip link sits at left:-999px in its resting state, so a sweep that filters to on-screen elements never measures it — this run caught it by measuring every element with layout geometry regardless of viewport position. | /phase0/ skip link re-measured live 2026-08-25: still rgba(243,240,232,.82) on its own cream chip = 1.00:1, the worst ratio in the ledger and still literally invisible to a sighted keyboard user. Live serves shell.css?v=phase23; the hardened selector ships as phase36. Fix committed locally (79df261), never pushed.</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-16) — `npm run build` clean, 19 pages; dist/css/shell.css carries the hardened selector and all 21 built pages reference shell.css?v=phase36. Cascade verified empirically rather than by reasoning alone: inserted the exact committed selector into the live shell.css CSSOM (CSP blocks &lt;style&gt; injection but not CSSOM mutation of an already-loaded same-origin sheet) and re-measured — /phase0/ 1.00:1 -&gt; 17.79:1, with the colour flipping to the intended rgb(6,6,6) on cream. Regression-checked on the two surfaces most likely to be disturbed: homepage and /brand/ both no-op (already rgb(6,6,6) on cream before and after). Goes live-verified on the next SCRUB after Dexter merges.</t>
+          <t>PASS (build-verified 2026-08-16) — `npm run build` clean, 19 pages; dist/css/shell.css carries the hardened selector and all 21 built pages reference shell.css?v=phase36. Cascade verified empirically rather than by reasoning alone: inserted the exact committed selector into the live shell.css CSSOM (CSP blocks &lt;style&gt; injection but not CSSOM mutation of an already-loaded same-origin sheet) and re-measured — /phase0/ 1.00:1 -&gt; 17.79:1, with the colour flipping to the intended rgb(6,6,6) on cream. Regression-checked on the two surfaces most likely to be disturbed: homepage and /brand/ both no-op (already rgb(6,6,6) on cream before and after). Goes live-verified on the next SCRUB after Dexter merges. | RETEST 2026-08-25: dist/css/shell.css:19-29 carries `.skip-link, .skip-link:link, .skip-link:visited` and all built pages reference shell.css?v=phase36. Live /phase0/ CSSOM injection of that selector: 1.00:1 -&gt; 17.79:1, with the chip resolving to #060606 on cream. Fix holds; not live.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -48,12 +48,12 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
@@ -97,12 +97,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0625B"/>
+        <fgColor rgb="00F0C24B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0C24B"/>
+        <fgColor rgb="00E0625B"/>
       </patternFill>
     </fill>
     <fill>
@@ -171,7 +171,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,9 +179,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -675,7 +675,7 @@
       </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
-          <t>PASS — masthead .brand-block → '/' present on home/about/404/phase0/brand/article; aria-label 'Dexter Jakes home' | 2026-08-15 re-verified live: brand-block present and linking / on all 20 pages | 2026-08-25 re-verified live: brand-block present and linking / on all 20 crawled routes; aria-label intact.</t>
+          <t>PASS — masthead .brand-block → '/' present on home/about/404/phase0/brand/article; aria-label 'Dexter Jakes home' | 2026-08-15 re-verified live: brand-block present and linking / on all 20 pages | 2026-08-25 re-verified live: brand-block present and linking / on all 20 crawled routes; aria-label intact. | 2026-08-27 re-verified live: masthead .brand-block → '/' confirmed under real Tab focus.</t>
         </is>
       </c>
       <c r="I4" s="6" t="inlineStr"/>
@@ -724,7 +724,7 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>PASS — brand-word: Words (home/article/about/brand), 404, Phase 0 — matches documented intent | 2026-08-15 re-verified live: brand-word: home/about/article 'Words', 404 '404', phase0 'Phase 0' — matches the documented about-page quirk | 2026-08-25 re-verified live: brand-word: "Words" on home/about/article, "404" on /404, "Phase 0" on /phase0/ — matches documented intent.</t>
+          <t>PASS — brand-word: Words (home/article/about/brand), 404, Phase 0 — matches documented intent | 2026-08-15 re-verified live: brand-word: home/about/article 'Words', 404 '404', phase0 'Phase 0' — matches the documented about-page quirk | 2026-08-25 re-verified live: brand-word: "Words" on home/about/article, "404" on /404, "Phase 0" on /phase0/ — matches documented intent. | 2026-08-27 re-verified live: brand word 'Words' confirmed on home/article/about.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks. | 2026-08-13 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways; --bg/--ink/--accent-text all re-resolved (#060606/#f3f0e8/#ff4d4d dark, #f4f4f1/#050505/#c00 light). | 2026-08-16 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways (dxmode=light then dxmode=dark); --bg #060606&lt;-&gt;#f4f4f1 and --ink #f3f0e8&lt;-&gt;#050505 both re-resolved; label and aria-pressed tracked ('Mode: Dark'/true &lt;-&gt; 'Mode: Light'/false). | 2026-08-25 re-verified live: toggle re-verified with a REAL pointer click (not element.click()) on both the homepage and /words/the-stone/: page repaints dark&lt;-&gt;light, dxmode cookie written both ways, label and aria-pressed track. METHOD NOTE: a programmatic element.click() flips the class, the tokens and the cookie but leaves body's used background/color stale in getComputedStyle until a repaint is forced — that is a measurement artifact, NOT a site defect, and it read as an article-page mode regression for several minutes this run. Always verify this row with a real click.</t>
+          <t>PASS — toggle cycles dark→light→dark; dxmode cookie written both ways; label + aria-pressed + bg/ink all update. Reconfirmed 2026-08-10 PM across 3 consecutive clicks. | 2026-08-13 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways; --bg/--ink/--accent-text all re-resolved (#060606/#f3f0e8/#ff4d4d dark, #f4f4f1/#050505/#c00 light). | 2026-08-16 re-verified live: toggle cycled dark-&gt;light-&gt;dark on the live homepage; dxmode cookie written both ways (dxmode=light then dxmode=dark); --bg #060606&lt;-&gt;#f4f4f1 and --ink #f3f0e8&lt;-&gt;#050505 both re-resolved; label and aria-pressed tracked ('Mode: Dark'/true &lt;-&gt; 'Mode: Light'/false). | 2026-08-25 re-verified live: toggle re-verified with a REAL pointer click (not element.click()) on both the homepage and /words/the-stone/: page repaints dark&lt;-&gt;light, dxmode cookie written both ways, label and aria-pressed track. METHOD NOTE: a programmatic element.click() flips the class, the tokens and the cookie but leaves body's used background/color stale in getComputedStyle until a repaint is forced — that is a measurement artifact, NOT a site defect, and it read as an article-page mode regression for several minutes this run. Always verify this row with a real click. | 2026-08-27 re-verified live: REAL pointer click (not element.click()) + 2s settle + screenshot: dark→light→dark, --bg #060606↔#f4f4f1, --ink #f3f0e8↔#050505, dxmode cookie written both ways, button label tracks.</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr"/>
@@ -826,7 +826,7 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production. | 2026-08-13 re-verified live: tab-target verified on live: .skip-link reveals from left:-999px to a 83x69 box at (12,12), cream-on-ink 17.79:1; activating it moved document.activeElement to MAIN#archive (tabindex=-1). Article pages target #article. | 2026-08-16 re-verified live: structural half re-verified live: .skip-link is the first focusable element in document order on every page type, and its target (MAIN#article / MAIN#archive / MAIN#phase0 / MAIN#main) carries tabindex=-1. End-to-end activation NOT re-exercisable this run — the browser pane reports document.visibilityState 'hidden' and drops page focus on every reload, so a fresh-load Tab lands on BODY. Harness limitation, not a site regression; last live activation was 2026-08-13. NOTE: this row's sweep is what surfaced F91 — see that row. | 2026-08-25 re-verified live: verified end-to-end live under REAL keyboard input on /words/the-stone/ — the gap the 2026-08-16 run had to leave open. .skip-link is the first focusable in DOM order, reveals from left:-999px to a 126x46 chip at (12,12), computes 17.79:1 (#060606 on #f3f0e8), and pressing Enter sets location.hash to #article and moves document.activeElement to MAIN#article (tabindex=-1).</t>
+          <t>PASS — live-verified 2026-08-10: skip link is first focusable; activating it lands document.activeElement on MAIN#archive (home) / MAIN#article (essay); tabindex=-1 present on both landmarks. The 2c7d88d fix holds in production. | 2026-08-13 re-verified live: tab-target verified on live: .skip-link reveals from left:-999px to a 83x69 box at (12,12), cream-on-ink 17.79:1; activating it moved document.activeElement to MAIN#archive (tabindex=-1). Article pages target #article. | 2026-08-16 re-verified live: structural half re-verified live: .skip-link is the first focusable element in document order on every page type, and its target (MAIN#article / MAIN#archive / MAIN#phase0 / MAIN#main) carries tabindex=-1. End-to-end activation NOT re-exercisable this run — the browser pane reports document.visibilityState 'hidden' and drops page focus on every reload, so a fresh-load Tab lands on BODY. Harness limitation, not a site regression; last live activation was 2026-08-13. NOTE: this row's sweep is what surfaced F91 — see that row. | 2026-08-25 re-verified live: verified end-to-end live under REAL keyboard input on /words/the-stone/ — the gap the 2026-08-16 run had to leave open. .skip-link is the first focusable in DOM order, reveals from left:-999px to a 126x46 chip at (12,12), computes 17.79:1 (#060606 on #f3f0e8), and pressing Enter sets location.hash to #article and moves document.activeElement to MAIN#article (tabindex=-1). | 2026-08-27 re-verified live: skip link is the first focusable (reached by real shift+Tab from .brand-block), renders as an opaque cream chip at 17.79:1, and activation moves focus to MAIN#archive with hash #archive.</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path | 2026-08-15 re-verified live: favicon-32.png + apple-touch-icon.png linked on every page; both 200 (1327b / 5729b) | 2026-08-25 re-verified live: /img/favicon-32.png 200, /img/apple-touch-icon.png 200 on every referenced path.</t>
+          <t>PASS — /img/favicon-32.png + /img/apple-touch-icon.png 200 on every referenced path | 2026-08-15 re-verified live: favicon-32.png + apple-touch-icon.png linked on every page; both 200 (1327b / 5729b) | 2026-08-25 re-verified live: /img/favicon-32.png 200, /img/apple-touch-icon.png 200 on every referenced path. | 2026-08-27 re-verified live: /img/favicon-32.png + /img/apple-touch-icon.png 200.</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-15 re-verified live: Anton + IBM Plex Sans preloaded with crossorigin; zero Google Fonts refs; document.fonts reports all 3 faces loaded | 2026-08-16 re-verified live: Anton + IBM Plex Sans (Regular/Bold) all report document.fonts status 'loaded', document.fonts.status 'loaded'; zero Google Fonts references. /brand/ additionally preloads IBMPlexSans-Italic.woff2 and the console warns it is 'not used within a few seconds of load' — investigated and DISMISSED as a non-finding: the italic face is genuinely used by 13 elements on that page and reports status 'loaded'; the warning is a below-the-fold timing artifact. No other page preloads italic, which is correct. | 2026-08-25 re-verified live: document.fonts.status "loaded"; Anton/400, IBM Plex Sans/400 and /700 all report loaded. All three woff2 200. No FOUT observed.</t>
+          <t>PASS — Anton + IBM Plex Sans self-hosted, preloaded, document.fonts status 'loaded'; CSP font-src intact | 2026-08-15 re-verified live: Anton + IBM Plex Sans preloaded with crossorigin; zero Google Fonts refs; document.fonts reports all 3 faces loaded | 2026-08-16 re-verified live: Anton + IBM Plex Sans (Regular/Bold) all report document.fonts status 'loaded', document.fonts.status 'loaded'; zero Google Fonts references. /brand/ additionally preloads IBMPlexSans-Italic.woff2 and the console warns it is 'not used within a few seconds of load' — investigated and DISMISSED as a non-finding: the italic face is genuinely used by 13 elements on that page and reports status 'loaded'; the warning is a below-the-fold timing artifact. No other page preloads italic, which is correct. | 2026-08-25 re-verified live: document.fonts.status "loaded"; Anton/400, IBM Plex Sans/400 and /700 all report loaded. All three woff2 200. No FOUT observed. | 2026-08-27 re-verified live: document.fonts: Anton 400, IBM Plex Sans 400 + 700 all 'loaded'; fonts.status 'loaded'; no FOUT observed.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr"/>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com | 2026-08-15 re-verified live: zero duplicate &lt;title&gt; across 20 pages; /404 canonical is /404 as specified | 2026-08-25 re-verified live: &lt;title&gt;, meta description and canonical present and correct on all 20 routes; every canonical points at imjustdex.com.</t>
+          <t>PASS — title/description/canonical on all 21 routes; every canonical on imjustdex.com | 2026-08-15 re-verified live: zero duplicate &lt;title&gt; across 20 pages; /404 canonical is /404 as specified | 2026-08-25 re-verified live: &lt;title&gt;, meta description and canonical present and correct on all 20 routes; every canonical points at imjustdex.com. | 2026-08-27 re-verified live: title/description/canonical present and on-domain across all 21 routes.</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand) | 2026-08-15 re-verified live: twitter:card summary_large_image on every page in scope (404 correctly excluded) | 2026-08-25 re-verified live: og:title / og:description / og:image present on all 20; all 16 og-&lt;slug&gt;.png 200; og:image byte-identical to the JSON-LD image on all 16.</t>
+          <t>PASS — og+twitter complete on all 21; all 19 OG images 200 (16 essays + home/about/phase0/brand) | 2026-08-15 re-verified live: twitter:card summary_large_image on every page in scope (404 correctly excluded) | 2026-08-25 re-verified live: og:title / og:description / og:image present on all 20; all 16 og-&lt;slug&gt;.png 200; og:image byte-identical to the JSON-LD image on all 16. | 2026-08-27 re-verified live: og+twitter complete across 21 routes; all 21 distinct OG images 200.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr"/>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor) | 2026-08-15 re-verified live: home @graph carries WebSite + Person; Person has name/url/sameAs/jobTitle/worksFor — no missing fields | 2026-08-25 re-verified live: WebSite + Person @graph complete on /; Person carries name, url, sameAs, jobTitle, worksFor.</t>
+          <t>PASS — WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor) | 2026-08-15 re-verified live: home @graph carries WebSite + Person; Person has name/url/sameAs/jobTitle/worksFor — no missing fields | 2026-08-25 re-verified live: WebSite + Person @graph complete on /; Person carries name, url, sameAs, jobTitle, worksFor. | 2026-08-27 re-verified live: WebSite + Person @graph complete (name/url/sameAs/jobTitle/worksFor).</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description) | 2026-08-15 re-verified live: about ProfilePage mainEntity Person complete — name/url/jobTitle/worksFor/sameAs/description all present | 2026-08-25 re-verified live: ProfilePage on /about/ with mainEntity @type Person carrying name, url, jobTitle, worksFor, sameAs, description.</t>
+          <t>PASS — ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description) | 2026-08-15 re-verified live: about ProfilePage mainEntity Person complete — name/url/jobTitle/worksFor/sameAs/description all present | 2026-08-25 re-verified live: ProfilePage on /about/ with mainEntity @type Person carrying name, url, jobTitle, worksFor, sameAs, description. | 2026-08-27 re-verified live: ProfilePage mainEntity Person complete (name/url/jobTitle/worksFor/sameAs/description).</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr"/>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift | 2026-08-13 re-verified live: all 16 BlogPosting blocks carry every required field (headline, description, datePublished, dateModified, author.@type=Person + name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount); zero og-default.png drift. | 2026-08-16 re-verified live: all 16 BlogPosting blocks re-verified live: every required field present (headline, description, datePublished, dateModified, author.@type=Person, publisher, mainEntityOfPage, image, url, inLanguage, wordCount) and JSON-LD image === og:image exactly, cache-bust included, on all 16. Zero og-default.png drift. | 2026-08-25 re-verified live: BlogPosting on all 16 articles; every required field present (headline, description, datePublished, dateModified, author.Person.name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount). Zero og-default.png regressions.</t>
+          <t>PASS — BlogPosting complete on all 16 (headline, description, datePublished, dateModified, author Person, publisher Organization+logo, mainEntityOfPage, image, url, inLanguage, wordCount); image == og:image exactly, no og-default drift | 2026-08-13 re-verified live: all 16 BlogPosting blocks carry every required field (headline, description, datePublished, dateModified, author.@type=Person + name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount); zero og-default.png drift. | 2026-08-16 re-verified live: all 16 BlogPosting blocks re-verified live: every required field present (headline, description, datePublished, dateModified, author.@type=Person, publisher, mainEntityOfPage, image, url, inLanguage, wordCount) and JSON-LD image === og:image exactly, cache-bust included, on all 16. Zero og-default.png drift. | 2026-08-25 re-verified live: BlogPosting on all 16 articles; every required field present (headline, description, datePublished, dateModified, author.Person.name, publisher, mainEntityOfPage, image, url, inLanguage, wordCount). Zero og-default.png regressions. | 2026-08-27 re-verified live: BlogPosting complete on all 16 — all 11 required fields, author.@type=Person, og:image == JSON-LD image, image == og-&lt;slug&gt;.png on every one.</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr"/>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>PASS — phase0 WebPage JSON-LD present and parses</t>
+          <t>PASS — phase0 WebPage JSON-LD present and parses | 2026-08-27 re-verified live: phase0 WebPage + Person JSON-LD present and parse.</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>PASS — robots.txt Allow / + Sitemap → sitemap-index.xml | 2026-08-13 re-verified live: /robots.txt 200, Sitemap directive -&gt; https://imjustdex.com/sitemap-index.xml. | 2026-08-25 re-verified live: robots.txt = "User-agent: *\nAllow: /\n\nSitemap: https://imjustdex.com/sitemap-index.xml". /DESIGN-SYSTEM.md correctly 404s.</t>
+          <t>PASS — robots.txt Allow / + Sitemap → sitemap-index.xml | 2026-08-13 re-verified live: /robots.txt 200, Sitemap directive -&gt; https://imjustdex.com/sitemap-index.xml. | 2026-08-25 re-verified live: robots.txt = "User-agent: *\nAllow: /\n\nSitemap: https://imjustdex.com/sitemap-index.xml". /DESIGN-SYSTEM.md correctly 404s. | 2026-08-27 re-verified live: robots.txt Allow / + Sitemap → sitemap-index.xml.</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>PASS — sitemap-0.xml 20 locs = exactly the published set + about/brand/phase0; no missing, no orphans | 2026-08-13 re-verified live: /sitemap-index.xml -&gt; sitemap-0.xml; sitemap-0 lists 20 URLs covering all 16 articles + /, /about/, /brand/, /phase0/. Zero missing. | 2026-08-25 re-verified live: sitemap-index.xml references sitemap-0.xml; sitemap-0.xml carries exactly 20 locs = 16 articles + /, /about/, /brand/, /phase0/. The drafted essay is correctly absent.</t>
+          <t>PASS — sitemap-0.xml 20 locs = exactly the published set + about/brand/phase0; no missing, no orphans | 2026-08-13 re-verified live: /sitemap-index.xml -&gt; sitemap-0.xml; sitemap-0 lists 20 URLs covering all 16 articles + /, /about/, /brand/, /phase0/. Zero missing. | 2026-08-25 re-verified live: sitemap-index.xml references sitemap-0.xml; sitemap-0.xml carries exactly 20 locs = 16 articles + /, /about/, /brand/, /phase0/. The drafted essay is correctly absent. | 2026-08-27 re-verified live: sitemap-0.xml 20 locs; every homepage-linked route plus /about/ /brand/ /phase0/ present.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr"/>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>PASS — Entry No. 16 / Week of July 5, 2026, LatestBar → newest essay | 2026-08-13 re-verified live: LatestBar reads 'Entry No. 16 / Week of July 5, 2026' and links to /words/send-someone-else/ (the newest). NOTE: its .latest-tag chip is the F77 finding this run. | 2026-08-25 re-verified live: issue head renders "Entry No. 16" / "Week of July 5, 2026" from the lead; standfirst links /words/send-someone-else/.</t>
+          <t>PASS — Entry No. 16 / Week of July 5, 2026, LatestBar → newest essay | 2026-08-13 re-verified live: LatestBar reads 'Entry No. 16 / Week of July 5, 2026' and links to /words/send-someone-else/ (the newest). NOTE: its .latest-tag chip is the F77 finding this run. | 2026-08-25 re-verified live: issue head renders "Entry No. 16" / "Week of July 5, 2026" from the lead; standfirst links /words/send-someone-else/. | 2026-08-27 re-verified live: issue head 'Entry No. 16 / Week of July 5, 2026', LatestBar → send-someone-else.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr"/>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>PASS — IdentityHero renders; hero copy contrast 5.17:1 (AA large)</t>
+          <t>PASS — IdentityHero renders; hero copy contrast 5.17:1 (AA large) | 2026-08-27 re-verified live: IdentityHero renders (screenshot-confirmed in both modes).</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr"/>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>PASS — Faith 13 / Identity 09 / Art 03, verified against frontmatter lanes; 16 articles | 2026-08-13 re-verified live: lane-index counts Faith 13 / Identity 09 / Art 03 — non-negative, zero-padded, and consistent with 16 essays counted per lane (15 .plate-lane chips + 1 .lead-badge-lane). | 2026-08-25 re-verified live: lane counts render Faith 13 / Identity 09 / Art 03 — matches the frontmatter tally across the 16 tracked essays exactly (multi-lane counted per lane).</t>
+          <t>PASS — Faith 13 / Identity 09 / Art 03, verified against frontmatter lanes; 16 articles | 2026-08-13 re-verified live: lane-index counts Faith 13 / Identity 09 / Art 03 — non-negative, zero-padded, and consistent with 16 essays counted per lane (15 .plate-lane chips + 1 .lead-badge-lane). | 2026-08-25 re-verified live: lane counts render Faith 13 / Identity 09 / Art 03 — matches the frontmatter tally across the 16 tracked essays exactly (multi-lane counted per lane). | 2026-08-27 re-verified live: lane counts Faith 13 / Identity 09 / Art 03.</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: Faith 13/13, Identity 9/9, Art 3/3 with zero non-matching plates in any filtered view; while filtered the .earlier-more-wrap computes display:none, 0 client rects, offsetHeight 0 (unreachable by mouse or keyboard). The ab07b15 fix holds in production. | 2026-08-16 re-verified live: all three lanes re-verified live: Faith 13, Identity 9, Art 3 — exactly matching the lane-index counts. Verified against the real filter key (data-lane, space-separated) rather than the visible chips: all 9 identity plates carry 'identity' in data-lane. While filtered, .earlier-more-wrap computes display:none with 0 client rects; clearing restores display:flex.</t>
+          <t>PASS — live-verified 2026-08-10: Faith 13/13, Identity 9/9, Art 3/3 with zero non-matching plates in any filtered view; while filtered the .earlier-more-wrap computes display:none, 0 client rects, offsetHeight 0 (unreachable by mouse or keyboard). The ab07b15 fix holds in production. | 2026-08-16 re-verified live: all three lanes re-verified live: Faith 13, Identity 9, Art 3 — exactly matching the lane-index counts. Verified against the real filter key (data-lane, space-separated) rather than the visible chips: all 9 identity plates carry 'identity' in data-lane. While filtered, .earlier-more-wrap computes display:none with 0 client rects; clearing restores display:flex. | 2026-08-27 re-verified live: real pointer clicks: Faith 13, Identity 9, Art 3, re-click clears to the default 8; aria-pressed single-select correct.</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>PASS — lead plate = send-someone-else (newest published) | 2026-08-25 re-verified live: lead plate renders send-someone-else with correct eyebrow, deck and 16 min read.</t>
+          <t>PASS — lead plate = send-someone-else (newest published) | 2026-08-25 re-verified live: lead plate renders send-someone-else with correct eyebrow, deck and 16 min read. | 2026-08-27 re-verified live: lead plate = send-someone-else.</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>PASS — 'This Month' = show-me-your-glory (same month as lead)</t>
+          <t>PASS — 'This Month' = show-me-your-glory (same month as lead) | 2026-08-27 re-verified live: row heads 'This Week' (01, lead) and 'This Month' (02) both render as authored.</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr"/>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>PASS — 'Earlier' = 14, 6 visible + 8 overflow</t>
+          <t>PASS — 'Earlier' = 14, 6 visible + 8 overflow | 2026-08-27 re-verified live: 8 of 16 plates visible by default, 8 under the overflow.</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr"/>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: expand 8→16, collapse 16→8, aria-expanded false↔true and the button label track; collapse state survives a full filter cycle (clear restores the wrap to display:flex). | 2026-08-16 re-verified live: expand 8-&gt;16 and collapse 16-&gt;8 re-verified live; aria-expanded false&lt;-&gt;true and the label tracked ('View Earlier Essays — 8 more' &lt;-&gt; 'Show Less — showing all'); collapse state survived a full filter cycle.</t>
+          <t>PASS — live-verified 2026-08-10: expand 8→16, collapse 16→8, aria-expanded false↔true and the button label track; collapse state survives a full filter cycle (clear restores the wrap to display:flex). | 2026-08-16 re-verified live: expand 8-&gt;16 and collapse 16-&gt;8 re-verified live; aria-expanded false&lt;-&gt;true and the label tracked ('View Earlier Essays — 8 more' &lt;-&gt; 'Show Less — showing all'); collapse state survived a full filter cycle. | 2026-08-27 re-verified live: real pointer clicks: 8→16→8, aria-expanded false↔true, label and count track.</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>PASS — correctly absent: zero upcoming essays in the collection | 2026-08-25 re-verified live: correctly ABSENT — index.astro renders IssueNext only when an upcoming entry exists, and none does. Not a regression.</t>
+          <t>PASS — correctly absent: zero upcoming essays in the collection | 2026-08-25 re-verified live: correctly ABSENT — index.astro renders IssueNext only when an upcoming entry exists, and none does. Not a regression. | 2026-08-27 re-verified live: correctly absent — zero upcoming essays; .next-meta not in the DOM.</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>PASS — manifesto form action=/api/subscribe, source=home, honeypot present</t>
+          <t>PASS — manifesto form action=/api/subscribe, source=home, honeypot present | 2026-08-27 re-verified live: manifesto form + #sm-email + submit present on the homepage.</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr"/>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>PASS — eyebrow lanes/tags + ' + ' separator, date, read time, h1, deck</t>
+          <t>PASS — eyebrow lanes/tags + ' + ' separator, date, read time, h1, deck | 2026-08-27 re-verified live: eyebrow lanes/date/read-time render on all 16.</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>PASS — all 16 MDX bodies render through [...slug].astro</t>
+          <t>PASS — all 16 MDX bodies render through [...slug].astro | 2026-08-27 re-verified live: all 16 MDX bodies render.</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr"/>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>PASS — bar width 0→249→698→1153px and aria-valuenow 0→30→69→100 across the scroll range. 2026-08-10 PM re-check: structural half re-verified (progress.js math recomputed by hand at 50% scroll = 51.5%; .article-body + .reading-progress present; role/aria-label/aria-valuemin/max initialized on load). Runtime paint not re-exercisable this run — the browser pane reports document.visibilityState 'hidden', so requestAnimationFrame never fires and the CSS width transition stays frozen at 0. Harness limitation, not a site regression. | 2026-08-13 re-verified live: reading-progress present on articles at 3px, background var(--ink) rgb(5,5,5) — correct per F82; the doc bullet claiming --accent was struck 2026-08-10.</t>
+          <t>PASS — bar width 0→249→698→1153px and aria-valuenow 0→30→69→100 across the scroll range. 2026-08-10 PM re-check: structural half re-verified (progress.js math recomputed by hand at 50% scroll = 51.5%; .article-body + .reading-progress present; role/aria-label/aria-valuemin/max initialized on load). Runtime paint not re-exercisable this run — the browser pane reports document.visibilityState 'hidden', so requestAnimationFrame never fires and the CSS width transition stays frozen at 0. Harness limitation, not a site regression. | 2026-08-13 re-verified live: reading-progress present on articles at 3px, background var(--ink) rgb(5,5,5) — correct per F82; the doc bullet claiming --accent was struck 2026-08-10. | 2026-08-27 NOT re-verified — rotation gap, not a failure. The reading-progress bar is scroll-driven and the browser pane would not scroll this run (window.scrollTo, scrollingElement.scrollTop, Page_Down x6 and the pointer scroll action all left scrollY at 0-2 on an 11,937px article; the pointer scroll action timed out with 'Browser pane is currently hidden'). Source unchanged since the last PASS, so the row keeps its prior result rather than being reset.</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>PASS — pill text tracks sections ('What the Fear Was Actually About' → 'A New Thing' → 'The Thirtieth'), opacity animates in. 2026-08-10 PM re-check: section collection re-verified live (5 .section-head h2 landmarks found on /words/send-someone-else/; the 40%-viewport rule resolves to the correct current section). Opacity fade not observable this run — same hidden-tab rAF/transition suspension as F35.</t>
+          <t>PASS — pill text tracks sections ('What the Fear Was Actually About' → 'A New Thing' → 'The Thirtieth'), opacity animates in. 2026-08-10 PM re-check: section collection re-verified live (5 .section-head h2 landmarks found on /words/send-someone-else/; the 40%-viewport rule resolves to the correct current section). Opacity fade not observable this run — same hidden-tab rAF/transition suspension as F35. | 2026-08-27 NOT re-verified — rotation gap, not a failure. The section-indicator pill is scroll-driven and the browser pane would not scroll this run (window.scrollTo, scrollingElement.scrollTop, Page_Down x6 and the pointer scroll action all left scrollY at 0-2 on an 11,937px article; the pointer scroll action timed out with 'Browser pane is currently hidden'). Source unchanged since the last PASS, so the row keeps its prior result rather than being reset.</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr"/>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>PASS — X intent carries encoded url + title</t>
+          <t>PASS — X intent carries encoded url + title | 2026-08-27 re-verified live: X intent carries encoded url + title (checked on /about/).</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>PASS — copy button + [data-copy-status] live region on article and about</t>
+          <t>PASS — copy button + [data-copy-status] live region on article and about | 2026-08-27 re-verified live: copy button + [data-copy-status] aria-live=polite region present on article and about.</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr"/>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>PASS — Follow Me → instagram.com/ImJustDex</t>
+          <t>PASS — Follow Me → instagram.com/ImJustDex | 2026-08-27 re-verified live: Follow Me → instagram.com/ImJustDex, 200.</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr"/>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>PASS — PullQuote, Scripture, Callout, DropCap, Closing, SectionHead, ResearchCTA, StudyNote all render and are styled via external hashed CSS (CSP-clean)</t>
+          <t>PASS — PullQuote, Scripture, Callout, DropCap, Closing, SectionHead, ResearchCTA, StudyNote all render and are styled via external hashed CSS (CSP-clean) | 2026-08-27 re-verified live: PullQuote/Scripture/Callout/StudyNote all render (the-stone: 2 pull-quotes, 4 scripture, 2 callouts, 3 study notes).</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr"/>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>PASS — &lt;details&gt; summary toggles open→closed→open on both sampled essays</t>
+          <t>PASS — &lt;details&gt; summary toggles open→closed→open on both sampled essays | 2026-08-27 re-verified live: &lt;details&gt; summary toggles closed→open→closed on the-stone.</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>PASS — about content + ProfilePage render</t>
+          <t>PASS — about content + ProfilePage render | 2026-08-27 re-verified live: about content + ProfilePage render.</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr"/>
@@ -3074,7 +3074,7 @@
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>PASS — share bar X + copy + Follow Me with live region</t>
+          <t>PASS — share bar X + copy + Follow Me with live region | 2026-08-27 re-verified live: share bar X + copy + Follow Me + live region present on /about/.</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr"/>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>PASS — bespoke notfound-plate, 200 on /404, noindex+nofollow, /* fallback 404s unmatched routes</t>
+          <t>PASS — bespoke notfound-plate, 200 on /404, noindex+nofollow, /* fallback 404s unmatched routes | 2026-08-27 re-verified live: bespoke notfound-plate, 200 on /404, noindex+nofollow, single h1.</t>
         </is>
       </c>
       <c r="I52" s="6" t="inlineStr"/>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid | 2026-08-13 re-verified live: /feed.xml 200, Atom namespace, 16 &lt;entry&gt; elements — exactly matching the 16 articles on the homepage, zero set difference either direction. | 2026-08-16 re-verified live: /feed.xml 200 with 16 &lt;entry&gt; elements; set-compared against the 16 article links on the live homepage — zero difference in either direction. | 2026-08-25 re-verified live: /feed.xml 200, 16 &lt;entry&gt; elements matching the 16 published articles exactly — no gaps, no extras.</t>
+          <t>PASS — Atom 16 entries = 16 published; namespace + entries valid | 2026-08-13 re-verified live: /feed.xml 200, Atom namespace, 16 &lt;entry&gt; elements — exactly matching the 16 articles on the homepage, zero set difference either direction. | 2026-08-16 re-verified live: /feed.xml 200 with 16 &lt;entry&gt; elements; set-compared against the 16 article links on the live homepage — zero difference in either direction. | 2026-08-25 re-verified live: /feed.xml 200, 16 &lt;entry&gt; elements matching the 16 published articles exactly — no gaps, no extras. | 2026-08-27 re-verified live: Atom 16 entries == 16 published on the homepage.</t>
         </is>
       </c>
       <c r="I53" s="6" t="inlineStr"/>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>PASS — feed.xsl 200 and &lt;?xml-stylesheet?&gt; PI present | 2026-08-13 re-verified live: /feed.xsl 200 and referenced via &lt;?xml-stylesheet?&gt; in the feed prolog. | 2026-08-25 re-verified live: /feed.xsl 200 and feed.xml carries &lt;?xml-stylesheet href="/feed.xsl"?&gt;.</t>
+          <t>PASS — feed.xsl 200 and &lt;?xml-stylesheet?&gt; PI present | 2026-08-13 re-verified live: /feed.xsl 200 and referenced via &lt;?xml-stylesheet?&gt; in the feed prolog. | 2026-08-25 re-verified live: /feed.xsl 200 and feed.xml carries &lt;?xml-stylesheet href="/feed.xsl"?&gt;. | 2026-08-27 re-verified live: feed.xsl 200 and the &lt;?xml-stylesheet?&gt; PI is present.</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr"/>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>PASS — 5 anchor links, all resolve to real targets</t>
+          <t>PASS — 5 anchor links, all resolve to real targets | 2026-08-27 re-verified live: 5 anchor links on /phase0/, all resolve to real targets.</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr"/>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: /phase0/ form action is /api/subscribe with no legacy Mailchimp query string; matches the other three subscribe surfaces.</t>
+          <t>PASS — live-verified 2026-08-10: /phase0/ form action is /api/subscribe with no legacy Mailchimp query string; matches the other three subscribe surfaces. | 2026-08-27 re-verified live: /phase0/ form action=/api/subscribe, honeypot present, source=phase0.</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr"/>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="H57" s="6" t="inlineStr">
         <is>
-          <t>PASS — footer year 2026 = current year</t>
+          <t>PASS — footer year 2026 = current year | 2026-08-27 re-verified live: phase0 footer year 2026.</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>PASS — GET /api/subscribe → 405 method_not_allowed | 2026-08-25 re-verified live: /api/subscribe reachable and behaving; rewrite chain intact.</t>
+          <t>PASS — GET /api/subscribe → 405 method_not_allowed | 2026-08-25 re-verified live: /api/subscribe reachable and behaving; rewrite chain intact. | 2026-08-27 re-verified live: GET /api/subscribe → 405 method_not_allowed.</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr"/>
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>PASS — filled honeypot → 200 silent success, no Mailchimp write; field off-canvas (left:-5000px, tabindex -1, aria-hidden) | 2026-08-25 re-verified live: honeypot re-verified live: POST with website=spam returned HTTP 200 {"ok":true,"message":"subscribed"} — the intended silent drop, indistinguishable from success to a bot.</t>
+          <t>PASS — filled honeypot → 200 silent success, no Mailchimp write; field off-canvas (left:-5000px, tabindex -1, aria-hidden) | 2026-08-25 re-verified live: honeypot re-verified live: POST with website=spam returned HTTP 200 {"ok":true,"message":"subscribed"} — the intended silent drop, indistinguishable from success to a bot. | 2026-08-27 re-verified live: filled honeypot → 200 silent success.</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr"/>
@@ -3657,7 +3657,7 @@
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>PASS — invalid address → 400 invalid_email; plus-addressed valid address accepted (clients encode + as %2B via URLSearchParams(FormData)) | 2026-08-25 re-verified live: email validation re-verified live: POST email=notanemail returned HTTP 400 {"ok":false,"error":"invalid_email"}.</t>
+          <t>PASS — invalid address → 400 invalid_email; plus-addressed valid address accepted (clients encode + as %2B via URLSearchParams(FormData)) | 2026-08-25 re-verified live: email validation re-verified live: POST email=notanemail returned HTTP 400 {"ok":false,"error":"invalid_email"}. | 2026-08-27 re-verified live: invalid address → 400 invalid_email.</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr"/>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s | 2026-08-13 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.16s using healthscrub+20260813@imjustdex.com. | 2026-08-16 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.05s using healthscrub+20260816@imjustdex.com. | 2026-08-25 re-verified live: smoke POST with healthscrub+20260825@imjustdex.com returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.20s.</t>
+          <t>PASS — healthscrub+20260807@imjustdex.com → 200 subscribed in 1.53s | 2026-08-13 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.16s using healthscrub+20260813@imjustdex.com. | 2026-08-16 re-verified live: live smoke test POST /api/subscribe returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.05s using healthscrub+20260816@imjustdex.com. | 2026-08-25 re-verified live: smoke POST with healthscrub+20260825@imjustdex.com returned HTTP 200 {"ok":true,"message":"subscribed"} in 2.20s. | 2026-08-27 re-verified live: healthscrub+20260827@imjustdex.com → 200 subscribed.</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical | 2026-08-13 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200; /sitemap.xml correctly 404 post-cutover. | 2026-08-16 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200 and /words/the-stone -&gt; 301 -&gt; /words/the-stone/ re-verified live; /sitemap.xml correctly 404 post-cutover; /words -&gt; 301 home; /opsmeeting -&gt; 301 home. | 2026-08-25 re-verified live: /about, /brand, /phase0 and /words/the-stone each return a single 301 to the trailing-slash form, which returns 200. No loops.</t>
+          <t>PASS — /about, /phase0 and all 16 /words/&lt;slug&gt; → single 301 to trailing-slash canonical | 2026-08-13 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200; /sitemap.xml correctly 404 post-cutover. | 2026-08-16 re-verified live: /about -&gt; 301 -&gt; /about/ -&gt; 200 and /words/the-stone -&gt; 301 -&gt; /words/the-stone/ re-verified live; /sitemap.xml correctly 404 post-cutover; /words -&gt; 301 home; /opsmeeting -&gt; 301 home. | 2026-08-25 re-verified live: /about, /brand, /phase0 and /words/the-stone each return a single 301 to the trailing-slash form, which returns 200. No loops. | 2026-08-27 re-verified live: /about and /words/the-stone → single 301 to the trailing-slash canonical.</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr"/>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>PASS — /words and /words/ → 301 home</t>
+          <t>PASS — /words and /words/ → 301 home | 2026-08-27 re-verified live: /words → 301 home.</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr"/>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>PASS — /opsmeeting, /leadership-prep, /asana-workflow (+ /*) all → 301 home</t>
+          <t>PASS — /opsmeeting, /leadership-prep, /asana-workflow (+ /*) all → 301 home | 2026-08-27 re-verified live: /opsmeeting → 301 home.</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr"/>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>PASS — /api/subscribe rewrite reaches the function (405 on GET, 400/200 on POST) | 2026-08-13 re-verified live: /api/subscribe rewrite reached the Netlify function and returned a Mailchimp success body. | 2026-08-25 re-verified live: /api/subscribe rewrite to the Netlify function verified by the live smoke POST.</t>
+          <t>PASS — /api/subscribe rewrite reaches the function (405 on GET, 400/200 on POST) | 2026-08-13 re-verified live: /api/subscribe rewrite reached the Netlify function and returned a Mailchimp success body. | 2026-08-25 re-verified live: /api/subscribe rewrite to the Netlify function verified by the live smoke POST. | 2026-08-27 re-verified live: /api/subscribe rewrite reaches the function.</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr"/>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>PASS — unmatched route → 404 with the branded body | 2026-08-13 re-verified live: /404 returns 200 with the bespoke 'Nothing to Document Here' body and noindex; /DESIGN-SYSTEM.md and /audit/features.json both 404 (docs not leaking). | 2026-08-25 re-verified live: /404 returns HTTP 200 with the bespoke notfound-plate body and meta robots noindex.</t>
+          <t>PASS — unmatched route → 404 with the branded body | 2026-08-13 re-verified live: /404 returns 200 with the bespoke 'Nothing to Document Here' body and noindex; /DESIGN-SYSTEM.md and /audit/features.json both 404 (docs not leaking). | 2026-08-25 re-verified live: /404 returns HTTP 200 with the bespoke notfound-plate body and meta robots noindex. | 2026-08-27 re-verified live: unmatched route → 404 with the branded body.</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr"/>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML | 2026-08-13 re-verified live: CSP header present and ENFORCING — a runtime &lt;style&gt; injection was blocked by style-src 'self' during F77 verification, which is direct proof the policy is live, not just declared. Per-route /brand/ and /feed.xml relaxations by design. | 2026-08-16 re-verified live: CSP present and strict on every page type; /brand/ and /feed.xml keep their by-design style-src 'unsafe-inline' relaxation. Zero inline &lt;style&gt; blocks in any built Astro page (home 0, article 0, about 0, phase0 0). Policy proven live again this run — a &lt;style&gt; injection was blocked, while CSSOM mutation of the already-loaded sheet succeeded, which is the documented distinction. | 2026-08-25 re-verified live: CSP present on every route and empirically ENFORCED — an injected inline &lt;style&gt; during this run was blocked by style-src 'self' and logged as the only console error of the whole scrub. Per-route relaxation for /brand/ (style-src adds 'unsafe-inline') confirmed by design. Zero inline &lt;style&gt; blocks in any built page.</t>
+          <t>PASS — CSP present and strict on every page; per-route /brand/ + /feed.xml overrides intact; 0 inline &lt;style&gt; in built Astro HTML | 2026-08-13 re-verified live: CSP header present and ENFORCING — a runtime &lt;style&gt; injection was blocked by style-src 'self' during F77 verification, which is direct proof the policy is live, not just declared. Per-route /brand/ and /feed.xml relaxations by design. | 2026-08-16 re-verified live: CSP present and strict on every page type; /brand/ and /feed.xml keep their by-design style-src 'unsafe-inline' relaxation. Zero inline &lt;style&gt; blocks in any built Astro page (home 0, article 0, about 0, phase0 0). Policy proven live again this run — a &lt;style&gt; injection was blocked, while CSSOM mutation of the already-loaded sheet succeeded, which is the documented distinction. | 2026-08-25 re-verified live: CSP present on every route and empirically ENFORCED — an injected inline &lt;style&gt; during this run was blocked by style-src 'self' and logged as the only console error of the whole scrub. Per-route relaxation for /brand/ (style-src adds 'unsafe-inline') confirmed by design. Zero inline &lt;style&gt; blocks in any built page. | 2026-08-27 re-verified live: CSP present and strict on / and on an article.</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr"/>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes | 2026-08-13 re-verified live: all 5 security headers present on all 6 page types (home, article, about, brand, phase0, 404, feed): X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present. | 2026-08-16 re-verified live: all security headers re-verified live on home/article/brand/404/feed: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy, COOP same-origin, CORP same-origin. | 2026-08-25 re-verified live: all five headers present on / and on an article: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000; includeSubDomains; preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present on /.</t>
+          <t>PASS — X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy, Permissions-Policy, COOP, CORP on all 21 routes | 2026-08-13 re-verified live: all 5 security headers present on all 6 page types (home, article, about, brand, phase0, 404, feed): X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present. | 2026-08-16 re-verified live: all security headers re-verified live on home/article/brand/404/feed: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000 includeSubDomains preload, CSP, Referrer-Policy strict-origin-when-cross-origin, Permissions-Policy, COOP same-origin, CORP same-origin. | 2026-08-25 re-verified live: all five headers present on / and on an article: X-Frame-Options DENY, X-Content-Type-Options nosniff, HSTS max-age=31536000; includeSubDomains; preload, CSP, Referrer-Policy strict-origin-when-cross-origin. Permissions-Policy also present on /. | 2026-08-27 re-verified live: X-Frame DENY, nosniff, HSTS max-age=31536000 includeSubDomains preload, Referrer-Policy all present.</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr"/>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate. | 2026-08-13 re-verified live: versioned assets (/css, /js, /img) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-16 re-verified live: versioned assets (/css, /js, /img, /fonts) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-25 re-verified live: versioned CSS, fonts and images all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift on either tier.</t>
+          <t>PASS — live-verified 2026-08-10: /brand/brand.css?v=brand5 and /img/* both return public,max-age=31536000,immutable; HTML remains public,max-age=0,must-revalidate. | 2026-08-13 re-verified live: versioned assets (/css, /js, /img) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-16 re-verified live: versioned assets (/css, /js, /img, /fonts) all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift. | 2026-08-25 re-verified live: versioned CSS, fonts and images all serve public,max-age=31536000,immutable; HTML serves public,max-age=0,must-revalidate. No drift on either tier. | 2026-08-27 re-verified live: HTML no-cache/must-revalidate; /css/*?v= and /img/* both public,max-age=31536000,immutable.</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr"/>
@@ -4399,18 +4399,22 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>PASS — daily-rebuild.yml fired 06:13Z today; Netlify commit_ref == GitHub main HEAD (8f5ba93)</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr"/>
+          <t>ISSUE/Medium (2026-08-27) — the scheduled run did not fire today. GitHub Actions shows 'Daily rebuild' completing every day 2026-08-19 through 2026-08-26 at 05:35-05:47Z; there is no run for 2026-08-27, checked at 14:06Z — 9h past the 05:05 UTC cron. Workflow state is 'active' and the YAML is unchanged and valid, so this is GitHub dropping/delaying the schedule, not a repo defect. Netlify's newest ready deploy is 2026-08-26T05:43Z (commit_ref b64a39b == GitHub main HEAD). Live impact today: none — zero date-gated essays are pending (F30 correctly absent), so the rebuild would have produced byte-identical output. It matters the day an essay is scheduled.</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>NOTE: workflow YAML valid; cron not runnable locally</t>
-        </is>
-      </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>BLOCKED — outside the repo. Nothing in daily-rebuild.yml is wrong; the cron simply did not run on GitHub's side. Options for Dexter, none auto-appliable: (a) do nothing, GitHub schedules are best-effort and this is the first miss in 8+ days; (b) fire it manually when a scheduled essay is due (`gh workflow run 'Daily rebuild'`); (c) move the trigger off GitHub cron to a Netlify scheduled function if publish-day reliability ever has to be guaranteed.</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>PENDING — re-check on the next run whether the 2026-08-28 cron fires.</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4456,7 @@
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>PASS — scripts/og-plate.mjs present; all 19 OG plates render and 200</t>
+          <t>PASS — scripts/og-plate.mjs present; all 19 OG plates render and 200 | 2026-08-27 re-verified live: all 21 OG plates 200.</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr"/>
@@ -4505,7 +4509,7 @@
       </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page) | 2026-08-13 re-verified live: verified in the DEPLOYED sheet, not just source: tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, *::before, *::after with !important, plus scroll-behavior auto. Catches all 29 transitioned elements on the homepage. | 2026-08-16 re-verified live: re-verified in the LOADED CSSOM (not source): tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, ::before, ::after with !important plus scroll-behavior auto — catching all 8 transitioned elements on the article page. | 2026-08-25 re-verified live: tokens.css:584 zeroes transition-duration and animation-duration on *, ::before and ::after under prefers-reduced-motion: reduce and sets scroll-behavior auto; home-augment.css:1012 adds the targeted transition:none block. Both present in the served sheets.</t>
+          <t>PASS — @media (prefers-reduced-motion: reduce) block in tokens.css (loads on every page) | 2026-08-13 re-verified live: verified in the DEPLOYED sheet, not just source: tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, *::before, *::after with !important, plus scroll-behavior auto. Catches all 29 transitioned elements on the homepage. | 2026-08-16 re-verified live: re-verified in the LOADED CSSOM (not source): tokens.css?v=phase23 carries @media (prefers-reduced-motion: reduce) zeroing transition-duration and animation-duration on *, ::before, ::after with !important plus scroll-behavior auto — catching all 8 transitioned elements on the article page. | 2026-08-25 re-verified live: tokens.css:584 zeroes transition-duration and animation-duration on *, ::before and ::after under prefers-reduced-motion: reduce and sets scroll-behavior auto; home-augment.css:1012 adds the targeted transition:none block. Both present in the served sheets. | 2026-08-27 re-verified live: @media (prefers-reduced-motion: reduce) block present in the loaded stylesheets.</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr"/>
@@ -4558,7 +4562,7 @@
       </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4. | 2026-08-13 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to a footer link that matched ':focus-visible' and computed outline 'solid 2px rgb(204, 0, 0)' at offset 2px. | 2026-08-16 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to SUMMARY.study-note-trigger, which matched ':focus-visible' and computed outline 'rgb(204, 0, 0) solid 2px' at offset -2px. | 2026-08-25 re-verified live: re-verified under REAL keyboard input: tabbing to .study-note-trigger on an article paints outline solid 2px rgb(204,0,0) (--focus-ring) at -2px offset. NOTE for future runs: a programmatic element.focus() does NOT satisfy :focus-visible in Chrome and will report outline:none across the board — a false positive this run initially produced.</t>
+          <t>PASS (closed live 2026-08-10) — was ISSUE/High: .subscribe-manifesto .sm-submit (homepage + /brand/ subscribe submit) had base and :hover styling but NO :focus-visible rule, so the site's primary conversion control showed no focus indicator for keyboard users (WCAG 2.4.7 AA). Every sibling control was covered — .sm-input directly above it had the rule, and .sm-submit was even named in home-augment.css's prefers-reduced-motion block — so it was an omission, not a decision. Missed by prior runs because F76 was tested at sheet level (':focus-visible present in all 8 stylesheets') rather than per control. Fixed and deployed same day; see p3/p4. | 2026-08-13 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to a footer link that matched ':focus-visible' and computed outline 'solid 2px rgb(204, 0, 0)' at offset 2px. | 2026-08-16 re-verified live: re-verified live by REAL keyboard input (not JS .focus(), which cannot trigger :focus-visible): pressing Tab moved focus to SUMMARY.study-note-trigger, which matched ':focus-visible' and computed outline 'rgb(204, 0, 0) solid 2px' at offset -2px. | 2026-08-25 re-verified live: re-verified under REAL keyboard input: tabbing to .study-note-trigger on an article paints outline solid 2px rgb(204,0,0) (--focus-ring) at -2px offset. NOTE for future runs: a programmatic element.focus() does NOT satisfy :focus-visible in Chrome and will report outline:none across the board — a false positive this run initially produced. | 2026-08-27 re-verified live: focus ring under REAL Tab (not element.focus()): outline rgb(204,0,0) solid 2px = --accent.</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -4672,7 +4676,7 @@
       </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt | 2026-08-13 re-verified live: home and article both single-h1, zero skipped heading levels (home H1 then 17x H2; article H1,H2,H2,H2,H2,H2), header/main/footer/nav all present. Zero images missing alt. | 2026-08-16 re-verified live: single &lt;h1&gt; and zero skipped heading levels across all 21 live pages; header/main/footer/nav present on every page type; zero &lt;img&gt; without an alt attribute. | 2026-08-25 re-verified live: header/main/footer/nav present on every page type; exactly one &lt;h1&gt; per page across all 20 routes; zero skipped heading levels; zero &lt;img&gt; without alt.</t>
+          <t>PASS — single h1 and zero skipped heading levels on all 21 pages; header/main/footer/nav present; zero &lt;img&gt; without alt | 2026-08-13 re-verified live: home and article both single-h1, zero skipped heading levels (home H1 then 17x H2; article H1,H2,H2,H2,H2,H2), header/main/footer/nav all present. Zero images missing alt. | 2026-08-16 re-verified live: single &lt;h1&gt; and zero skipped heading levels across all 21 live pages; header/main/footer/nav present on every page type; zero &lt;img&gt; without an alt attribute. | 2026-08-25 re-verified live: header/main/footer/nav present on every page type; exactly one &lt;h1&gt; per page across all 20 routes; zero skipped heading levels; zero &lt;img&gt; without alt. | 2026-08-27 re-verified live: single h1 and zero skipped heading levels across all 21 routes.</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr"/>
@@ -5054,7 +5058,7 @@
           <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.latest-meta` 3.36:1 dark / 2.93:1 light on the homepage, and 3.36:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .latest-meta re-measured live 2026-08-25: 3.36:1 dark (homepage + /brand/), 2.93:1 light — unchanged from 2026-08-15. Root cause of the non-closure is NOT the fix: it is that the fix never shipped. origin/main is still b64a39b; the F85 commit (55a6d72) sits on LOCAL main, 8 commits ahead of origin, unpushed for 9 days.</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
+      <c r="I88" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5111,7 +5115,7 @@
           <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.hero-corner` 3.71:1 dark on the homepage, and 3.71:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .hero-corner re-measured live 2026-08-25: 3.71:1 dark. Unchanged — fix committed locally (55a6d72), never pushed.</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
+      <c r="I89" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5168,7 +5172,7 @@
           <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: /brand/ `.latest-tag` 3.44:1 — and /brand/'s loaded-sheet list confirms the cause directly: tokens, shell, plates, home-augment, article, brand.css, with NO home-v2.css. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /brand/ re-measured live 2026-08-25: .latest-tag still 3.44:1 (the pre-F77 value), because live /brand/ serves home-augment.css?v=phase32 which does not yet carry the moved override blocks. The move (55a6d72) is committed locally and confirmed present in a fresh dist build; it has never been pushed.</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5225,7 +5229,7 @@
           <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.next-meta` 2.81:1 dark on the /brand/ dogfood demo (still latent on the live homepage — no upcoming essay exists). Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .next-meta re-measured on the /brand/ demo of the strip 2026-08-25: still 2.81:1 dark. Unchanged — fix committed locally (55a6d72), never pushed. Still latent on the homepage itself: zero ghost:true flags remain in the collection and no upcoming entry exists, so IssueNext does not render.</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5282,7 +5286,7 @@
           <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.notfound-eyebrow span.divider` 3.61:1 on /404. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /404 span.divider re-measured live 2026-08-25: still 3.61:1 at opacity .5; live serves notfound.css?v=phase10 (the fix bumps it to phase11). Fix committed locally (8c1e6aa), never pushed.</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
@@ -5396,7 +5400,7 @@
           <t>ISSUE/High (2026-08-16) — /phase0/'s skip link, the first focusable element on the page, computed `color: rgba(243,240,232,.82)` on its own `background: var(--ink)` cream chip: 1.00:1. This is the worst ratio the ledger has recorded and the only finding to date where the text is not merely low-contrast but literally invisible — a sighted keyboard user sees the accent focus ring land on a blank cream box. NOT a colour bug: `--bg` resolves correctly to #060606 at every level of the chain (verified by walking the ancestor chain: A.skip-link / BODY.phase0 / HTML.dark-mode all report #060606). It is a specificity bug. Three rules set colour on this element — `a {color:inherit}` (0,0,1) in tokens.css, `.skip-link {color:var(--bg)}` (0,1,0) in shell.css, and `.phase0 a {color:inherit}` (0,1,1) in phase0.css. The last wins on specificity and hands the chip back the inherited body cream. Scope is exactly one page: /brand/, the other bespoke-CSS surface, carries no blanket `a` rule and measured clean. Missed by every prior run because the skip link sits at left:-999px in its resting state, so a sweep that filters to on-screen elements never measures it — this run caught it by measuring every element with layout geometry regardless of viewport position. | /phase0/ skip link re-measured live 2026-08-25: still rgba(243,240,232,.82) on its own cream chip = 1.00:1, the worst ratio in the ledger and still literally invisible to a sighted keyboard user. Live serves shell.css?v=phase23; the hardened selector ships as phase36. Fix committed locally (79df261), never pushed.</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
@@ -5412,8 +5416,65 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>F92</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>View Earlier toggle — glyph tracks the button state</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>As a reader, I want the arrow on the View Earlier button to point the way the button will act, so the affordance doesn't contradict its own label.</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>earlier-toggle.js updates .btn-label and .btn-count on every click; .btn-glyph (aria-hidden decoration) must track the same state — down-arrow when collapsed ('View Earlier Essays'), up-arrow when expanded ('Show Less').</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>js/earlier-toggle.js, src/pages/index.astro:218-222, src/layouts/HomeLayout.astro:135</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-27</t>
+        </is>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/Low (2026-08-27) — the click handler rewrote the label and the count but never touched the glyph. Live on b64a39b the expanded state reads 'Show Less — showing all ↓': the arrow still points down, i.e. 'more below', while the button's own words say it will collapse. The glyph carries aria-hidden="true" so nothing is exposed to assistive tech — this is a purely visual affordance contradiction, which is why it survived every prior scrub.</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260827) — js/earlier-toggle.js: the click handler now sets .btn-glyph to '↑' when expanding and '↓' when collapsing, alongside the label/count updates it already did. Three lines, same ternary shape as its two neighbours; aria-hidden untouched. Cache-bust earlier-toggle.js phase30→31 in src/layouts/HomeLayout.astro:135 (JS is served immutable/1y).</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — 2026-08-27 on a clean `npm run build` served from dist: collapsed ↓ / 'View Earlier Essays' / '— 8 more' / aria-expanded=false → expanded ↑ / 'Show Less' / '— showing all' / aria-expanded=true → back to ↓. Neighbour regression (F23+F27 interleaved) clean: expand(16,↑) → filter Faith(13, wrap hidden) → clear(16, still ↑ and 'Show Less') → collapse(8,↓). Zero console errors.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K94"/>
+  <autoFilter ref="A3:K95"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -5456,7 +5517,7 @@
         </is>
       </c>
       <c r="B4" s="12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5">
@@ -5503,7 +5564,7 @@
         </is>
       </c>
       <c r="B10" s="14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -5530,7 +5591,7 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -5540,7 +5601,7 @@
         </is>
       </c>
       <c r="B15" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -5550,7 +5611,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
@@ -5560,13 +5621,13 @@
         </is>
       </c>
       <c r="B18" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Total features: 91</t>
+          <t>Total features: 92</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,11 +53,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00CC0000"/>
       <sz val="13"/>
     </font>
@@ -73,7 +68,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -98,11 +93,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0C24B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E0625B"/>
       </patternFill>
     </fill>
     <fill>
@@ -147,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -168,23 +158,19 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4414,7 +4400,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>PENDING — re-check on the next run whether the 2026-08-28 cron fires.</t>
+          <t>PENDING — re-check on the next run whether the 2026-08-28 cron fires. Note the 2026-08-27 push to origin/main triggered a Netlify build directly, so today's site is current regardless of the missed cron.</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5041,12 @@
       </c>
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.latest-meta` 3.36:1 dark / 2.93:1 light on the homepage, and 3.36:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .latest-meta re-measured live 2026-08-25: 3.36:1 dark (homepage + /brand/), 2.93:1 light — unchanged from 2026-08-15. Root cause of the non-closure is NOT the fix: it is that the fix never shipped. origin/main is still b64a39b; the F85 commit (55a6d72) sits on LOCAL main, 8 commits ahead of origin, unpushed for 9 days.</t>
-        </is>
-      </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>ISSUE/High (2026-08-15) — `.latest-meta` ('Faith · Jul 5 · 16 min', the metadata in the homepage standfirst bar) pairs `color: var(--body-muted)` with `opacity: .75`. --body-muted is ALREADY an alpha colour (rgba(243,240,232,.52) dark / rgba(5,5,5,.56) light), tuned to land just over AA on its own — 5.13:1 dark, 4.67:1 light. The extra multiplier composites a second time and drops the control to 3.36:1 dark / 2.93:1 light, under the 4.5:1 floor for 11.52px/400 text. FAILS IN BOTH MODES — the only finding this run that is not dark-mode-specific. Measured on the settled live page with a compositor that resolves the painted surface by walking every ancestor background (flat #0d0d0d here, no image layer to confound it), then confirmed visually in a full-page screenshot where this is plainly the faintest text on the homepage. Missed by every prior run for a precise reason: the 2026-08-13 scrub measured .latest-meta ONLY under pointer hover, where `.issue-latest:hover .latest-meta` re-declares `color: var(--bg); opacity: .6` against the cream hover bar and clears at 5.23:1. F83 recorded that number and closed the question. The RESTING state — which is what a reader actually sees — was never measured. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.latest-meta` 3.36:1 dark / 2.93:1 light on the homepage, and 3.36:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .latest-meta re-measured live 2026-08-25: 3.36:1 dark (homepage + /brand/), 2.93:1 light — unchanged from 2026-08-15. Root cause of the non-closure is NOT the fix: it is that the fix never shipped. origin/main is still b64a39b; the F85 commit (55a6d72) sits on LOCAL main, 8 commits ahead of origin, unpushed for 9 days. | RESOLVED LIVE 2026-08-27 — see p4.</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>HIGH (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
@@ -5070,7 +5056,7 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — `npm run build` clean, 19 pages. dist/css/*.css confirmed to carry the rules with zero opacity declarations. Post-fix values measured on the live DOM with the exact shipped declarations applied: dark 3.36:1 -&gt; 5.13:1, light 2.93:1 -&gt; 4.67:1. Both clear the 4.5:1 floor. Goes live-verified on the next scrub after Dexter merges. | RETEST 2026-08-25 (build + live-DOM, both clean): fresh `npm run build` emits dist/css/home-augment.css:148-161 and dist/css/home-v2.css:107-118 with the opacity declaration absent and the explanatory comment intact. Then measured empirically rather than inferred — inserted the exact shipped state into the live home-v2.css CSSOM (insertRule, then deleteRule to restore): 3.36:1 -&gt; 5.13:1 on the homepage and 3.36:1 -&gt; 5.13:1 on /brand/. Matches the 2026-08-15 build-verified figure exactly. Fix holds; still not live.</t>
+          <t>PASS (closed live 2026-08-27 on deploy e3fe698) — was ISSUE/High since 2026-08-15. `.issue-head .latest-meta` measured 3.36:1 dark on the live site this morning; after the push it measures 5.13:1 with the opacity multiplier gone (computed opacity now 1, --body-muted carrying the muting alone). 12 days between fix and ship.</t>
         </is>
       </c>
     </row>
@@ -5112,12 +5098,12 @@
       </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.hero-corner` 3.71:1 dark on the homepage, and 3.71:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .hero-corner re-measured live 2026-08-25: 3.71:1 dark. Unchanged — fix committed locally (55a6d72), never pushed.</t>
-        </is>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>ISSUE/High (2026-08-15) — `.hero-corner` sets `color: var(--bg); opacity: .5`. The identity hero is an INVERTED plate: in dark mode it presents a cream ground (243,240,232) and the label paints #060606 over it, which at .5 opacity computes 3.71:1 — under the 4.5:1 floor for 11.52px/700 (bold, but well below the 18.66px large-text threshold). Light mode inverts to cream-on-black and clears at 4.91:1, so this is dark-mode-only. Same root shape as F85 — a decorative opacity multiplier stacked on a colour that was already correct — but reached by the opposite route: here the multiplier sits on a SOLID token rather than an alpha one. Surface resolved by walking to the first opaque ancestor (.hero-main, flat cream, no image layer); confirmed visually in a dark-mode full-page screenshot. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.hero-corner` 3.71:1 dark on the homepage, and 3.71:1 again on /brand/. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .hero-corner re-measured live 2026-08-25: 3.71:1 dark. Unchanged — fix committed locally (55a6d72), never pushed. | RESOLVED LIVE 2026-08-27 — see p4.</t>
+        </is>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>HIGH (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
@@ -5127,7 +5113,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — post-fix values measured on the live DOM with opacity .6 applied: dark 3.71:1 -&gt; 5.23:1, light 4.91:1 -&gt; 6.74:1. Both clear. dist confirmed to carry `opacity: .6` in both sheets. | RETEST 2026-08-25: dist carries `opacity: .6` in both sheets (home-augment.css:229, home-v2.css:860). Live-DOM CSSOM injection measured 3.71:1 -&gt; 5.23:1 on the homepage and on /brand/. Matches 2026-08-15. Fix holds; not live.</t>
+          <t>PASS (closed live 2026-08-27 on deploy e3fe698) — was ISSUE/High since 2026-08-15. `.identity-hero .hero-corner` ('The Writer → 01') measured 3.71:1 live this morning, now 5.23:1 at opacity .6.</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5155,12 @@
       </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: /brand/ `.latest-tag` 3.44:1 — and /brand/'s loaded-sheet list confirms the cause directly: tokens, shell, plates, home-augment, article, brand.css, with NO home-v2.css. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /brand/ re-measured live 2026-08-25: .latest-tag still 3.44:1 (the pre-F77 value), because live /brand/ serves home-augment.css?v=phase32 which does not yet carry the moved override blocks. The move (55a6d72) is committed locally and confirmed present in a fresh dist build; it has never been pushed.</t>
-        </is>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>ISSUE/High (2026-08-15) — /brand/ was still rendering `.latest-tag` at 3.44:1, the exact pre-fix value F77 closed on 2026-08-13, two days after that row went green. Cause: the F77 and F83 dark-mode overrides were written into css/home-v2.css. The homepage loads home-augment.css AND home-v2.css; /brand/ loads home-augment.css and never home-v2.css. So the fixes reached the homepage and silently skipped the design system's own documentation page. This is a broken contract, not a cosmetic gap: brand/index.html:115 states a 'Dogfood rule' — '/brand/ runs the same stylesheets as the live site... If a live component breaks, this page breaks too. That is intentional.' A fix that lands on one surface and not the other makes the dogfood page a liar in the safer direction, which is worse than an obvious break. The F77 comment even asserted it 'Covers the .issue-head hook in home-augment.css too; wins on specificity, not source order' — true about specificity, but specificity is irrelevant in a sheet that never loads. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: /brand/ `.latest-tag` 3.44:1 — and /brand/'s loaded-sheet list confirms the cause directly: tokens, shell, plates, home-augment, article, brand.css, with NO home-v2.css. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /brand/ re-measured live 2026-08-25: .latest-tag still 3.44:1 (the pre-F77 value), because live /brand/ serves home-augment.css?v=phase32 which does not yet carry the moved override blocks. The move (55a6d72) is committed locally and confirmed present in a fresh dist build; it has never been pushed. | RESOLVED LIVE 2026-08-27 — see p4.</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>HIGH (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J90" s="4" t="inlineStr">
@@ -5184,7 +5170,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — grepped the built sheets: dist/css/home-augment.css carries both blocks at lines 127-134, dist/css/home-v2.css carries neither (only the breadcrumbs). Measured on the live /brand/ page in dark mode with the override applied: `.latest-tag` 3.44:1 -&gt; 5.17:1, the identical figure the homepage has been serving since deploy 791bfc5. Dogfood parity restored. | RETEST 2026-08-25: grepped the fresh build — dist/css/home-augment.css carries the dark-mode .latest-tag override (1 occurrence, lines 127-130); dist/css/home-v2.css carries none. Injecting that exact rule into the live /brand/ home-augment.css CSSOM took .latest-tag 3.44:1 -&gt; 5.17:1. Fix holds; not live.</t>
+          <t>PASS (closed live 2026-08-27 on deploy e3fe698) — was ISSUE/High since 2026-08-15. /brand/ now loads home-augment.css?v=phase33 (was phase32), so the relocated F77/F83 dark-mode overrides reach it: `.latest-tag` renders rgb(243,240,232) on rgb(204,0,0) = 5.17:1, matching the homepage. The dogfood contract holds again.</t>
         </is>
       </c>
     </row>
@@ -5226,12 +5212,12 @@
       </c>
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.next-meta` 2.81:1 dark on the /brand/ dogfood demo (still latent on the live homepage — no upcoming essay exists). Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .next-meta re-measured on the /brand/ demo of the strip 2026-08-25: still 2.81:1 dark. Unchanged — fix committed locally (55a6d72), never pushed. Still latent on the homepage itself: zero ghost:true flags remain in the collection and no upcoming entry exists, so IssueNext does not render.</t>
-        </is>
-      </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>ISSUE/Medium (2026-08-15) — `.next-meta` repeats the F85 defect one notch worse: `color: var(--body-muted)` plus `opacity: .65`, computing 2.81:1 in dark against the 4.5:1 floor. Graded MEDIUM rather than HIGH because it is LATENT — the Issue-next strip only renders when an upcoming essay exists, and all 16 entries are status:published with past dates (see F41/F46), so no reader has hit it. It was found because /brand/ demos the strip under its dogfood rule, which is the same page that exposed F87. Worth recording precisely: this would have shipped broken on the day Dexter scheduled his next essay, and it would have shipped inside the one component whose whole job is to advertise that essay. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.next-meta` 2.81:1 dark on the /brand/ dogfood demo (still latent on the live homepage — no upcoming essay exists). Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | .next-meta re-measured on the /brand/ demo of the strip 2026-08-25: still 2.81:1 dark. Unchanged — fix committed locally (55a6d72), never pushed. Still latent on the homepage itself: zero ghost:true flags remain in the collection and no upcoming entry exists, so IssueNext does not render. | RESOLVED LIVE 2026-08-27 — see p4.</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM (closed at source) (resolved)</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
@@ -5241,7 +5227,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — measured on the live /brand/ demo of the strip in dark mode with the fix applied: 2.81:1 -&gt; 5.13:1. Clears. (An earlier reading of 1.02:1 during this run was an artifact of forcing the dark-mode class onto an already-rendered light page, which left tokens half-resolved; discarded and re-measured after a clean reload with the dxmode cookie set. Recording it here so the number is not mistaken for a real regression if it resurfaces.) | RETEST 2026-08-25: dist/css/home-augment.css:728-740 and home-v2.css:206-216 both carry .next-meta with no opacity. Live /brand/ CSSOM injection: 2.81:1 -&gt; 5.13:1. Fix holds; not live.</t>
+          <t>PASS (closed live 2026-08-27 on deploy e3fe698) — was ISSUE/Medium since 2026-08-15, latent. The issue-next strip still does not render (zero upcoming essays, F30 correctly absent), so `.next-meta` cannot be measured on a live page — but the shipped home-v2.css?v=phase35 carries the fix (no opacity multiplier on --body-muted), verified in the served sheet. Closes as fixed-at-source; the first scheduled essay will exercise it for real.</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5269,12 @@
       </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.notfound-eyebrow span.divider` 3.61:1 on /404. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /404 span.divider re-measured live 2026-08-25: still 3.61:1 at opacity .5; live serves notfound.css?v=phase10 (the fix bumps it to phase11). Fix committed locally (8c1e6aa), never pushed.</t>
-        </is>
-      </c>
-      <c r="I92" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>ISSUE/Medium (2026-08-15) — the `·` separators in the 404 eyebrow carry `opacity: .5`, computing 3.61:1. Unlike the homepage's `.dot` separators — which are `aria-hidden="true"` and therefore exempt as decoration — these carry no aria-hidden, so they are exposed text in both the accessibility tree and the visual read. Caught by explicitly checking aria-hidden per separator rather than assuming all separators are decorative: the homepage `.dot` at 4.25:1 was correctly DISMISSED as a non-finding by that same check, and this one was correctly kept. | 2026-08-16 LIVE RE-CHECK: still failing on production — qa/fixes-20260815 is UNMERGED, so yesterday's fix has not shipped. Re-measured on the live page with the same compositor: `.notfound-eyebrow span.divider` 3.61:1 on /404. Value is identical to the 2026-08-15 reading, which confirms the defect is static and the fix is simply undeployed, not regressed. Row stays ISSUE until a live-verified deploy. | /404 span.divider re-measured live 2026-08-25: still 3.61:1 at opacity .5; live serves notfound.css?v=phase10 (the fix bumps it to phase11). Fix committed locally (8c1e6aa), never pushed. | RESOLVED LIVE 2026-08-27 — see p4.</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>MEDIUM (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
@@ -5298,7 +5284,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-15) — measured on the live /404 with opacity .7 applied: 3.61:1 -&gt; 7.19:1. | RETEST 2026-08-25: dist/css/notfound.css:64-69 carries `opacity: .7` and dist/404.html references notfound.css?v=phase11. Live /404 CSSOM injection: 3.61:1 -&gt; 7.19:1. Matches 2026-08-15. Fix holds; not live.</t>
+          <t>PASS (closed live 2026-08-27 on deploy e3fe698) — was ISSUE/Medium since 2026-08-15. The /404 eyebrow `·` dividers measured 3.61:1 live this morning at opacity .5; now 7.19:1 at opacity .7. Still correctly NOT aria-hidden — they are exposed text, which is why they were in scope while the homepage .dot separators are not.</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5329,7 @@
           <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions. | Re-confirmed live 2026-08-25, all five values unchanged: .demo-ghost-meta 2.05:1, .demo-ghost-date 2.45:1, .demo-ghost-title 2.93:1 (vs its 3:1 large-text floor), .demo-plate-meta 3.17:1, and the bespoke "Download Pack" h3 2.87:1 (#ff4d4d on the cream panel). Still BLOCKED — still the same two questions for Dexter, now open 10 days.</t>
         </is>
       </c>
-      <c r="I93" s="9" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5397,12 +5383,12 @@
       </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/High (2026-08-16) — /phase0/'s skip link, the first focusable element on the page, computed `color: rgba(243,240,232,.82)` on its own `background: var(--ink)` cream chip: 1.00:1. This is the worst ratio the ledger has recorded and the only finding to date where the text is not merely low-contrast but literally invisible — a sighted keyboard user sees the accent focus ring land on a blank cream box. NOT a colour bug: `--bg` resolves correctly to #060606 at every level of the chain (verified by walking the ancestor chain: A.skip-link / BODY.phase0 / HTML.dark-mode all report #060606). It is a specificity bug. Three rules set colour on this element — `a {color:inherit}` (0,0,1) in tokens.css, `.skip-link {color:var(--bg)}` (0,1,0) in shell.css, and `.phase0 a {color:inherit}` (0,1,1) in phase0.css. The last wins on specificity and hands the chip back the inherited body cream. Scope is exactly one page: /brand/, the other bespoke-CSS surface, carries no blanket `a` rule and measured clean. Missed by every prior run because the skip link sits at left:-999px in its resting state, so a sweep that filters to on-screen elements never measures it — this run caught it by measuring every element with layout geometry regardless of viewport position. | /phase0/ skip link re-measured live 2026-08-25: still rgba(243,240,232,.82) on its own cream chip = 1.00:1, the worst ratio in the ledger and still literally invisible to a sighted keyboard user. Live serves shell.css?v=phase23; the hardened selector ships as phase36. Fix committed locally (79df261), never pushed.</t>
-        </is>
-      </c>
-      <c r="I94" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>ISSUE/High (2026-08-16) — /phase0/'s skip link, the first focusable element on the page, computed `color: rgba(243,240,232,.82)` on its own `background: var(--ink)` cream chip: 1.00:1. This is the worst ratio the ledger has recorded and the only finding to date where the text is not merely low-contrast but literally invisible — a sighted keyboard user sees the accent focus ring land on a blank cream box. NOT a colour bug: `--bg` resolves correctly to #060606 at every level of the chain (verified by walking the ancestor chain: A.skip-link / BODY.phase0 / HTML.dark-mode all report #060606). It is a specificity bug. Three rules set colour on this element — `a {color:inherit}` (0,0,1) in tokens.css, `.skip-link {color:var(--bg)}` (0,1,0) in shell.css, and `.phase0 a {color:inherit}` (0,1,1) in phase0.css. The last wins on specificity and hands the chip back the inherited body cream. Scope is exactly one page: /brand/, the other bespoke-CSS surface, carries no blanket `a` rule and measured clean. Missed by every prior run because the skip link sits at left:-999px in its resting state, so a sweep that filters to on-screen elements never measures it — this run caught it by measuring every element with layout geometry regardless of viewport position. | /phase0/ skip link re-measured live 2026-08-25: still rgba(243,240,232,.82) on its own cream chip = 1.00:1, the worst ratio in the ledger and still literally invisible to a sighted keyboard user. Live serves shell.css?v=phase23; the hardened selector ships as phase36. Fix committed locally (79df261), never pushed. | RESOLVED LIVE 2026-08-27 — see p4.</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>HIGH (closed live) (resolved)</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
@@ -5412,7 +5398,7 @@
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>PASS (build-verified 2026-08-16) — `npm run build` clean, 19 pages; dist/css/shell.css carries the hardened selector and all 21 built pages reference shell.css?v=phase36. Cascade verified empirically rather than by reasoning alone: inserted the exact committed selector into the live shell.css CSSOM (CSP blocks &lt;style&gt; injection but not CSSOM mutation of an already-loaded same-origin sheet) and re-measured — /phase0/ 1.00:1 -&gt; 17.79:1, with the colour flipping to the intended rgb(6,6,6) on cream. Regression-checked on the two surfaces most likely to be disturbed: homepage and /brand/ both no-op (already rgb(6,6,6) on cream before and after). Goes live-verified on the next SCRUB after Dexter merges. | RETEST 2026-08-25: dist/css/shell.css:19-29 carries `.skip-link, .skip-link:link, .skip-link:visited` and all built pages reference shell.css?v=phase36. Live /phase0/ CSSOM injection of that selector: 1.00:1 -&gt; 17.79:1, with the chip resolving to #060606 on cream. Fix holds; not live.</t>
+          <t>PASS (closed live 2026-08-27 on deploy e3fe698) — was ISSUE/High since 2026-08-16, the worst ratio this ledger has recorded. /phase0/'s skip link — the first focusable element on the page — measured 1.00:1 live this morning (rgba(243,240,232,.82) on rgb(243,240,232), literally invisible). It now measures 17.79:1 (rgb(6,6,6) on rgb(243,240,232)) and is still confirmed first in the focus order. shell.css?v=phase36 live on all surfaces.</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5443,7 @@
           <t>ISSUE/Low (2026-08-27) — the click handler rewrote the label and the count but never touched the glyph. Live on b64a39b the expanded state reads 'Show Less — showing all ↓': the arrow still points down, i.e. 'more below', while the button's own words say it will collapse. The glyph carries aria-hidden="true" so nothing is exposed to assistive tech — this is a purely visual affordance contradiction, which is why it survived every prior scrub.</t>
         </is>
       </c>
-      <c r="I95" s="9" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -5489,7 +5475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5497,14 +5483,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -5516,7 +5502,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="12" t="n">
+      <c r="B4" s="11" t="n">
         <v>79</v>
       </c>
     </row>
@@ -5526,7 +5512,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5536,12 +5522,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
@@ -5553,7 +5539,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <v>87</v>
       </c>
     </row>
@@ -5563,12 +5549,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="13" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
@@ -5577,55 +5563,45 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>4</v>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B14" s="15" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Resolved (P4 PASS)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>12</v>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Resolved (P4 PASS)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n">
+      <c r="B17" s="18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Total features: 92</t>
         </is>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H95" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Low (2026-08-27) — the click handler rewrote the label and the count but never touched the glyph. Live on b64a39b the expanded state reads 'Show Less — showing all ↓': the arrow still points down, i.e. 'more below', while the button's own words say it will collapse. The glyph carries aria-hidden="true" so nothing is exposed to assistive tech — this is a purely visual affordance contradiction, which is why it survived every prior scrub.</t>
-        </is>
-      </c>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>ISSUE/Low (2026-08-27) — the click handler rewrote the label and the count but never touched the glyph. Live on b64a39b the expanded state reads 'Show Less — showing all ↓': the arrow still points down, i.e. 'more below', while the button's own words say it will collapse. The glyph carries aria-hidden="true" so nothing is exposed to assistive tech — this is a purely visual affordance contradiction, which is why it survived every prior scrub. | RESOLVED LIVE 2026-08-27 — see p4.</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>Low (closed live)</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27 on a clean `npm run build` served from dist: collapsed ↓ / 'View Earlier Essays' / '— 8 more' / aria-expanded=false → expanded ↑ / 'Show Less' / '— showing all' / aria-expanded=true → back to ↓. Neighbour regression (F23+F27 interleaved) clean: expand(16,↑) → filter Faith(13, wrap hidden) → clear(16, still ↑ and 'Show Less') → collapse(8,↓). Zero console errors.</t>
+          <t>PASS (closed live 2026-08-27 on deploy 910abae) — was ISSUE/Low, opened and fixed the same day. Verified on the live homepage serving earlier-toggle.js?v=phase31: collapsed ↓ / 'View Earlier Essays' / '— 8 more' / aria-expanded=false / 8 plates → expanded ↑ / 'Show Less' / '— showing all' / aria-expanded=true / 16 plates → back to ↓ / 8. Glyph still carries aria-hidden="true". Zero console errors. Asset served public,max-age=31536000,immutable, so the phase30→31 bust was required and worked.</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="B14" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,7 +68,7 @@
       <color rgb="00C0211B"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -93,11 +93,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0C24B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9C7E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -158,19 +153,15 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5326,22 +5317,22 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions. | Re-confirmed live 2026-08-25, all five values unchanged: .demo-ghost-meta 2.05:1, .demo-ghost-date 2.45:1, .demo-ghost-title 2.93:1 (vs its 3:1 large-text floor), .demo-plate-meta 3.17:1, and the bespoke "Download Pack" h3 2.87:1 (#ff4d4d on the cream panel). Still BLOCKED — still the same two questions for Dexter, now open 10 days.</t>
-        </is>
-      </c>
-      <c r="I93" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
+          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions. | Re-confirmed live 2026-08-25, all five values unchanged: .demo-ghost-meta 2.05:1, .demo-ghost-date 2.45:1, .demo-ghost-title 2.93:1 (vs its 3:1 large-text floor), .demo-plate-meta 3.17:1, and the bespoke "Download Pack" h3 2.87:1 (#ff4d4d on the cream panel). Still BLOCKED — still the same two questions for Dexter, now open 10 days. | 2026-08-27 RE-DIAGNOSED, and the premise of this row was wrong. Four of the five are not documentation-intent choices at all — `.demo-ghost-title/-date/-meta` and `.demo-plate-meta` are faithful mirrors of `.plate-ghost` and `.identity-plate` in css/plates.css, carrying the same tokens and the same opacity multipliers. Composited against their real grounds those production rules measure .plate-title 2.92:1 light / 2.84:1 dark (3:1 large-text floor), .teaser-date 2.06/2.37, `.plate-ghost .meta-rail` 1.80/1.97, and `.identity-plate .meta-rail` 4.14/4.09 (4.5:1 floor) — every one under AA. css/plates.css:377-380 carried a comment asserting these values PASSED ("3.1:1 on #f4f4f1", "3.7:1 on #060606"); both figures are wrong and are what kept the defect invisible. The fifth, the /brand/ 'Download Pack' h3, is worse than recorded: it fails in BOTH modes (2.87:1 dark, 3.46:1 light), not just dark. Separately found: the /brand/ identity specimen had drifted — it used var(--ink)/var(--bg), which invert, so in dark mode it rendered a CREAM identity plate while production deliberately holds #0a0a0a.</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>Low (fixed)</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER. Two questions: (a) should the ghost specimens keep their dim demonstration value, or does the doc need a readable annotation beside them explaining the treatment? (b) the "Download Pack" h3 in brand.css is not a specimen and can be lifted on his word.</t>
+          <t>FIX (qa/fixes-20260827) — repaired the components, not the illustrations, so /brand/ keeps dogfooding (the F87 lesson). css/plates.css: `.plate-ghost .plate-title` .42-&gt;.46 light and .35-&gt;.40 dark (the smallest values clearing the 3:1 floor with headroom; the recession is preserved and is carried mostly by the dashed border and absent cover anyway) and the false comment replaced with the measured truth; `.plate-ghost .teaser-date` and `.plate-ghost .meta-rail` dropped their --ink+opacity multipliers for plain `--body-muted` — the same fix shape as F85/F86/F88, now applied to the last component still carrying it; `.identity-plate .meta-rail` .45-&gt;.55 (--body-muted is deliberately NOT used here: that plate has its own inverted ground, and a page-ground-tuned token would be wrong against it — the F86/F91 lesson). brand/brand.css: the three demo-ghost rules mirror production exactly, including its light/dark split which the specimen had been missing; `.demo-plate.identity` retokenised from var(--ink)/var(--bg) to the real --identity-plate-* pair so it stops inverting; `.logo-download h3` pinned per mode to the accent that is correct against the PANEL rather than the page (#ff4d4d light, #c00 dark — the inverse of --accent-text). brand/index.html: the identity specimen's inline style retokenised to match. Cache-bust plates.css phase15-&gt;16 (HomeLayout + brand/index.html) and brand.css brand5-&gt;brand6.</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS (verified against build) — 2026-08-27, all five elements measured in BOTH modes on a clean `npm run build` served from dist, 10/10 clear their floor: demo-ghost-title 2.93-&gt;3.48 dark / 3.33 light (floor 3.0); demo-ghost-date 2.45-&gt;5.13 dark / 4.67 light; demo-ghost-meta 2.05-&gt;5.13 dark / 4.67 light; demo-plate-meta 3.17-&gt;5.63 dark / 5.77 light; 'Download Pack' h3 2.87-&gt;5.17 dark / 3.46-&gt;6.23 light (floor 4.5 on all four). The identity specimen now computes rgb(10,10,10) in dark and rgb(5,5,5) in light, matching production instead of inverting. Homepage regression clean: 16 plates, opaque .meta-rail untouched at 17.38:1, .hero-corner 5.23 and .latest-meta 5.13 (F85/F86) intact, zero console errors. NOTE: the plates.css half of this fix cannot be verified live — see F93.</t>
         </is>
       </c>
     </row>
@@ -5459,8 +5450,65 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>F93</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Ghost teaser plate + identity plate — orphaned by the Astro migration</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>As the author, when an essay is scheduled ahead of its publish date, I want the archive to show its ghost teaser plate; and I want the identity plate the design system documents to actually exist.</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Either css/plates.css's `.plate-ghost` and `.identity-plate` rules are reachable from a component, or they are retired from plates.css and from /brand/'s documented component set.</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>css/plates.css:355-410 (.plate-ghost), :262-345 (.identity-plate); src/components/home/Plate.astro; brand/index.html (Ghost Teaser Plate, demo-plate.identity)</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-27</t>
+        </is>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/Medium (2026-08-27) — both class names are DEAD in production. `Plate.astro` can only ever emit `plate plate-{wide|secondary|banner|half|lead}` plus `plate-image`, `img-*` and `plate-row`; there is no code path to `plate-ghost` or `identity-plate`, the strings appear nowhere in src/, and they appear in none of the 19 built pages. This is almost certainly fallout from the 2026-04-21 Astro cutover — the ghost teaser is clearly still intended (ComingSoonLayout exists, visibility.ts date-gates future essays, and F30/F41 both describe an upcoming-essay flow), it just never got rewired to the new cascade. Two consequences: css/plates.css ships ~90 lines of unreachable rules on every homepage load, and /brand/ documents both as live components when neither can render. Found while re-diagnosing F90 — the F90 contrast failures are in these same dead rules, which is why they only ever surfaced on /brand/.</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — NEEDS DEXTER. Not auto-fixable in either direction: rewiring the ghost plate into the cascade is a layout/product decision (where an upcoming essay sits in the reading order, whether it counts in the lane index, whether it is linkable), and deleting the rules retires two documented components from the design system. Both are your call. The contrast fix from F90 is already applied to these rules either way, so whichever direction you pick, they ship AA-clean.</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K95"/>
+  <autoFilter ref="A3:K96"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -5475,7 +5523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5483,14 +5531,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Phase 2 Test Results</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>— P2 (test) —</t>
         </is>
@@ -5502,7 +5550,7 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="10" t="n">
         <v>79</v>
       </c>
     </row>
@@ -5512,7 +5560,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5522,12 +5570,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>— P4 (re-test) —</t>
         </is>
@@ -5539,8 +5587,8 @@
           <t>PASS</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
-        <v>87</v>
+      <c r="B9" s="10" t="n">
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -5549,12 +5597,12 @@
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
@@ -5566,44 +5614,34 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>1</v>
+      <c r="B13" s="13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Resolved (P4 PASS)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Resolved (P4 PASS)</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B17" s="18" t="n">
+      <c r="B16" s="16" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>Total features: 92</t>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Total features: 93</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5317,12 +5317,12 @@
       </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions. | Re-confirmed live 2026-08-25, all five values unchanged: .demo-ghost-meta 2.05:1, .demo-ghost-date 2.45:1, .demo-ghost-title 2.93:1 (vs its 3:1 large-text floor), .demo-plate-meta 3.17:1, and the bespoke "Download Pack" h3 2.87:1 (#ff4d4d on the cream panel). Still BLOCKED — still the same two questions for Dexter, now open 10 days. | 2026-08-27 RE-DIAGNOSED, and the premise of this row was wrong. Four of the five are not documentation-intent choices at all — `.demo-ghost-title/-date/-meta` and `.demo-plate-meta` are faithful mirrors of `.plate-ghost` and `.identity-plate` in css/plates.css, carrying the same tokens and the same opacity multipliers. Composited against their real grounds those production rules measure .plate-title 2.92:1 light / 2.84:1 dark (3:1 large-text floor), .teaser-date 2.06/2.37, `.plate-ghost .meta-rail` 1.80/1.97, and `.identity-plate .meta-rail` 4.14/4.09 (4.5:1 floor) — every one under AA. css/plates.css:377-380 carried a comment asserting these values PASSED ("3.1:1 on #f4f4f1", "3.7:1 on #060606"); both figures are wrong and are what kept the defect invisible. The fifth, the /brand/ 'Download Pack' h3, is worse than recorded: it fails in BOTH modes (2.87:1 dark, 3.46:1 light), not just dark. Separately found: the /brand/ identity specimen had drifted — it used var(--ink)/var(--bg), which invert, so in dark mode it rendered a CREAM identity plate while production deliberately holds #0a0a0a.</t>
+          <t>ISSUE/Low (2026-08-15) — five /brand/-only text elements measure under AA in dark mode: `.demo-ghost-meta` ('Coming Soon') 2.05:1, `.demo-ghost-date` 2.45:1, `.demo-ghost-title` 2.93:1 (against its 3:1 large-text floor), `.demo-plate-meta` 3.17:1, and the bespoke 'Download Pack' h3 at 2.87:1. Held BLOCKED rather than fixed: four of the five are `demo-ghost-*` specimens whose entire purpose is to DEMONSTRATE the dim 'not yet published' ghost treatment, so raising their contrast would edit the documentation's illustration rather than repair a defect — that is a call about what the design system wants to say, and it is Dexter's. The fifth ('Download Pack') is bespoke brand.css chrome and is a genuine, if low-traffic, AA miss. Deliberately NOT bundled with F87: that row was a broken contract with an objectively correct fix; this one is a judgement about intent. | 2026-08-16 LIVE RE-CHECK: still open and still BLOCKED — unchanged by design. Re-measured on live /brand/: `.demo-ghost-meta` 2.05:1 and `.demo-plate-meta` 3.17:1 both reproduce exactly. The other three named elements (demo-ghost-date, demo-ghost-title, the 'Download Pack' h3) did not surface in today's sweep because this run only measures elements holding their own text node and not inside an aria-hidden subtree; that is a narrower filter than the 2026-08-15 pass used, not evidence they were fixed. Still NEEDS DEXTER on both questions. | Re-confirmed live 2026-08-25, all five values unchanged: .demo-ghost-meta 2.05:1, .demo-ghost-date 2.45:1, .demo-ghost-title 2.93:1 (vs its 3:1 large-text floor), .demo-plate-meta 3.17:1, and the bespoke "Download Pack" h3 2.87:1 (#ff4d4d on the cream panel). Still BLOCKED — still the same two questions for Dexter, now open 10 days. | 2026-08-27 RE-DIAGNOSED, and the premise of this row was wrong. Four of the five are not documentation-intent choices at all — `.demo-ghost-title/-date/-meta` and `.demo-plate-meta` are faithful mirrors of `.plate-ghost` and `.identity-plate` in css/plates.css, carrying the same tokens and the same opacity multipliers. Composited against their real grounds those production rules measure .plate-title 2.92:1 light / 2.84:1 dark (3:1 large-text floor), .teaser-date 2.06/2.37, `.plate-ghost .meta-rail` 1.80/1.97, and `.identity-plate .meta-rail` 4.14/4.09 (4.5:1 floor) — every one under AA. css/plates.css:377-380 carried a comment asserting these values PASSED ("3.1:1 on #f4f4f1", "3.7:1 on #060606"); both figures are wrong and are what kept the defect invisible. The fifth, the /brand/ 'Download Pack' h3, is worse than recorded: it fails in BOTH modes (2.87:1 dark, 3.46:1 light), not just dark. Separately found: the /brand/ identity specimen had drifted — it used var(--ink)/var(--bg), which invert, so in dark mode it rendered a CREAM identity plate while production deliberately holds #0a0a0a. | RESOLVED LIVE 2026-08-27 — see p4.</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>Low (fixed)</t>
+          <t>Low (closed live)</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27, all five elements measured in BOTH modes on a clean `npm run build` served from dist, 10/10 clear their floor: demo-ghost-title 2.93-&gt;3.48 dark / 3.33 light (floor 3.0); demo-ghost-date 2.45-&gt;5.13 dark / 4.67 light; demo-ghost-meta 2.05-&gt;5.13 dark / 4.67 light; demo-plate-meta 3.17-&gt;5.63 dark / 5.77 light; 'Download Pack' h3 2.87-&gt;5.17 dark / 3.46-&gt;6.23 light (floor 4.5 on all four). The identity specimen now computes rgb(10,10,10) in dark and rgb(5,5,5) in light, matching production instead of inverting. Homepage regression clean: 16 plates, opaque .meta-rail untouched at 17.38:1, .hero-corner 5.23 and .latest-meta 5.13 (F85/F86) intact, zero console errors. NOTE: the plates.css half of this fix cannot be verified live — see F93.</t>
+          <t>PASS (verified against build) — 2026-08-27, all five elements measured in BOTH modes on a clean `npm run build` served from dist, 10/10 clear their floor: demo-ghost-title 2.93-&gt;3.48 dark / 3.33 light (floor 3.0); demo-ghost-date 2.45-&gt;5.13 dark / 4.67 light; demo-ghost-meta 2.05-&gt;5.13 dark / 4.67 light; demo-plate-meta 3.17-&gt;5.63 dark / 5.77 light; 'Download Pack' h3 2.87-&gt;5.17 dark / 3.46-&gt;6.23 light (floor 4.5 on all four). The identity specimen now computes rgb(10,10,10) in dark and rgb(5,5,5) in light, matching production instead of inverting. Homepage regression clean: 16 plates, opaque .meta-rail untouched at 17.38:1, .hero-corner 5.23 and .latest-meta 5.13 (F85/F86) intact, zero console errors. NOTE: the plates.css half of this fix cannot be verified live — see F93. || CLOSED LIVE 2026-08-27 on deploy b0bfe3c. Re-measured on production /brand/ in both modes, serving plates.css?v=phase16 and brand.css?v=brand6 — all ten measurements reproduce the build values exactly: ghost-title 3.48 dark / 3.33 light (floor 3.0); ghost-date 5.13 / 4.67; ghost-meta 5.13 / 4.67; identity meta-rail 5.63 / 5.77; 'Download Pack' h3 5.17 / 6.23 (floor 4.5). The identity specimen computes rgb(10,10,10) dark and rgb(5,5,5) light — it no longer inverts, and now matches production. Live homepage regression clean: 16 plates, opaque .meta-rail 17.38:1, .hero-corner 5.23, .latest-meta 5.13, glyph ↓ at rest, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, both new asset versions served immutable.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5488,22 +5488,22 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-27) — both class names are DEAD in production. `Plate.astro` can only ever emit `plate plate-{wide|secondary|banner|half|lead}` plus `plate-image`, `img-*` and `plate-row`; there is no code path to `plate-ghost` or `identity-plate`, the strings appear nowhere in src/, and they appear in none of the 19 built pages. This is almost certainly fallout from the 2026-04-21 Astro cutover — the ghost teaser is clearly still intended (ComingSoonLayout exists, visibility.ts date-gates future essays, and F30/F41 both describe an upcoming-essay flow), it just never got rewired to the new cascade. Two consequences: css/plates.css ships ~90 lines of unreachable rules on every homepage load, and /brand/ documents both as live components when neither can render. Found while re-diagnosing F90 — the F90 contrast failures are in these same dead rules, which is why they only ever surfaced on /brand/.</t>
-        </is>
-      </c>
-      <c r="I96" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>ISSUE/Medium (2026-08-27) — both class names are DEAD in production. `Plate.astro` can only ever emit `plate plate-{wide|secondary|banner|half|lead}` plus `plate-image`, `img-*` and `plate-row`; there is no code path to `plate-ghost` or `identity-plate`, the strings appear nowhere in src/, and they appear in none of the 19 built pages. This is almost certainly fallout from the 2026-04-21 Astro cutover — the ghost teaser is clearly still intended (ComingSoonLayout exists, visibility.ts date-gates future essays, and F30/F41 both describe an upcoming-essay flow), it just never got rewired to the new cascade. Two consequences: css/plates.css ships ~90 lines of unreachable rules on every homepage load, and /brand/ documents both as live components when neither can render. Found while re-diagnosing F90 — the F90 contrast failures are in these same dead rules, which is why they only ever surfaced on /brand/. | Dexter chose REWIRE over retire, 2026-08-27.</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>Medium (fixed)</t>
         </is>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER. Not auto-fixable in either direction: rewiring the ghost plate into the cascade is a layout/product decision (where an upcoming essay sits in the reading order, whether it counts in the lane index, whether it is linkable), and deleting the rules retires two documented components from the design system. Both are your call. The contrast fix from F90 is already applied to these rules either way, so whichever direction you pick, they ship AA-clean.</t>
+          <t>FIX (qa/fixes-20260827, 96b0bc9) — new src/components/home/GhostPlate.astro emits the held-space card for every isUpcoming entry, wired into src/pages/index.astro as its own '01 / Next' section at the head of the cascade. Three decisions, all taken from DESIGN-SYSTEM.md rather than invented: (1) STATIC — no &lt;a&gt;, no href, no hover, no focus ring, per the doc's 'identity plate, ghost teaser (static). No hover highlight, no pointer cursor, no focus outline'; the linked CTA for the same essay remains the IssueNext strip, so the plate holds the space and the strip does the asking. (2) PLACEMENT at the head of the cascade — the cascade's organising principle is strict reverse chronology and an upcoming essay is newer than the lead, so this is the only placement that preserves it; at span 5 the ghost does not dominate and the lead plate's full-width hero sits immediately beneath. (3) NO data-lane, which is load-bearing: lane-filter.js matches on the inner [data-lane], so with none the ghost is hidden by any active filter and restored by baseHidden() on clear — keeping the published-only lane counts (F22) honest against what is on screen. Row-head numbers were hardcoded 01/02 plus a conditional on Earlier, which cannot survive a section appearing above them; now derived from which sections actually render.</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS (verified against build) — 2026-08-27. The collection holds no upcoming entry, so verification used a temporary future-dated fixture, removed before commit (git status clean of it). Renders span 5 at 503x230 desktop, span 1 at 339px mobile with no overflow at 375px. Static: cursor default, not a link, not focusable. Contrast clears AA on the values F90 just landed — title 3.40 dark / 3.31 light (floor 3.0); teaser-date, meta rail and lane badge all 5.11 dark / 4.62 light (floor 4.5). Single h1, no skipped heading levels. Lane filter: 9 visible with ghost -&gt; Faith 13 ghost hidden -&gt; clear 9 ghost back -&gt; Art 3 ghost hidden (matching the lane index exactly) -&gt; clear 9. Earlier toggle: expand 17 / collapse 9, glyph tracks, ghost unaffected. With zero upcoming the page is behaviourally identical to before — row heads 01/02/03, no ghost markup. Zero console errors in both modes. Does not surface Dexter's before-i-had-the-words.mdx (status 'drafted' fails isUpcomingData). OBSERVED, not opened as its own row: DESIGN-SYSTEM.md specifies .plate-ghost min-height 346px while plates.css ships 230px. Doc-vs-implementation drift of the F82/F84 class, but the doc file currently carries Dexter's uncommitted 'Two-plane rule' edit, so it is his to reconcile, not the loop's.</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5625,7 +5625,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="B16" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5488,7 +5488,7 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-27) — both class names are DEAD in production. `Plate.astro` can only ever emit `plate plate-{wide|secondary|banner|half|lead}` plus `plate-image`, `img-*` and `plate-row`; there is no code path to `plate-ghost` or `identity-plate`, the strings appear nowhere in src/, and they appear in none of the 19 built pages. This is almost certainly fallout from the 2026-04-21 Astro cutover — the ghost teaser is clearly still intended (ComingSoonLayout exists, visibility.ts date-gates future essays, and F30/F41 both describe an upcoming-essay flow), it just never got rewired to the new cascade. Two consequences: css/plates.css ships ~90 lines of unreachable rules on every homepage load, and /brand/ documents both as live components when neither can render. Found while re-diagnosing F90 — the F90 contrast failures are in these same dead rules, which is why they only ever surfaced on /brand/. | Dexter chose REWIRE over retire, 2026-08-27.</t>
+          <t>ISSUE/Medium (2026-08-27) — both class names are DEAD in production. `Plate.astro` can only ever emit `plate plate-{wide|secondary|banner|half|lead}` plus `plate-image`, `img-*` and `plate-row`; there is no code path to `plate-ghost` or `identity-plate`, the strings appear nowhere in src/, and they appear in none of the 19 built pages. This is almost certainly fallout from the 2026-04-21 Astro cutover — the ghost teaser is clearly still intended (ComingSoonLayout exists, visibility.ts date-gates future essays, and F30/F41 both describe an upcoming-essay flow), it just never got rewired to the new cascade. Two consequences: css/plates.css ships ~90 lines of unreachable rules on every homepage load, and /brand/ documents both as live components when neither can render. Found while re-diagnosing F90 — the F90 contrast failures are in these same dead rules, which is why they only ever surfaced on /brand/. | Dexter chose REWIRE over retire, 2026-08-27. | RESOLVED 2026-08-27 — see p4.</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27. The collection holds no upcoming entry, so verification used a temporary future-dated fixture, removed before commit (git status clean of it). Renders span 5 at 503x230 desktop, span 1 at 339px mobile with no overflow at 375px. Static: cursor default, not a link, not focusable. Contrast clears AA on the values F90 just landed — title 3.40 dark / 3.31 light (floor 3.0); teaser-date, meta rail and lane badge all 5.11 dark / 4.62 light (floor 4.5). Single h1, no skipped heading levels. Lane filter: 9 visible with ghost -&gt; Faith 13 ghost hidden -&gt; clear 9 ghost back -&gt; Art 3 ghost hidden (matching the lane index exactly) -&gt; clear 9. Earlier toggle: expand 17 / collapse 9, glyph tracks, ghost unaffected. With zero upcoming the page is behaviourally identical to before — row heads 01/02/03, no ghost markup. Zero console errors in both modes. Does not surface Dexter's before-i-had-the-words.mdx (status 'drafted' fails isUpcomingData). OBSERVED, not opened as its own row: DESIGN-SYSTEM.md specifies .plate-ghost min-height 346px while plates.css ships 230px. Doc-vs-implementation drift of the F82/F84 class, but the doc file currently carries Dexter's uncommitted 'Two-plane rule' edit, so it is his to reconcile, not the loop's.</t>
+          <t>PASS (verified against build) — 2026-08-27. The collection holds no upcoming entry, so verification used a temporary future-dated fixture, removed before commit (git status clean of it). Renders span 5 at 503x230 desktop, span 1 at 339px mobile with no overflow at 375px. Static: cursor default, not a link, not focusable. Contrast clears AA on the values F90 just landed — title 3.40 dark / 3.31 light (floor 3.0); teaser-date, meta rail and lane badge all 5.11 dark / 4.62 light (floor 4.5). Single h1, no skipped heading levels. Lane filter: 9 visible with ghost -&gt; Faith 13 ghost hidden -&gt; clear 9 ghost back -&gt; Art 3 ghost hidden (matching the lane index exactly) -&gt; clear 9. Earlier toggle: expand 17 / collapse 9, glyph tracks, ghost unaffected. With zero upcoming the page is behaviourally identical to before — row heads 01/02/03, no ghost markup. Zero console errors in both modes. Does not surface Dexter's before-i-had-the-words.mdx (status 'drafted' fails isUpcomingData). OBSERVED, not opened as its own row: DESIGN-SYSTEM.md specifies .plate-ghost min-height 346px while plates.css ships 230px. Doc-vs-implementation drift of the F82/F84 class, but the doc file currently carries Dexter's uncommitted 'Two-plane rule' edit, so it is his to reconcile, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 2387e1d. The ghost plate cannot be observed on production yet — the collection holds no upcoming entry — so what was verified live is that the change is INERT until one exists, which is the correct behaviour: row heads read 01 This Week / 02 This Month / 03 Earlier, zero .plate-ghost markup, IssueNext correctly absent (F30), 16 plates, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep clean: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The section-numbering and ghost rendering will first be exercised on production the day Dexter schedules an essay; that run's SCRUB should re-test this row live.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>If an upcoming essay exists, IssueNext renders earliest upcoming with 'Next' tag, title, meta, 'Notify me →', linking to its coming-soon URL. Hidden when no upcoming essays.</t>
+          <t>If an upcoming essay exists, IssueNext renders earliest upcoming with 'Next' tag, title, meta, 'Notify me →', linking to its coming-soon URL. Hidden when no upcoming essays. AS OF 2026-08-27 [F94]: the strip is additionally gated on there being NO ghost plate, and since both surfaces derive from the same upcoming list, that makes it unreachable. Expected behaviour is now 'absent in every state' until the gate is reversed. Do not flag its absence as a regression; DO flag it if it ever renders alongside a ghost plate.</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>PASS — correctly absent: zero upcoming essays in the collection | 2026-08-25 re-verified live: correctly ABSENT — index.astro renders IssueNext only when an upcoming entry exists, and none does. Not a regression. | 2026-08-27 re-verified live: correctly absent — zero upcoming essays; .next-meta not in the DOM.</t>
+          <t>PASS — correctly absent: zero upcoming essays in the collection | 2026-08-25 re-verified live: correctly ABSENT — index.astro renders IssueNext only when an upcoming entry exists, and none does. Not a regression. | 2026-08-27 re-verified live: correctly absent — zero upcoming essays; .next-meta not in the DOM. | 2026-08-27 re-scoped by F94: still correctly absent, but now for two independent reasons — zero upcoming essays AND the new ghost-plate gate. Verified on a fixture build that with an upcoming essay present the strip stays absent and the ghost plate renders in its place.</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -5507,8 +5507,61 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>F94</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>IssueNext strip stands down when a ghost plate shows</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>As a reader, when an essay is forthcoming I want to see it once, not twice — the held-space plate in the archive rather than the plate and a repeat strip below it.</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>When any ghost plate renders, the IssueNext strip does not. Because both surfaces derive from the same `upcomingSoonestFirst` list, this makes the strip unreachable in every state; the component, its CSS and F30 stay intact so the decision is one line to reverse.</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>src/pages/index.astro (showIssueNext), src/components/home/IssueNext.astro, css/home-v2.css:162-250</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-27</t>
+        </is>
+      </c>
+      <c r="H97" s="6" t="inlineStr">
+        <is>
+          <t>N/A by decision (2026-08-27) — not a defect. Dexter's call after seeing F93 ship: the ghost plate and the IssueNext strip are two presentations of the same upcoming essay, so with both live the title appeared on the homepage twice. The plate wins.</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr"/>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>IMPLEMENTED (qa/fixes-20260827, 6436636) — `showIssueNext = Boolean(issueNext) &amp;&amp; upcomingSoonestFirst.length === 0` in src/pages/index.astro. Gated rather than deleted on purpose: IssueNext.astro, its ~90 lines of CSS in home-v2.css and ledger row F30 all stay intact, and reversing is one line. TRACKED HERE BECAUSE THE COMPONENT IS NOW UNREACHABLE — the same shape of orphaning F93 was opened for, the difference being that F93's orphan was an accident nobody chose and this one is a decision with a name on it. If the decision stands, a future run should propose retiring the component and its CSS properly rather than leaving dead weight on every homepage load.</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K96"/>
+  <autoFilter ref="A3:K97"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -5561,7 +5614,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5588,7 +5641,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -5641,7 +5694,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Total features: 93</t>
+          <t>Total features: 94</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5556,7 +5556,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's.</t>
+          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 121a621. Like F93, the gate cannot be observed doing its job on production yet — no upcoming entry exists, so the strip would have been absent anyway. What was verified live is that the change is inert: row heads 01 This Week / 02 This Month / 03 Earlier, 16 plates, zero .plate-ghost, zero .issue-next, single h1, SubscribeManifesto form still present, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The gate is first exercised on production the day an essay is scheduled — that run's SCRUB must confirm the ghost renders AND the strip stays absent, and must not read the strip's absence as a regression (see the re-scoped F30).</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>PASS — correctly absent: zero upcoming essays in the collection | 2026-08-25 re-verified live: correctly ABSENT — index.astro renders IssueNext only when an upcoming entry exists, and none does. Not a regression. | 2026-08-27 re-verified live: correctly absent — zero upcoming essays; .next-meta not in the DOM. | 2026-08-27 re-scoped by F94: still correctly absent, but now for two independent reasons — zero upcoming essays AND the new ghost-plate gate. Verified on a fixture build that with an upcoming essay present the strip stays absent and the ghost plate renders in its place.</t>
+          <t>PASS — correctly absent: zero upcoming essays in the collection | 2026-08-25 re-verified live: correctly ABSENT — index.astro renders IssueNext only when an upcoming entry exists, and none does. Not a regression. | 2026-08-27 re-verified live: correctly absent — zero upcoming essays; .next-meta not in the DOM. | 2026-08-27 re-scoped by F94: still correctly absent, but now for two independent reasons — zero upcoming essays AND the new ghost-plate gate. Verified on a fixture build that with an upcoming essay present the strip stays absent and the ghost plate renders in its place. | 2026-08-27 RETIRED: the component no longer exists. IssueNext.astro is deleted and all 202 lines of `.issue-next` CSS are removed from home-v2.css and home-augment.css. Row marked N/A per the never-delete rule — see F94 for the decision and the verification.</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr"/>
@@ -2126,9 +2126,9 @@
           <t>NOTE: correctly absent (no upcoming)</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>N/A — retired by owner decision 2026-08-27. Superseded by the ghost teaser plate (F93). Future runs: do not test this row and do not flag the strip's absence. DO flag it if `.issue-next` ever reappears in the DOM or in any shipped stylesheet, which would mean the retirement regressed.</t>
         </is>
       </c>
     </row>
@@ -5551,12 +5551,12 @@
       <c r="I97" s="6" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>IMPLEMENTED (qa/fixes-20260827, 6436636) — `showIssueNext = Boolean(issueNext) &amp;&amp; upcomingSoonestFirst.length === 0` in src/pages/index.astro. Gated rather than deleted on purpose: IssueNext.astro, its ~90 lines of CSS in home-v2.css and ledger row F30 all stay intact, and reversing is one line. TRACKED HERE BECAUSE THE COMPONENT IS NOW UNREACHABLE — the same shape of orphaning F93 was opened for, the difference being that F93's orphan was an accident nobody chose and this one is a decision with a name on it. If the decision stands, a future run should propose retiring the component and its CSS properly rather than leaving dead weight on every homepage load.</t>
+          <t>IMPLEMENTED (qa/fixes-20260827, 6436636) — `showIssueNext = Boolean(issueNext) &amp;&amp; upcomingSoonestFirst.length === 0` in src/pages/index.astro. Gated rather than deleted on purpose: IssueNext.astro, its ~90 lines of CSS in home-v2.css and ledger row F30 all stay intact, and reversing is one line. TRACKED HERE BECAUSE THE COMPONENT IS NOW UNREACHABLE — the same shape of orphaning F93 was opened for, the difference being that F93's orphan was an accident nobody chose and this one is a decision with a name on it. If the decision stands, a future run should propose retiring the component and its CSS properly rather than leaving dead weight on every homepage load. || COMPLETED (e3b4e91) — Dexter took the retirement. IssueNext.astro deleted; index.astro cleared of the import, `issueNext`, `showIssueNext` and the render; 99 lines out of home-v2.css and 103 out of home-augment.css including its file-index entry and its two selectors in the prefers-reduced-motion block. 202 lines off every homepage load. /brand/ was rendering a LIVE `.issue-next` specimen under 'Live component' — the F87 dogfood contract — so deleting the CSS alone would have left the design system demoing a component that no longer exists, F93's problem in reverse. Section 19 is kept in place and converted to a retirement note rather than deleted, because section numbers are cross-referenced in the surrounding prose ('Section 13/17/20') and a gap reads as an error; the heading carries a new `.u-retired` utility. Cache-bust home-v2 phase35-&gt;36, home-augment phase33-&gt;34, brand.css brand6-&gt;7.</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 121a621. Like F93, the gate cannot be observed doing its job on production yet — no upcoming entry exists, so the strip would have been absent anyway. What was verified live is that the change is inert: row heads 01 This Week / 02 This Month / 03 Earlier, 16 plates, zero .plate-ghost, zero .issue-next, single h1, SubscribeManifesto form still present, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The gate is first exercised on production the day an essay is scheduled — that run's SCRUB must confirm the ghost renders AND the strip stays absent, and must not read the strip's absence as a regression (see the re-scoped F30).</t>
+          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 121a621. Like F93, the gate cannot be observed doing its job on production yet — no upcoming entry exists, so the strip would have been absent anyway. What was verified live is that the change is inert: row heads 01 This Week / 02 This Month / 03 Earlier, 16 plates, zero .plate-ghost, zero .issue-next, single h1, SubscribeManifesto form still present, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The gate is first exercised on production the day an essay is scheduled — that run's SCRUB must confirm the ghost renders AND the strip stays absent, and must not read the strip's absence as a regression (see the re-scoped F30). || RETIREMENT VERIFIED against a clean build 2026-08-27: homepage still loads its 5 sheets, 0 `.issue-next` elements, 16 plates, single h1, subscribe manifesto form intact, row heads 01/02/03, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. The prefers-reduced-motion @media block still parses and still applies to its remaining five selectors (F75 unaffected). Brace balance verified in all three edited sheets. /brand/: 0 `.issue-next` elements, all 21 sections intact, heading reads '19. Issue Next (retired)', `.u-retired` renders SF Mono at --body-muted = 5.11:1 dark (AA). Fixture build with an upcoming essay: 1 ghost plate, 0 strips, the title appears exactly once, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier. Zero console errors on either page. NOTE FOR THE NEXT RUN: DESIGN-SYSTEM.md:1413 still describes 'the homepage's issue-next ghost CTA' while explaining the `next.ghost` frontmatter flag — that sentence already conflated this strip with ArticleLayout's `.article-nav-ghost` (which stays), and the retirement makes it more wrong. Left alone because that file carries Dexter's uncommitted Two-plane-rule edit; his to reconcile.</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5641,58 +5641,68 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>PENDING</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B11" s="12" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>— Issues by severity (found) —</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B14" s="13" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Resolved (P4 PASS)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B16" s="10" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Still open</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
+      <c r="B17" s="16" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Total features: 94</t>
         </is>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5556,7 +5556,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 121a621. Like F93, the gate cannot be observed doing its job on production yet — no upcoming entry exists, so the strip would have been absent anyway. What was verified live is that the change is inert: row heads 01 This Week / 02 This Month / 03 Earlier, 16 plates, zero .plate-ghost, zero .issue-next, single h1, SubscribeManifesto form still present, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The gate is first exercised on production the day an essay is scheduled — that run's SCRUB must confirm the ghost renders AND the strip stays absent, and must not read the strip's absence as a regression (see the re-scoped F30). || RETIREMENT VERIFIED against a clean build 2026-08-27: homepage still loads its 5 sheets, 0 `.issue-next` elements, 16 plates, single h1, subscribe manifesto form intact, row heads 01/02/03, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. The prefers-reduced-motion @media block still parses and still applies to its remaining five selectors (F75 unaffected). Brace balance verified in all three edited sheets. /brand/: 0 `.issue-next` elements, all 21 sections intact, heading reads '19. Issue Next (retired)', `.u-retired` renders SF Mono at --body-muted = 5.11:1 dark (AA). Fixture build with an upcoming essay: 1 ghost plate, 0 strips, the title appears exactly once, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier. Zero console errors on either page. NOTE FOR THE NEXT RUN: DESIGN-SYSTEM.md:1413 still describes 'the homepage's issue-next ghost CTA' while explaining the `next.ghost` frontmatter flag — that sentence already conflated this strip with ArticleLayout's `.article-nav-ghost` (which stays), and the retirement makes it more wrong. Left alone because that file carries Dexter's uncommitted Two-plane-rule edit; his to reconcile.</t>
+          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 121a621. Like F93, the gate cannot be observed doing its job on production yet — no upcoming entry exists, so the strip would have been absent anyway. What was verified live is that the change is inert: row heads 01 This Week / 02 This Month / 03 Earlier, 16 plates, zero .plate-ghost, zero .issue-next, single h1, SubscribeManifesto form still present, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The gate is first exercised on production the day an essay is scheduled — that run's SCRUB must confirm the ghost renders AND the strip stays absent, and must not read the strip's absence as a regression (see the re-scoped F30). || RETIREMENT VERIFIED against a clean build 2026-08-27: homepage still loads its 5 sheets, 0 `.issue-next` elements, 16 plates, single h1, subscribe manifesto form intact, row heads 01/02/03, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. The prefers-reduced-motion @media block still parses and still applies to its remaining five selectors (F75 unaffected). Brace balance verified in all three edited sheets. /brand/: 0 `.issue-next` elements, all 21 sections intact, heading reads '19. Issue Next (retired)', `.u-retired` renders SF Mono at --body-muted = 5.11:1 dark (AA). Fixture build with an upcoming essay: 1 ghost plate, 0 strips, the title appears exactly once, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier. Zero console errors on either page. NOTE FOR THE NEXT RUN: DESIGN-SYSTEM.md:1413 still describes 'the homepage's issue-next ghost CTA' while explaining the `next.ghost` frontmatter flag — that sentence already conflated this strip with ArticleLayout's `.article-nav-ghost` (which stays), and the retirement makes it more wrong. Left alone because that file carries Dexter's uncommitted Two-plane-rule edit; his to reconcile. || RETIREMENT SHIPPED LIVE 2026-08-27 on deploy 3b46f34. Verified on production, not inferred: the homepage serves home-v2.css?v=phase36 and home-augment.css?v=phase34 and the CSSOM reports ZERO rules whose selectorText contains 'issue-next' across every loaded sheet, on both / and /brand/; zero `.issue-next` elements on either page. The only surviving mentions anywhere are three CSS comments, confirmed by fetching the shipped sheets. Homepage otherwise unchanged: 16 plates, row heads 01/02/03, single h1, subscribe form present, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16 with the glyph tracking, prefers-reduced-motion block still present (F75 intact). /brand/ keeps all 21 sections and reads '19. Issue Next (retired)'. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs, subscribe function 200. Zero console errors on either page.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K97"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>PASS (resolved 2026-08-10) — was ISSUE/Low: DESIGN-SYSTEM.md:115 listed "Reading progress bar (`var(--accent)`)" as a permitted accent use, but css/article.css:876 ships `.reading-progress { background: var(--ink) }`. Commit 68b0c1d (2026-04-10) recolored it on purpose and left the reason in the CSS: red was competing with the masthead and diluting the accent's semantic weight. That commit rewrote 136 lines of DESIGN-SYSTEM.md but missed this one bullet, which dated to c75ded9 earlier the same day. The CSS was correct; the doc line was stale.</t>
+          <t>PASS (resolved 2026-08-10) — was ISSUE/Low: DESIGN-SYSTEM.md:115 listed "Reading progress bar (`var(--accent)`)" as a permitted accent use, but css/article.css:876 ships `.reading-progress { background: var(--ink) }`. Commit 68b0c1d (2026-04-10) recolored it on purpose and left the reason in the CSS: red was competing with the masthead and diluting the accent's semantic weight. That commit rewrote 136 lines of DESIGN-SYSTEM.md but missed this one bullet, which dated to c75ded9 earlier the same day. The CSS was correct; the doc line was stale. | 2026-08-27 second doc-parity pass (9b8e4c4): three more drifts closed, all doc-side. The Ghost Teaser Plate code block was pre-F90 and pre-cutover (min-height 346 vs the shipped 230; .plate-title opacity .35 vs .46/.40; --ink+opacity on .teaser-date and .meta-rail vs --body-muted), its prose still carried the static-HTML instruction 'swap for the full article plate and remove the ghost CSS from index.html', and the prev/next section claimed `next.ghost: true` drives 'the homepage's issue-next ghost CTA' — which conflated .article-nav-ghost with a component that no longer exists and was wrong before any of today's work. Also corrected a stale comment inside plates.css that justified a padding choice against '346px min-height' on a rule setting 230px — the same wrong number that had propagated into the doc.</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Ghost teaser plate + identity plate — orphaned by the Astro migration</t>
+          <t>Ghost teaser plate — orphaned by the Astro migration (rewired)</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Either css/plates.css's `.plate-ghost` and `.identity-plate` rules are reachable from a component, or they are retired from plates.css and from /brand/'s documented component set.</t>
+          <t>Either css/plates.css's `.plate-ghost` rules are reachable from a component, or they are retired from plates.css and from /brand/'s documented component set. (The identity-plate half of the original row moved to F95 on 2026-08-27.)</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-27) — both class names are DEAD in production. `Plate.astro` can only ever emit `plate plate-{wide|secondary|banner|half|lead}` plus `plate-image`, `img-*` and `plate-row`; there is no code path to `plate-ghost` or `identity-plate`, the strings appear nowhere in src/, and they appear in none of the 19 built pages. This is almost certainly fallout from the 2026-04-21 Astro cutover — the ghost teaser is clearly still intended (ComingSoonLayout exists, visibility.ts date-gates future essays, and F30/F41 both describe an upcoming-essay flow), it just never got rewired to the new cascade. Two consequences: css/plates.css ships ~90 lines of unreachable rules on every homepage load, and /brand/ documents both as live components when neither can render. Found while re-diagnosing F90 — the F90 contrast failures are in these same dead rules, which is why they only ever surfaced on /brand/. | Dexter chose REWIRE over retire, 2026-08-27. | RESOLVED 2026-08-27 — see p4.</t>
+          <t>ISSUE/Medium (2026-08-27) — both class names are DEAD in production. `Plate.astro` can only ever emit `plate plate-{wide|secondary|banner|half|lead}` plus `plate-image`, `img-*` and `plate-row`; there is no code path to `plate-ghost` or `identity-plate`, the strings appear nowhere in src/, and they appear in none of the 19 built pages. This is almost certainly fallout from the 2026-04-21 Astro cutover — the ghost teaser is clearly still intended (ComingSoonLayout exists, visibility.ts date-gates future essays, and F30/F41 both describe an upcoming-essay flow), it just never got rewired to the new cascade. Two consequences: css/plates.css ships ~90 lines of unreachable rules on every homepage load, and /brand/ documents both as live components when neither can render. Found while re-diagnosing F90 — the F90 contrast failures are in these same dead rules, which is why they only ever surfaced on /brand/. | Dexter chose REWIRE over retire, 2026-08-27. | RESOLVED 2026-08-27 — see p4. | CORRECTION 2026-08-27: this row was closed as 'fixed' while it named TWO orphaned components and only ONE was rewired. `.plate-ghost` has an emitter now; `.identity-plate` still has none — no occurrence anywhere in src/, zero in the 19 built pages. F93 is hereby narrowed to the ghost plate, which is genuinely fixed, and the identity-plate half is split out to F95 so it is not buried under a green row. My closure, my error.</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
@@ -5560,8 +5560,65 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>F95</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Homepage</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Identity plate — still orphaned by the Astro migration</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>As the author, I want the identity plate the design system documents to either exist on the site or stop being documented as if it does.</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Either css/plates.css's `.identity-plate` rules are reachable from a component, or they are retired from plates.css and from /brand/'s documented component set.</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>css/plates.css:262-345 (.identity-plate, .identity-sub, .identity-plate .meta-rail); src/components/home/Plate.astro; brand/index.html (demo-plate.identity)</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-27 (split from F93)</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/Medium (2026-08-27) — SPLIT FROM F93, WHICH I CLOSED TOO BROADLY. F93 named two orphaned components; Dexter asked for the ghost plate to be rewired and it was, but `.identity-plate` was never in scope and is still dead. Re-verified today: the string appears nowhere in src/ and in none of the 19 built pages, because Plate.astro can only emit plate-{wide|secondary|banner|half|lead} plus plate-image/img-*/plate-row. css/plates.css ships ~85 lines of unreachable rules on every homepage load, and /brand/ documents the plate as live. Note this is NOT the same thing as `.identity-hero`, which does render on the homepage and is fine (F21). Contrast is not at issue — F90 already lifted `.identity-plate .meta-rail` to 5.77/5.63 — this is purely reachability.</t>
+        </is>
+      </c>
+      <c r="I98" s="7" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — NEEDS DEXTER, same shape as F93 was. Rewiring means deciding what an identity plate is FOR in the current cascade (the homepage already opens with .identity-hero, which may simply have superseded it); retiring means removing a documented component and ~85 lines of CSS, the F94 treatment. Both are his call. Whichever way it goes, the rules are AA-clean already.</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K97"/>
+  <autoFilter ref="A3:K98"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -5661,7 +5718,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -5678,7 +5735,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -5698,13 +5755,13 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Total features: 94</t>
+          <t>Total features: 95</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -4876,7 +4876,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>PASS — permitted-accent list re-read after the edit: 10 entries remain, every one of them verified against live CSS this run (section-head h2 + rule, callout left-border, .callout-emph, scripture cite, stat bar, identity plate tagline, article link hover underline, plate hover border, focus rings). Zero doc-vs-implementation mismatches remain in the section. grep confirms no other line in DESIGN-SYSTEM.md claims the progress bar uses --accent. Not a deploy-visible change — /DESIGN-SYSTEM.md returns 404 by design.</t>
+          <t>PASS — permitted-accent list re-read after the edit: 10 entries remain, every one of them verified against live CSS this run (section-head h2 + rule, callout left-border, .callout-emph, scripture cite, stat bar, identity plate tagline, article link hover underline, plate hover border, focus rings). Zero doc-vs-implementation mismatches remain in the section. grep confirms no other line in DESIGN-SYSTEM.md claims the progress bar uses --accent. Not a deploy-visible change — /DESIGN-SYSTEM.md returns 404 by design. || Doc-parity pass VERIFIED LIVE 2026-08-27 on deploy b12ca66. DESIGN-SYSTEM.md is a repo document, not a route — the live check that matters is that it stayed unserved, and /DESIGN-SYSTEM.md still returns 404. Sweep clean: 25 routes 200, both correct 404s, 5/5 security headers, feed 16, sitemap 20. Homepage: 16 plates, row heads 01/02/03, single h1, 0 .identity-plate, 1 .identity-hero, 0 .issue-next. /brand/: 21 sections, '19. Issue Next (retired)', 0 .issue-next. Zero console errors on either page. The plates.css comment correction reached production without a cache-bust as intended — the served sheet carries it for new visitors and cached clients keep a byte-identical rendering.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -4376,7 +4376,7 @@
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-27) — the scheduled run did not fire today. GitHub Actions shows 'Daily rebuild' completing every day 2026-08-19 through 2026-08-26 at 05:35-05:47Z; there is no run for 2026-08-27, checked at 14:06Z — 9h past the 05:05 UTC cron. Workflow state is 'active' and the YAML is unchanged and valid, so this is GitHub dropping/delaying the schedule, not a repo defect. Netlify's newest ready deploy is 2026-08-26T05:43Z (commit_ref b64a39b == GitHub main HEAD). Live impact today: none — zero date-gated essays are pending (F30 correctly absent), so the rebuild would have produced byte-identical output. It matters the day an essay is scheduled.</t>
+          <t>ISSUE/Medium (2026-08-27) — the scheduled run did not fire today. GitHub Actions shows 'Daily rebuild' completing every day 2026-08-19 through 2026-08-26 at 05:35-05:47Z; there is no run for 2026-08-27, checked at 14:06Z — 9h past the 05:05 UTC cron. Workflow state is 'active' and the YAML is unchanged and valid, so this is GitHub dropping/delaying the schedule, not a repo defect. Netlify's newest ready deploy is 2026-08-26T05:43Z (commit_ref b64a39b == GitHub main HEAD). Live impact today: none — zero date-gated essays are pending (F30 correctly absent), so the rebuild would have produced byte-identical output. It matters the day an essay is scheduled. | CORRECTION 2026-08-28. Yesterday's conclusion was WRONG IN ITS CAUSE. I reported at 14:06Z that no run existed for 2026-08-27 and inferred GitHub had dropped the schedule. The run did happen — at 16:23:33Z, about 11.3 hours after the 05:05Z cron and about two hours after I looked. Today's fired at 17:21:17Z, about 12.3 hours late. So the real finding is not a dropped run but a DRIFTED one: the workflow moved from a steady 05:35-05:47Z window (2026-08-19 through 08-26) to 16:23-17:21Z on the two days since. Still open, still GitHub-side, and still worth knowing — a date-gated essay would go live roughly twelve hours after its intended 00:00 CST rather than roughly forty minutes after. The measurement was sound; the inference from a single missing data point was not, and 'checked once, concluded never' is the antipattern to carry forward.</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — outside the repo. Nothing in daily-rebuild.yml is wrong; the cron simply did not run on GitHub's side. Options for Dexter, none auto-appliable: (a) do nothing, GitHub schedules are best-effort and this is the first miss in 8+ days; (b) fire it manually when a scheduled essay is due (`gh workflow run 'Daily rebuild'`); (c) move the trigger off GitHub cron to a Netlify scheduled function if publish-day reliability ever has to be guaranteed.</t>
+          <t>BLOCKED — outside the repo, and the YAML is still correct. Options for Dexter, unchanged in substance but re-aimed at lateness rather than absence: (a) accept it — nothing is scheduled, and a late rebuild costs nothing on a day with no date-gated content; (b) fire it by hand on publish day (`gh workflow run "Daily rebuild"`), which is the reliable move for a timed drop; (c) move the trigger to a Netlify scheduled function if publish-hour precision ever has to be guaranteed. Worth noting the workflow header already accepts an hour of latency by design; twelve is a different order.</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>PENDING — re-check on the next run whether the 2026-08-28 cron fires. Note the 2026-08-27 push to origin/main triggered a Netlify build directly, so today's site is current regardless of the missed cron.</t>
+          <t>PENDING — track the fire time daily. Two consecutive late runs is a drift, not yet a pattern.</t>
         </is>
       </c>
     </row>
@@ -5598,22 +5598,22 @@
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>ISSUE/Medium (2026-08-27) — SPLIT FROM F93, WHICH I CLOSED TOO BROADLY. F93 named two orphaned components; Dexter asked for the ghost plate to be rewired and it was, but `.identity-plate` was never in scope and is still dead. Re-verified today: the string appears nowhere in src/ and in none of the 19 built pages, because Plate.astro can only emit plate-{wide|secondary|banner|half|lead} plus plate-image/img-*/plate-row. css/plates.css ships ~85 lines of unreachable rules on every homepage load, and /brand/ documents the plate as live. Note this is NOT the same thing as `.identity-hero`, which does render on the homepage and is fine (F21). Contrast is not at issue — F90 already lifted `.identity-plate .meta-rail` to 5.77/5.63 — this is purely reachability.</t>
-        </is>
-      </c>
-      <c r="I98" s="7" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>ISSUE/Medium (2026-08-27) — SPLIT FROM F93, WHICH I CLOSED TOO BROADLY. F93 named two orphaned components; Dexter asked for the ghost plate to be rewired and it was, but `.identity-plate` was never in scope and is still dead. Re-verified today: the string appears nowhere in src/ and in none of the 19 built pages, because Plate.astro can only emit plate-{wide|secondary|banner|half|lead} plus plate-image/img-*/plate-row. css/plates.css ships ~85 lines of unreachable rules on every homepage load, and /brand/ documents the plate as live. Note this is NOT the same thing as `.identity-hero`, which does render on the homepage and is fine (F21). Contrast is not at issue — F90 already lifted `.identity-plate .meta-rail` to 5.77/5.63 — this is purely reachability. | RESOLVED 2026-08-28 — Dexter chose retire. See p4.</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Medium (fixed)</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>BLOCKED — NEEDS DEXTER, same shape as F93 was. Rewiring means deciding what an identity plate is FOR in the current cascade (the homepage already opens with .identity-hero, which may simply have superseded it); retiring means removing a documented component and ~85 lines of CSS, the F94 treatment. Both are his call. Whichever way it goes, the rules are AA-clean already.</t>
+          <t>FIX (qa/fixes-20260827, af2d31f) — retired, the F94 treatment. Removed: 98 lines from css/plates.css (the section plus both responsive overrides); --identity-plate-bg/-ink from all three blocks of css/tokens.css plus their doc comment and identity-sub from the --track-badge comment; .demo-plate.identity from brand/brand.css; the specimen and the identity-sub mention from brand/index.html; and from DESIGN-SYSTEM.md the Plate Sizes row, three typography-table rows, the hairline exemption and two token comments, with the section itself converted to a retirement note. Confirmed zero surviving var(--identity-plate-*) references anywhere before bumping. Verified first that the surviving .identity-hero shares NO classes with the retired plate — the hero is entirely hero-*, the plate entirely identity-* — so the retirement cannot touch it. Cache-bust tokens.css phase23-&gt;24 across all 7 referencing files, plates.css phase16-&gt;17 across both, brand.css brand7-&gt;8; checked for skew afterwards, 21/21 built pages on tokens phase24. ONE ADDITION, flagged for Dexter: removing a span-4 left the /brand/ plates demo summing to 8 while that section's own prose says 'Rows must sum to 12', so the slot was refilled with a plain span-4 cell carrying a real essay title — plain because the row had none and the Texture Alternation Rule wants one between textured neighbours.</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>PASS (verified against build) — 2026-08-28. Homepage: 0 .identity-plate, 1 .identity-hero, 16 plates, row heads 01/02/03, single h1, --identity-plate-bg resolves to empty. Contrast unchanged on everything the token removal could have touched: hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38. Article page: 4 sheets, single h1, body #060606 on cream. /phase0/: skip link still 6,6,6 on cream, F91 intact. /brand/: 0 identity specimen, all 21 sections, first plates grid now one row of 5+3+4 = 12 filling the full 900px with zero right-edge gap. Brace balance verified in all three edited sheets. Zero console errors on any surface.</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="B14" s="13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5745,7 +5745,7 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5603,7 +5603,7 @@
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>Medium (fixed)</t>
+          <t>Medium (closed live)</t>
         </is>
       </c>
       <c r="J98" s="4" t="inlineStr">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-28. Homepage: 0 .identity-plate, 1 .identity-hero, 16 plates, row heads 01/02/03, single h1, --identity-plate-bg resolves to empty. Contrast unchanged on everything the token removal could have touched: hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38. Article page: 4 sheets, single h1, body #060606 on cream. /phase0/: skip link still 6,6,6 on cream, F91 intact. /brand/: 0 identity specimen, all 21 sections, first plates grid now one row of 5+3+4 = 12 filling the full 900px with zero right-edge gap. Brace balance verified in all three edited sheets. Zero console errors on any surface.</t>
+          <t>PASS (verified against build) — 2026-08-28. Homepage: 0 .identity-plate, 1 .identity-hero, 16 plates, row heads 01/02/03, single h1, --identity-plate-bg resolves to empty. Contrast unchanged on everything the token removal could have touched: hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38. Article page: 4 sheets, single h1, body #060606 on cream. /phase0/: skip link still 6,6,6 on cream, F91 intact. /brand/: 0 identity specimen, all 21 sections, first plates grid now one row of 5+3+4 = 12 filling the full 900px with zero right-edge gap. Brace balance verified in all three edited sheets. Zero console errors on any surface. || CLOSED LIVE 2026-08-28 on deploy 517ab13. Verified on production: 0 .identity-plate on / and on /brand/, 0 identity specimen, `--identity-plate-bg` resolves empty in the live CSSOM, and the shipped tokens.css and plates.css carry zero occurrences. No version skew — all 8 sampled surfaces (home, about, brand, phase0, 404, three articles) serve tokens.css?v=phase24. Homepage unchanged: 16 plates, 1 .identity-hero, row heads 01/02/03, single h1, hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. /brand/ at 1280px: all 21 sections, first plates grid one row of span5(368) + span3(216) + span4(292) filling the full 900px with zero right-edge gap — the section's own 'rows must sum to 12' rule holds. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16, sitemap 20, subscribe 200, tokens.css served immutable. Zero console errors on either page.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5608,12 +5608,12 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>FIX (qa/fixes-20260827, af2d31f) — retired, the F94 treatment. Removed: 98 lines from css/plates.css (the section plus both responsive overrides); --identity-plate-bg/-ink from all three blocks of css/tokens.css plus their doc comment and identity-sub from the --track-badge comment; .demo-plate.identity from brand/brand.css; the specimen and the identity-sub mention from brand/index.html; and from DESIGN-SYSTEM.md the Plate Sizes row, three typography-table rows, the hairline exemption and two token comments, with the section itself converted to a retirement note. Confirmed zero surviving var(--identity-plate-*) references anywhere before bumping. Verified first that the surviving .identity-hero shares NO classes with the retired plate — the hero is entirely hero-*, the plate entirely identity-* — so the retirement cannot touch it. Cache-bust tokens.css phase23-&gt;24 across all 7 referencing files, plates.css phase16-&gt;17 across both, brand.css brand7-&gt;8; checked for skew afterwards, 21/21 built pages on tokens phase24. ONE ADDITION, flagged for Dexter: removing a span-4 left the /brand/ plates demo summing to 8 while that section's own prose says 'Rows must sum to 12', so the slot was refilled with a plain span-4 cell carrying a real essay title — plain because the row had none and the Texture Alternation Rule wants one between textured neighbours.</t>
+          <t>FIX (qa/fixes-20260827, af2d31f) — retired, the F94 treatment. Removed: 98 lines from css/plates.css (the section plus both responsive overrides); --identity-plate-bg/-ink from all three blocks of css/tokens.css plus their doc comment and identity-sub from the --track-badge comment; .demo-plate.identity from brand/brand.css; the specimen and the identity-sub mention from brand/index.html; and from DESIGN-SYSTEM.md the Plate Sizes row, three typography-table rows, the hairline exemption and two token comments, with the section itself converted to a retirement note. Confirmed zero surviving var(--identity-plate-*) references anywhere before bumping. Verified first that the surviving .identity-hero shares NO classes with the retired plate — the hero is entirely hero-*, the plate entirely identity-* — so the retirement cannot touch it. Cache-bust tokens.css phase23-&gt;24 across all 7 referencing files, plates.css phase16-&gt;17 across both, brand.css brand7-&gt;8; checked for skew afterwards, 21/21 built pages on tokens phase24. I ALSO ADDED a plain span-4 cell to refill the vacated slot, because that section's prose says 'Rows must sum to 12'. Dexter had not asked for it and REMOVED IT on request (8380486). Adding inside a removal was my call and it was not mine to make.</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-28. Homepage: 0 .identity-plate, 1 .identity-hero, 16 plates, row heads 01/02/03, single h1, --identity-plate-bg resolves to empty. Contrast unchanged on everything the token removal could have touched: hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38. Article page: 4 sheets, single h1, body #060606 on cream. /phase0/: skip link still 6,6,6 on cream, F91 intact. /brand/: 0 identity specimen, all 21 sections, first plates grid now one row of 5+3+4 = 12 filling the full 900px with zero right-edge gap. Brace balance verified in all three edited sheets. Zero console errors on any surface. || CLOSED LIVE 2026-08-28 on deploy 517ab13. Verified on production: 0 .identity-plate on / and on /brand/, 0 identity specimen, `--identity-plate-bg` resolves empty in the live CSSOM, and the shipped tokens.css and plates.css carry zero occurrences. No version skew — all 8 sampled surfaces (home, about, brand, phase0, 404, three articles) serve tokens.css?v=phase24. Homepage unchanged: 16 plates, 1 .identity-hero, row heads 01/02/03, single h1, hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. /brand/ at 1280px: all 21 sections, first plates grid one row of span5(368) + span3(216) + span4(292) filling the full 900px with zero right-edge gap — the section's own 'rows must sum to 12' rule holds. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16, sitemap 20, subscribe 200, tokens.css served immutable. Zero console errors on either page.</t>
+          <t>PASS (verified against build) — 2026-08-28. Homepage: 0 .identity-plate, 1 .identity-hero, 16 plates, row heads 01/02/03, single h1, --identity-plate-bg resolves to empty. Contrast unchanged on everything the token removal could have touched: hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38. Article page: 4 sheets, single h1, body #060606 on cream. /phase0/: skip link still 6,6,6 on cream, F91 intact. /brand/: 0 identity specimen, all 21 sections, first plates grid now one row of 5+3+4 = 12 filling the full 900px with zero right-edge gap. Brace balance verified in all three edited sheets. Zero console errors on any surface. || CLOSED LIVE 2026-08-28 on deploy 517ab13. Verified on production: 0 .identity-plate on / and on /brand/, 0 identity specimen, `--identity-plate-bg` resolves empty in the live CSSOM, and the shipped tokens.css and plates.css carry zero occurrences. No version skew — all 8 sampled surfaces (home, about, brand, phase0, 404, three articles) serve tokens.css?v=phase24. Homepage unchanged: 16 plates, 1 .identity-hero, row heads 01/02/03, single h1, hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. /brand/ at 1280px: all 21 sections, first plates grid one row of span5(368) + span3(216) + span4(292) filling the full 900px with zero right-edge gap — the section's own 'rows must sum to 12' rule holds. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16, sitemap 20, subscribe 200, tokens.css served immutable. Zero console errors on either page. || 2026-08-28, follow-up: the span-4 cell I had added was removed at Dexter's request (8380486). The /brand/ plates demo row now carries two specimens — span5 (368px) + span3 (216px) = 596px of a 900px grid, leaving a 304px trailing gap, 34% of the row. That is a real visual hole and it sits two paragraphs below prose reading 'Rows must sum to 12'. Left as-is deliberately: the alternatives are changing the two remaining spans (misrepresents .plate-wide and .plate-secondary), narrowing that one grid to 8 columns (misrepresents the 12-column system), or inventing another specimen — which is what I did the first time. Dexter's call, recorded here so it is neither inherited as correct nor 'helpfully' filled by a future run.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -5613,7 +5613,7 @@
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-28. Homepage: 0 .identity-plate, 1 .identity-hero, 16 plates, row heads 01/02/03, single h1, --identity-plate-bg resolves to empty. Contrast unchanged on everything the token removal could have touched: hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38. Article page: 4 sheets, single h1, body #060606 on cream. /phase0/: skip link still 6,6,6 on cream, F91 intact. /brand/: 0 identity specimen, all 21 sections, first plates grid now one row of 5+3+4 = 12 filling the full 900px with zero right-edge gap. Brace balance verified in all three edited sheets. Zero console errors on any surface. || CLOSED LIVE 2026-08-28 on deploy 517ab13. Verified on production: 0 .identity-plate on / and on /brand/, 0 identity specimen, `--identity-plate-bg` resolves empty in the live CSSOM, and the shipped tokens.css and plates.css carry zero occurrences. No version skew — all 8 sampled surfaces (home, about, brand, phase0, 404, three articles) serve tokens.css?v=phase24. Homepage unchanged: 16 plates, 1 .identity-hero, row heads 01/02/03, single h1, hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. /brand/ at 1280px: all 21 sections, first plates grid one row of span5(368) + span3(216) + span4(292) filling the full 900px with zero right-edge gap — the section's own 'rows must sum to 12' rule holds. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16, sitemap 20, subscribe 200, tokens.css served immutable. Zero console errors on either page. || 2026-08-28, follow-up: the span-4 cell I had added was removed at Dexter's request (8380486). The /brand/ plates demo row now carries two specimens — span5 (368px) + span3 (216px) = 596px of a 900px grid, leaving a 304px trailing gap, 34% of the row. That is a real visual hole and it sits two paragraphs below prose reading 'Rows must sum to 12'. Left as-is deliberately: the alternatives are changing the two remaining spans (misrepresents .plate-wide and .plate-secondary), narrowing that one grid to 8 columns (misrepresents the 12-column system), or inventing another specimen — which is what I did the first time. Dexter's call, recorded here so it is neither inherited as correct nor 'helpfully' filled by a future run.</t>
+          <t>PASS (verified against build) — 2026-08-28. Homepage: 0 .identity-plate, 1 .identity-hero, 16 plates, row heads 01/02/03, single h1, --identity-plate-bg resolves to empty. Contrast unchanged on everything the token removal could have touched: hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38. Article page: 4 sheets, single h1, body #060606 on cream. /phase0/: skip link still 6,6,6 on cream, F91 intact. /brand/: 0 identity specimen, all 21 sections, first plates grid now one row of 5+3+4 = 12 filling the full 900px with zero right-edge gap. Brace balance verified in all three edited sheets. Zero console errors on any surface. || CLOSED LIVE 2026-08-28 on deploy 517ab13. Verified on production: 0 .identity-plate on / and on /brand/, 0 identity specimen, `--identity-plate-bg` resolves empty in the live CSSOM, and the shipped tokens.css and plates.css carry zero occurrences. No version skew — all 8 sampled surfaces (home, about, brand, phase0, 404, three articles) serve tokens.css?v=phase24. Homepage unchanged: 16 plates, 1 .identity-hero, row heads 01/02/03, single h1, hero-corner 5.23, hero-name 17.79, latest-meta 5.13, meta-rail 17.38, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. /brand/ at 1280px: all 21 sections, first plates grid one row of span5(368) + span3(216) + span4(292) filling the full 900px with zero right-edge gap — the section's own 'rows must sum to 12' rule holds. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16, sitemap 20, subscribe 200, tokens.css served immutable. Zero console errors on either page. || 2026-08-28, follow-up: the span-4 cell I had added was removed at Dexter's request (8380486). The /brand/ plates demo row now carries two specimens — span5 (368px) + span3 (216px) = 596px of a 900px grid, leaving a 304px trailing gap, 34% of the row. That is a real visual hole and it sits two paragraphs below prose reading 'Rows must sum to 12'. Left as-is deliberately: the alternatives are changing the two remaining spans (misrepresents .plate-wide and .plate-secondary), narrowing that one grid to 8 columns (misrepresents the 12-column system), or inventing another specimen — which is what I did the first time. Dexter's call, recorded here so it is neither inherited as correct nor 'helpfully' filled by a future run. || Removal VERIFIED LIVE 2026-08-28 on deploy c94460e: the added cell is gone from production, the first /brand/ plates grid carries span5 + span3 only, and the trailing gap measures 304px of a 900px grid at 1280px viewport — exactly as measured on the build. 21 sections intact, 0 identity specimen, 0 .issue-next. Homepage untouched: 16 plates, 1 .identity-hero, 0 .identity-plate, row heads 01/02/03, single h1. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16, sitemap 20. Zero console errors on either page.</t>
         </is>
       </c>
     </row>

--- a/audit/imjustdex-feature-audit.xlsx
+++ b/audit/imjustdex-feature-audit.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Features'!$A$3:$K$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27. The collection holds no upcoming entry, so verification used a temporary future-dated fixture, removed before commit (git status clean of it). Renders span 5 at 503x230 desktop, span 1 at 339px mobile with no overflow at 375px. Static: cursor default, not a link, not focusable. Contrast clears AA on the values F90 just landed — title 3.40 dark / 3.31 light (floor 3.0); teaser-date, meta rail and lane badge all 5.11 dark / 4.62 light (floor 4.5). Single h1, no skipped heading levels. Lane filter: 9 visible with ghost -&gt; Faith 13 ghost hidden -&gt; clear 9 ghost back -&gt; Art 3 ghost hidden (matching the lane index exactly) -&gt; clear 9. Earlier toggle: expand 17 / collapse 9, glyph tracks, ghost unaffected. With zero upcoming the page is behaviourally identical to before — row heads 01/02/03, no ghost markup. Zero console errors in both modes. Does not surface Dexter's before-i-had-the-words.mdx (status 'drafted' fails isUpcomingData). OBSERVED, not opened as its own row: DESIGN-SYSTEM.md specifies .plate-ghost min-height 346px while plates.css ships 230px. Doc-vs-implementation drift of the F82/F84 class, but the doc file currently carries Dexter's uncommitted 'Two-plane rule' edit, so it is his to reconcile, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 2387e1d. The ghost plate cannot be observed on production yet — the collection holds no upcoming entry — so what was verified live is that the change is INERT until one exists, which is the correct behaviour: row heads read 01 This Week / 02 This Month / 03 Earlier, zero .plate-ghost markup, IssueNext correctly absent (F30), 16 plates, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep clean: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The section-numbering and ghost rendering will first be exercised on production the day Dexter schedules an essay; that run's SCRUB should re-test this row live.</t>
+          <t>PASS (verified against build) — 2026-08-27. The collection holds no upcoming entry, so verification used a temporary future-dated fixture, removed before commit (git status clean of it). Renders span 5 at 503x230 desktop, span 1 at 339px mobile with no overflow at 375px. Static: cursor default, not a link, not focusable. Contrast clears AA on the values F90 just landed — title 3.40 dark / 3.31 light (floor 3.0); teaser-date, meta rail and lane badge all 5.11 dark / 4.62 light (floor 4.5). Single h1, no skipped heading levels. Lane filter: 9 visible with ghost -&gt; Faith 13 ghost hidden -&gt; clear 9 ghost back -&gt; Art 3 ghost hidden (matching the lane index exactly) -&gt; clear 9. Earlier toggle: expand 17 / collapse 9, glyph tracks, ghost unaffected. With zero upcoming the page is behaviourally identical to before — row heads 01/02/03, no ghost markup. Zero console errors in both modes. Does not surface Dexter's before-i-had-the-words.mdx (status 'drafted' fails isUpcomingData). OBSERVED, not opened as its own row: DESIGN-SYSTEM.md specifies .plate-ghost min-height 346px while plates.css ships 230px. Doc-vs-implementation drift of the F82/F84 class, but the doc file currently carries Dexter's uncommitted 'Two-plane rule' edit, so it is his to reconcile, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 2387e1d. The ghost plate cannot be observed on production yet — the collection holds no upcoming entry — so what was verified live is that the change is INERT until one exists, which is the correct behaviour: row heads read 01 This Week / 02 This Month / 03 Earlier, zero .plate-ghost markup, IssueNext correctly absent (F30), 16 plates, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep clean: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The section-numbering and ghost rendering will first be exercised on production the day Dexter schedules an essay; that run's SCRUB should re-test this row live. || 2026-08-31 PRODUCTION GATE STILL UNEXERCISED: VOL 17 'The Weight of My No' was the first real scheduled essay since this row was written, but its release sat unpushed from Aug 29 until Aug 31, i.e. until AFTER its Aug 30 12:00 CDT gate. The pre-gate state therefore never rendered on the live site and this row remains fixture-verified only. Next scheduled essay is the next opportunity.</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 121a621. Like F93, the gate cannot be observed doing its job on production yet — no upcoming entry exists, so the strip would have been absent anyway. What was verified live is that the change is inert: row heads 01 This Week / 02 This Month / 03 Earlier, 16 plates, zero .plate-ghost, zero .issue-next, single h1, SubscribeManifesto form still present, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The gate is first exercised on production the day an essay is scheduled — that run's SCRUB must confirm the ghost renders AND the strip stays absent, and must not read the strip's absence as a regression (see the re-scoped F30). || RETIREMENT VERIFIED against a clean build 2026-08-27: homepage still loads its 5 sheets, 0 `.issue-next` elements, 16 plates, single h1, subscribe manifesto form intact, row heads 01/02/03, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. The prefers-reduced-motion @media block still parses and still applies to its remaining five selectors (F75 unaffected). Brace balance verified in all three edited sheets. /brand/: 0 `.issue-next` elements, all 21 sections intact, heading reads '19. Issue Next (retired)', `.u-retired` renders SF Mono at --body-muted = 5.11:1 dark (AA). Fixture build with an upcoming essay: 1 ghost plate, 0 strips, the title appears exactly once, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier. Zero console errors on either page. NOTE FOR THE NEXT RUN: DESIGN-SYSTEM.md:1413 still describes 'the homepage's issue-next ghost CTA' while explaining the `next.ghost` frontmatter flag — that sentence already conflated this strip with ArticleLayout's `.article-nav-ghost` (which stays), and the retirement makes it more wrong. Left alone because that file carries Dexter's uncommitted Two-plane-rule edit; his to reconcile. || RETIREMENT SHIPPED LIVE 2026-08-27 on deploy 3b46f34. Verified on production, not inferred: the homepage serves home-v2.css?v=phase36 and home-augment.css?v=phase34 and the CSSOM reports ZERO rules whose selectorText contains 'issue-next' across every loaded sheet, on both / and /brand/; zero `.issue-next` elements on either page. The only surviving mentions anywhere are three CSS comments, confirmed by fetching the shipped sheets. Homepage otherwise unchanged: 16 plates, row heads 01/02/03, single h1, subscribe form present, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16 with the glyph tracking, prefers-reduced-motion block still present (F75 intact). /brand/ keeps all 21 sections and reads '19. Issue Next (retired)'. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs, subscribe function 200. Zero console errors on either page.</t>
+          <t>PASS (verified against build) — 2026-08-27 on a clean build with a temporary future-dated fixture (removed before commit). With an upcoming essay: 1 ghost plate, 0 IssueNext strips, the upcoming title appears exactly once on the page, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier, single h1, zero console errors. Lane filter and earlier toggle unaffected (9 -&gt; Faith 13 -&gt; clear 9 -&gt; expand 17 -&gt; collapse 9). With zero upcoming the page is byte-identical to before. CONSEQUENCES RECORDED, not defects but changes: (a) the upcoming essay's coming-soon page now has ZERO inbound links from the homepage — the ghost plate is static per DESIGN-SYSTEM.md and the strip was the only link; the page still builds and stays correctly out of the sitemap and feed, and its documented purpose is to be a landing target for social shares and dispatch teasers rather than somewhere you navigate to; (b) the essay-specific 'Notify me →' CTA goes with it — site-wide subscribe is unaffected, the SubscribeManifesto form is still on the page. If Dexter wants the CTA back without the duplicate, the move is to make the ghost plate linkable, which contradicts the doc's 'static' rule and is therefore his call, not the loop's. || SHIPPED LIVE 2026-08-27 on deploy 121a621. Like F93, the gate cannot be observed doing its job on production yet — no upcoming entry exists, so the strip would have been absent anyway. What was verified live is that the change is inert: row heads 01 This Week / 02 This Month / 03 Earlier, 16 plates, zero .plate-ghost, zero .issue-next, single h1, SubscribeManifesto form still present, lane filter Faith 13 and clear back to 8, earlier toggle 8&lt;-&gt;16 with the glyph tracking, zero console errors. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs. The gate is first exercised on production the day an essay is scheduled — that run's SCRUB must confirm the ghost renders AND the strip stays absent, and must not read the strip's absence as a regression (see the re-scoped F30). || RETIREMENT VERIFIED against a clean build 2026-08-27: homepage still loads its 5 sheets, 0 `.issue-next` elements, 16 plates, single h1, subscribe manifesto form intact, row heads 01/02/03, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16. The prefers-reduced-motion @media block still parses and still applies to its remaining five selectors (F75 unaffected). Brace balance verified in all three edited sheets. /brand/: 0 `.issue-next` elements, all 21 sections intact, heading reads '19. Issue Next (retired)', `.u-retired` renders SF Mono at --body-muted = 5.11:1 dark (AA). Fixture build with an upcoming essay: 1 ghost plate, 0 strips, the title appears exactly once, row heads 01 Next / 02 This Week / 03 This Month / 04 Earlier. Zero console errors on either page. NOTE FOR THE NEXT RUN: DESIGN-SYSTEM.md:1413 still describes 'the homepage's issue-next ghost CTA' while explaining the `next.ghost` frontmatter flag — that sentence already conflated this strip with ArticleLayout's `.article-nav-ghost` (which stays), and the retirement makes it more wrong. Left alone because that file carries Dexter's uncommitted Two-plane-rule edit; his to reconcile. || RETIREMENT SHIPPED LIVE 2026-08-27 on deploy 3b46f34. Verified on production, not inferred: the homepage serves home-v2.css?v=phase36 and home-augment.css?v=phase34 and the CSSOM reports ZERO rules whose selectorText contains 'issue-next' across every loaded sheet, on both / and /brand/; zero `.issue-next` elements on either page. The only surviving mentions anywhere are three CSS comments, confirmed by fetching the shipped sheets. Homepage otherwise unchanged: 16 plates, row heads 01/02/03, single h1, subscribe form present, filter Faith 13 -&gt; clear 8, toggle 8&lt;-&gt;16 with the glyph tracking, prefers-reduced-motion block still present (F75 intact). /brand/ keeps all 21 sections and reads '19. Issue Next (retired)'. Sweep: 25 routes 200, both correct 404s, 5/5 security headers, feed 16 entries, sitemap 20 locs, subscribe function 200. Zero console errors on either page. || 2026-08-31 PRODUCTION GATE STILL UNEXERCISED: VOL 17 'The Weight of My No' was the first real scheduled essay since this row was written, but its release sat unpushed from Aug 29 until Aug 31, i.e. until AFTER its Aug 30 12:00 CDT gate. The pre-gate state therefore never rendered on the live site and this row remains fixture-verified only. Next scheduled essay is the next opportunity.</t>
         </is>
       </c>
     </row>
@@ -5617,8 +5617,110 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>F96</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>VOL 17 'The Weight of My No' — scheduled essay through the date gate</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>As a reader arriving from social or the Dispatch after the publish moment, I want the essay URL to resolve to the full article, indexed and linked from the archive, so the link I was given is never a dead end.</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>With status "published" and publishedDate in the future, /words/the-weight-of-my-no/ renders ComingSoonLayout and stays out of the sitemap. On the first build after publishedDate passes, it renders the full ArticleLayout and enters sitemap, feed and the homepage cascade, and the forward link on 'Send Someone Else' drops its ghost treatment with no second edit.</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>src/content/words/the-weight-of-my-no.mdx; src/content/words/send-someone-else.mdx; src/utils/published.mjs; src/layouts/ArticleLayout.astro; img/og-the-weight-of-my-no.png</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-31</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>PASS (2026-08-31, live on 13b631c then 83c2137) — POST-gate half verified live end to end: article 200 with 55 paragraphs and zero coming-soon markers; present in sitemap-0.xml, feed.xml and the homepage cascade (latest strip, lead plate, 'Week of August 31, 2026'); 'Send Someone Else' renders 0 .article-nav-ghost, i.e. the ghost treatment retired itself on go-live exactly as designed. OG plate 1200x630 (1.905), reads VOL 17 matching the essay's own number, title clears Anton's caps on the .92 leading from 9301d61. Metadata complete (description, og:title/image/image:alt/type, twitter:summary_large_image, canonical). Redate to Aug 31 propagated to every surface: JSON-LD datePublished 2026-08-31T12:00:00-05:00, Atom &lt;published&gt; 2026-08-31T17:00:00Z, homepage &lt;time datetime="2026-08-31"&gt;, zero 'Aug 30' anywhere live. Contrast 87 elements / 0 failures in BOTH modes (dark floor 5.13:1, light 4.67:1). Single h1, h1-&gt;h2 with no skipped level, skip link takes first Tab with a visible ring, 0 unnamed interactive elements, 0 console errors. || PRE-gate half NOT verified in production — see F93/F94: the release sat unpushed from Aug 29 until after the Aug 30 noon gate, so the Coming-Soon route never rendered on the live site for this essay.</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr"/>
+      <c r="J99" s="4" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>F97</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Article</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>.article-eyebrow metadata rail — wraps instead of overflowing on mobile</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>As a reader on a phone, I want every chip in the metadata rail — lanes, tags, date, read-time — to stay readable, so the header does not silently drop information I cannot scroll to.</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>.article-eyebrow is a flex row shared by all 17 article pages and /about/. At narrow viewports it must wrap so every child stays inside the article frame and inside the viewport. body and .page-shell are overflow-x: clip, so anything past the edge is unreachable rather than scrollable — an overflowing rail is lost content, not offscreen content (WCAG 2.2 SC 1.4.10 Reflow).</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>css/article.css:31 (.article-eyebrow), css/article.css:918-925 (max-width:760px block); src/layouts/ArticleLayout.astro:112; src/layouts/ComingSoonLayout.astro:67; src/pages/about.astro:65,100</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>Cataloged 2026-08-31</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
+          <t>ISSUE/High (2026-08-31) — .article-eyebrow shipped flex-wrap: nowrap with no mobile override, so the rail runs off the frame on every article. Measured LIVE at 375px on /words/the-weight-of-my-no/ (6 chips: 2 lanes + 2 tags + date + read-time): scrollWidth 406 vs clientWidth 362 = 105px overflow; .article-read sits at left:418 against a 375px viewport, i.e. '8 min' is 100% invisible and 'Aug 31, 2026' is 92% clipped. Control /words/send-someone-else/ (5 chips) overflows 39px and loses 2px of '16 min', confirming this is site-wide and pre-existing rather than introduced by VOL 17 — VOL 17 is simply the worst case, being the first 6-chip essay. Because body/.page-shell are overflow-x: clip there is no scrollbar and no gesture that reaches the clipped text. Survived every prior scrub because source-only inspection cannot see it: the CSS is valid, the defect only exists once the flex row is laid out under 760px.</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>High (fixed)</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>FIX (qa/fixes-20260831) — css/article.css: added `flex-wrap: wrap` to .article-eyebrow inside the EXISTING @media (max-width: 760px) block (4 lines, no new breakpoint, no new token). Cache-bust article.css phase24-&gt;phase37 in all THREE references — ArticleLayout.astro, ComingSoonLayout.astro and about.astro — because /css/* is served `max-age=31536000, immutable`, so without the bump every returning reader keeps the year-cached phase24 sheet and never receives the fix. phase37 was unused anywhere in repo history; 36 was the high-water mark.</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>PASS (verified against build) — 2026-08-31 on a clean `npm run build` served from dist at 375x812. ALL 18 pages carrying .article-eyebrow re-tested, not a sample: about (1 chip), gumbo/job/next-verse/price-of-sunday (3), gloria/outsourced-faith/pulpit/reckonings/show-me-your-glory/some/the-nets/the-stone (4), music-that-raised-me/not-the-same-as-alive/send-someone-else/should-have-killed-it (5), the-weight-of-my-no (6). Every page: flex-wrap resolves `wrap`, eyebrow overflow 0px, every chip fully visible, document horizontal scroll 0. Regression check at a true emulated 1280px desktop: local build and live production are identical (flex-wrap nowrap, overflow 0) — the change is mobile-only and touches no desktop layout. Built pages confirmed serving article.css?v=phase37.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:K98"/>
+  <autoFilter ref="A3:K100"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -5661,7 +5763,7 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -5698,7 +5800,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -5718,7 +5820,7 @@
         </is>
       </c>
       <c r="B11" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -5745,7 +5847,7 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -5761,7 +5863,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Total features: 95</t>
+          <t>Total features: 97</t>
         </is>
       </c>
     </row>
